--- a/research/traditional_assets/database/data/ireland/ireland_drugs_biotechnology.xlsx
+++ b/research/traditional_assets/database/data/ireland/ireland_drugs_biotechnology.xlsx
@@ -353,7 +353,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ3"/>
+  <dimension ref="A1:AQ4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -581,7 +581,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -596,31 +596,31 @@
         <v>0.134</v>
       </c>
       <c r="G2">
-        <v>0.5023586472659625</v>
+        <v>0.4572453657564282</v>
       </c>
       <c r="H2">
-        <v>0.3288818018736297</v>
+        <v>0.2012490864394392</v>
       </c>
       <c r="I2">
-        <v>0.2081904311289989</v>
+        <v>0.10482214920394</v>
       </c>
       <c r="J2">
-        <v>0.2081904311289989</v>
+        <v>0.10482214920394</v>
       </c>
       <c r="K2">
-        <v>333.3</v>
+        <v>179.5</v>
       </c>
       <c r="L2">
-        <v>0.221447079928244</v>
+        <v>0.1192611786592253</v>
       </c>
       <c r="M2">
         <v>232</v>
       </c>
       <c r="N2">
-        <v>0.04985601925473847</v>
+        <v>0.04927363860334721</v>
       </c>
       <c r="O2">
-        <v>0.6960696069606961</v>
+        <v>1.292479108635098</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -638,55 +638,55 @@
         <v>1</v>
       </c>
       <c r="U2">
-        <v>396.3</v>
+        <v>507.3</v>
       </c>
       <c r="V2">
-        <v>0.08516353633902093</v>
+        <v>0.107743607170164</v>
       </c>
       <c r="W2">
-        <v>0.245868987902036</v>
+        <v>11.28403754184652</v>
       </c>
       <c r="X2">
-        <v>0.1088333762389972</v>
+        <v>0.1132950608557304</v>
       </c>
       <c r="Y2">
-        <v>0.1370356116630388</v>
+        <v>11.17074248099079</v>
       </c>
       <c r="Z2">
-        <v>1.530875487537755</v>
+        <v>1.520040606553277</v>
       </c>
       <c r="AA2">
-        <v>0.3187136277553016</v>
+        <v>-0.3406431861223492</v>
       </c>
       <c r="AB2">
-        <v>0.1053699107105566</v>
+        <v>0.1058654333012188</v>
       </c>
       <c r="AC2">
-        <v>0.213343717044745</v>
+        <v>-0.446508619423568</v>
       </c>
       <c r="AD2">
         <v>288.8</v>
       </c>
       <c r="AE2">
-        <v>76.76291053871914</v>
+        <v>90.6609161657497</v>
       </c>
       <c r="AF2">
-        <v>365.5629105387192</v>
+        <v>379.4609161657497</v>
       </c>
       <c r="AG2">
-        <v>-30.73708946128085</v>
+        <v>-127.8390838342503</v>
       </c>
       <c r="AH2">
-        <v>0.07283634429159008</v>
+        <v>0.07458162131753286</v>
       </c>
       <c r="AI2">
-        <v>0.2205291004670641</v>
+        <v>0.2055962245513966</v>
       </c>
       <c r="AJ2">
-        <v>-0.006649217140883583</v>
+        <v>-0.02790904567671607</v>
       </c>
       <c r="AK2">
-        <v>-0.02436815701846922</v>
+        <v>-0.09551914008404742</v>
       </c>
       <c r="AL2">
         <v>24</v>
@@ -695,16 +695,16 @@
         <v>-16.8</v>
       </c>
       <c r="AN2">
-        <v>0.7828679859040389</v>
+        <v>1.316917464660283</v>
       </c>
       <c r="AO2">
-        <v>13.275</v>
+        <v>6.6375</v>
       </c>
       <c r="AP2">
-        <v>-0.08332092562017035</v>
+        <v>-0.5829415587517112</v>
       </c>
       <c r="AQ2">
-        <v>-18.96428571428572</v>
+        <v>-9.482142857142859</v>
       </c>
     </row>
     <row r="3">
@@ -781,10 +781,10 @@
         <v>0.245868987902036</v>
       </c>
       <c r="X3">
-        <v>0.1088333762389972</v>
+        <v>0.1088039390308511</v>
       </c>
       <c r="Y3">
-        <v>0.1370356116630388</v>
+        <v>0.1370650488711849</v>
       </c>
       <c r="Z3">
         <v>1.530875487537755</v>
@@ -793,10 +793,10 @@
         <v>0.3187136277553016</v>
       </c>
       <c r="AB3">
-        <v>0.1053699107105566</v>
+        <v>0.1053426176010381</v>
       </c>
       <c r="AC3">
-        <v>0.213343717044745</v>
+        <v>0.2133710101542635</v>
       </c>
       <c r="AD3">
         <v>288.8</v>
@@ -839,6 +839,110 @@
       </c>
       <c r="AQ3">
         <v>-18.96428571428572</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Mural Oncology plc (NasdaqGM:MURA)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Drugs (Biotechnology)</t>
+        </is>
+      </c>
+      <c r="K4">
+        <v>-153.8</v>
+      </c>
+      <c r="M4">
+        <v>-0</v>
+      </c>
+      <c r="N4">
+        <v>-0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>-0</v>
+      </c>
+      <c r="Q4">
+        <v>-0</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>111</v>
+      </c>
+      <c r="V4">
+        <v>2.018181818181818</v>
+      </c>
+      <c r="W4">
+        <v>22.322206095791</v>
+      </c>
+      <c r="X4">
+        <v>0.1177861826806096</v>
+      </c>
+      <c r="Y4">
+        <v>22.20441991311039</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+      <c r="AA4">
+        <v>-1</v>
+      </c>
+      <c r="AB4">
+        <v>0.1063882490013995</v>
+      </c>
+      <c r="AC4">
+        <v>-1.106388249001399</v>
+      </c>
+      <c r="AD4">
+        <v>0</v>
+      </c>
+      <c r="AE4">
+        <v>13.89800562703055</v>
+      </c>
+      <c r="AF4">
+        <v>13.89800562703055</v>
+      </c>
+      <c r="AG4">
+        <v>-97.10199437296944</v>
+      </c>
+      <c r="AH4">
+        <v>0.2017185475914267</v>
+      </c>
+      <c r="AI4">
+        <v>0.07392634608370698</v>
+      </c>
+      <c r="AJ4">
+        <v>2.306351416818188</v>
+      </c>
+      <c r="AK4">
+        <v>-1.261097525607615</v>
+      </c>
+      <c r="AL4">
+        <v>0</v>
+      </c>
+      <c r="AM4">
+        <v>0</v>
+      </c>
+      <c r="AN4">
+        <v>-0</v>
+      </c>
+      <c r="AP4">
+        <v>0.6490775024931112</v>
       </c>
     </row>
   </sheetData>
@@ -1133,7 +1237,7 @@
         <v>14.95</v>
       </c>
       <c r="F2">
-        <v>13.781530777661</v>
+        <v>14.1246193956073</v>
       </c>
       <c r="G2">
         <v>0.990953945618648</v>
@@ -1151,13 +1255,13 @@
         <v>4653.4</v>
       </c>
       <c r="L2">
-        <v>4628.69034540379</v>
+        <v>4636.89869236138</v>
       </c>
       <c r="M2">
         <v>4622.66291053872</v>
       </c>
       <c r="N2">
-        <v>4684.09700735228</v>
+        <v>4692.30535430986</v>
       </c>
       <c r="O2">
         <v>365.562910538719</v>
@@ -1166,16 +1270,16 @@
         <v>451.706661948485</v>
       </c>
       <c r="Q2">
-        <v>0.105369910710557</v>
+        <v>0.105342617601038</v>
       </c>
       <c r="R2">
-        <v>0.104532601698152</v>
+        <v>0.104395117682851</v>
       </c>
       <c r="S2">
         <v>0.0612820395797173</v>
       </c>
       <c r="T2">
-        <v>0.0504320395797173</v>
+        <v>0.0492070395797173</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -1188,10 +1292,10 @@
         </is>
       </c>
       <c r="W2">
-        <v>0.108833376238997</v>
+        <v>0.108803939030851</v>
       </c>
       <c r="X2">
-        <v>0.109883206742832</v>
+        <v>0.10985327925349</v>
       </c>
       <c r="Y2">
         <v>1.22806404088134</v>
@@ -1230,7 +1334,7 @@
         <v>4653.4</v>
       </c>
       <c r="AK2">
-        <v>0.05132743418963755</v>
+        <v>0.05130346377183671</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
@@ -1418,13 +1522,13 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.1047792345243763</v>
+        <v>0.1047516906403805</v>
       </c>
       <c r="C2">
-        <v>5062.132351382909</v>
+        <v>5062.151926770843</v>
       </c>
       <c r="D2">
-        <v>4665.832351382909</v>
+        <v>4665.851926770843</v>
       </c>
       <c r="E2">
         <v>-365.5629105387191</v>
@@ -1469,19 +1573,19 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0.1047792345243763</v>
+        <v>0.1047516906403805</v>
       </c>
       <c r="T2">
         <v>1.149078177305102</v>
       </c>
       <c r="U2">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V2">
         <v>0.125</v>
       </c>
       <c r="W2">
-        <v>0.05043203957971733</v>
+        <v>0.04920703957971734</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1500,13 +1604,13 @@
         <v>0.01</v>
       </c>
       <c r="B3">
-        <v>0.104751830877018</v>
+        <v>0.1047120714228772</v>
       </c>
       <c r="C3">
-        <v>5013.965091452108</v>
+        <v>5014.88682884293</v>
       </c>
       <c r="D3">
-        <v>4667.854720557495</v>
+        <v>4668.776457948317</v>
       </c>
       <c r="E3">
         <v>-315.373281433332</v>
@@ -1533,37 +1637,37 @@
         <v>358.8</v>
       </c>
       <c r="M3">
-        <v>2.892760413181965</v>
+        <v>2.822494932434423</v>
       </c>
       <c r="N3">
-        <v>355.907239586818</v>
+        <v>355.9775050675656</v>
       </c>
       <c r="O3">
-        <v>44.48840494835225</v>
+        <v>44.4971881334457</v>
       </c>
       <c r="P3">
-        <v>311.4188346384658</v>
+        <v>311.4803169341199</v>
       </c>
       <c r="Q3">
-        <v>321.5188346384658</v>
+        <v>321.5803169341199</v>
       </c>
       <c r="R3">
         <v>0.0101010101010101</v>
       </c>
       <c r="S3">
-        <v>0.1053005156375968</v>
+        <v>0.1052727283101818</v>
       </c>
       <c r="T3">
         <v>1.159234171296435</v>
       </c>
       <c r="U3">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V3">
         <v>0.125</v>
       </c>
       <c r="W3">
-        <v>0.05043203957971733</v>
+        <v>0.04920703957971734</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1571,7 +1675,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>124.0337769989492</v>
+        <v>127.121574560466</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1582,13 +1686,13 @@
         <v>0.02</v>
       </c>
       <c r="B4">
-        <v>0.1047244272296597</v>
+        <v>0.1046724522053738</v>
       </c>
       <c r="C4">
-        <v>4965.799585442283</v>
+        <v>4967.625399375574</v>
       </c>
       <c r="D4">
-        <v>4669.878843653058</v>
+        <v>4671.704657586348</v>
       </c>
       <c r="E4">
         <v>-265.1836523279447</v>
@@ -1615,37 +1719,37 @@
         <v>358.8</v>
       </c>
       <c r="M4">
-        <v>5.78552082636393</v>
+        <v>5.644989864868847</v>
       </c>
       <c r="N4">
-        <v>353.0144791736361</v>
+        <v>353.1550101351312</v>
       </c>
       <c r="O4">
-        <v>44.12680989670451</v>
+        <v>44.1443762668914</v>
       </c>
       <c r="P4">
-        <v>308.8876692769315</v>
+        <v>309.0106338682398</v>
       </c>
       <c r="Q4">
-        <v>318.9876692769316</v>
+        <v>319.1106338682398</v>
       </c>
       <c r="R4">
         <v>0.02040816326530612</v>
       </c>
       <c r="S4">
-        <v>0.105832435140883</v>
+        <v>0.1058043994018158</v>
       </c>
       <c r="T4">
         <v>1.169597430471265</v>
       </c>
       <c r="U4">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V4">
         <v>0.125</v>
       </c>
       <c r="W4">
-        <v>0.05043203957971733</v>
+        <v>0.04920703957971734</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1653,7 +1757,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>62.0168884994746</v>
+        <v>63.56078728023301</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1664,13 +1768,13 @@
         <v>0.03</v>
       </c>
       <c r="B5">
-        <v>0.1046970235823014</v>
+        <v>0.1046328329878706</v>
       </c>
       <c r="C5">
-        <v>4917.635835636085</v>
+        <v>4920.367645275541</v>
       </c>
       <c r="D5">
-        <v>4671.904722952247</v>
+        <v>4674.636532591702</v>
       </c>
       <c r="E5">
         <v>-214.9940232225576</v>
@@ -1697,37 +1801,37 @@
         <v>358.8</v>
       </c>
       <c r="M5">
-        <v>8.678281239545896</v>
+        <v>8.467484797303269</v>
       </c>
       <c r="N5">
-        <v>350.1217187604541</v>
+        <v>350.3325152026968</v>
       </c>
       <c r="O5">
-        <v>43.76521484505676</v>
+        <v>43.79156440033709</v>
       </c>
       <c r="P5">
-        <v>306.3565039153973</v>
+        <v>306.5409508023596</v>
       </c>
       <c r="Q5">
-        <v>316.4565039153973</v>
+        <v>316.6409508023597</v>
       </c>
       <c r="R5">
         <v>0.03092783505154639</v>
       </c>
       <c r="S5">
-        <v>0.1063753220566081</v>
+        <v>0.106347032783999</v>
       </c>
       <c r="T5">
         <v>1.180174365092998</v>
       </c>
       <c r="U5">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V5">
         <v>0.125</v>
       </c>
       <c r="W5">
-        <v>0.05043203957971733</v>
+        <v>0.04920703957971734</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1735,7 +1839,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>41.34459233298306</v>
+        <v>42.37385818682201</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1746,13 +1850,13 @@
         <v>0.04</v>
       </c>
       <c r="B6">
-        <v>0.1046696199349431</v>
+        <v>0.1045932137703673</v>
       </c>
       <c r="C6">
-        <v>4869.473844320125</v>
+        <v>4873.113573466957</v>
       </c>
       <c r="D6">
-        <v>4673.932360741674</v>
+        <v>4677.572089888506</v>
       </c>
       <c r="E6">
         <v>-164.8043941171704</v>
@@ -1779,37 +1883,37 @@
         <v>358.8</v>
       </c>
       <c r="M6">
-        <v>11.57104165272786</v>
+        <v>11.28997972973769</v>
       </c>
       <c r="N6">
-        <v>347.2289583472722</v>
+        <v>347.5100202702623</v>
       </c>
       <c r="O6">
-        <v>43.40361979340902</v>
+        <v>43.43875253378279</v>
       </c>
       <c r="P6">
-        <v>303.8253385538632</v>
+        <v>304.0712677364795</v>
       </c>
       <c r="Q6">
-        <v>313.9253385538632</v>
+        <v>314.1712677364795</v>
       </c>
       <c r="R6">
         <v>0.04166666666666667</v>
       </c>
       <c r="S6">
-        <v>0.1069295191164109</v>
+        <v>0.106900971028311</v>
       </c>
       <c r="T6">
         <v>1.190971652519351</v>
       </c>
       <c r="U6">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V6">
         <v>0.125</v>
       </c>
       <c r="W6">
-        <v>0.05043203957971733</v>
+        <v>0.04920703957971734</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1817,7 +1921,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>31.0084442497373</v>
+        <v>31.7803936401165</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1828,13 +1932,13 @@
         <v>0.05</v>
       </c>
       <c r="B7">
-        <v>0.1046422162875848</v>
+        <v>0.1045535945528639</v>
       </c>
       <c r="C7">
-        <v>4821.313613784984</v>
+        <v>4825.863190891351</v>
       </c>
       <c r="D7">
-        <v>4675.96175931192</v>
+        <v>4680.511336418287</v>
       </c>
       <c r="E7">
         <v>-114.6147650117832</v>
@@ -1861,37 +1965,37 @@
         <v>358.8</v>
       </c>
       <c r="M7">
-        <v>14.46380206590983</v>
+        <v>14.11247466217212</v>
       </c>
       <c r="N7">
-        <v>344.3361979340902</v>
+        <v>344.6875253378279</v>
       </c>
       <c r="O7">
-        <v>43.04202474176127</v>
+        <v>43.08594066722848</v>
       </c>
       <c r="P7">
-        <v>301.2941731923289</v>
+        <v>301.6015846705994</v>
       </c>
       <c r="Q7">
-        <v>311.3941731923289</v>
+        <v>311.7015846705994</v>
       </c>
       <c r="R7">
         <v>0.05263157894736843</v>
       </c>
       <c r="S7">
-        <v>0.1074953834827357</v>
+        <v>0.107466571130398</v>
       </c>
       <c r="T7">
         <v>1.201996251259942</v>
       </c>
       <c r="U7">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V7">
         <v>0.125</v>
       </c>
       <c r="W7">
-        <v>0.05043203957971733</v>
+        <v>0.04920703957971734</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1899,7 +2003,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>24.80675539978984</v>
+        <v>25.4243149120932</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1910,13 +2014,13 @@
         <v>0.06</v>
       </c>
       <c r="B8">
-        <v>0.1046148126402265</v>
+        <v>0.1045139753353607</v>
       </c>
       <c r="C8">
-        <v>4773.155146325229</v>
+        <v>4778.6165045077</v>
       </c>
       <c r="D8">
-        <v>4677.992920957552</v>
+        <v>4683.454279140024</v>
       </c>
       <c r="E8">
         <v>-64.42513590639601</v>
@@ -1943,37 +2047,37 @@
         <v>358.8</v>
       </c>
       <c r="M8">
-        <v>17.35656247909179</v>
+        <v>16.93496959460654</v>
       </c>
       <c r="N8">
-        <v>341.4434375209082</v>
+        <v>341.8650304053935</v>
       </c>
       <c r="O8">
-        <v>42.68042969011353</v>
+        <v>42.73312880067419</v>
       </c>
       <c r="P8">
-        <v>298.7630078307947</v>
+        <v>299.1319016047193</v>
       </c>
       <c r="Q8">
-        <v>308.8630078307947</v>
+        <v>309.2319016047193</v>
       </c>
       <c r="R8">
         <v>0.06382978723404255</v>
       </c>
       <c r="S8">
-        <v>0.1080732875164293</v>
+        <v>0.1080442052772102</v>
       </c>
       <c r="T8">
         <v>1.213255415931185</v>
       </c>
       <c r="U8">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V8">
         <v>0.125</v>
       </c>
       <c r="W8">
-        <v>0.05043203957971733</v>
+        <v>0.04920703957971734</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1981,7 +2085,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>20.67229616649153</v>
+        <v>21.186929093411</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1992,13 +2096,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="B9">
-        <v>0.1045874089928682</v>
+        <v>0.1044743561178573</v>
       </c>
       <c r="C9">
-        <v>4724.998444239412</v>
+        <v>4731.373521292508</v>
       </c>
       <c r="D9">
-        <v>4680.025847977122</v>
+        <v>4686.400925030219</v>
       </c>
       <c r="E9">
         <v>-14.2355068010088</v>
@@ -2025,37 +2129,37 @@
         <v>358.8</v>
       </c>
       <c r="M9">
-        <v>20.24932289227376</v>
+        <v>19.75746452704097</v>
       </c>
       <c r="N9">
-        <v>338.5506771077262</v>
+        <v>339.0425354729591</v>
       </c>
       <c r="O9">
-        <v>42.31883463846578</v>
+        <v>42.38031693411988</v>
       </c>
       <c r="P9">
-        <v>296.2318424692605</v>
+        <v>296.6622185388392</v>
       </c>
       <c r="Q9">
-        <v>306.3318424692605</v>
+        <v>306.7622185388392</v>
       </c>
       <c r="R9">
         <v>0.07526881720430109</v>
       </c>
       <c r="S9">
-        <v>0.1086636195938581</v>
+        <v>0.1086342616637389</v>
       </c>
       <c r="T9">
         <v>1.224756713176003</v>
       </c>
       <c r="U9">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V9">
         <v>0.125</v>
       </c>
       <c r="W9">
-        <v>0.05043203957971733</v>
+        <v>0.04920703957971734</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2063,7 +2167,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>17.71911099984988</v>
+        <v>18.16022493720943</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2074,13 +2178,13 @@
         <v>0.08</v>
       </c>
       <c r="B10">
-        <v>0.1045600053455099</v>
+        <v>0.1044347369003541</v>
       </c>
       <c r="C10">
-        <v>4676.843509830081</v>
+        <v>4684.134248239835</v>
       </c>
       <c r="D10">
-        <v>4682.060542673178</v>
+        <v>4689.351281082932</v>
       </c>
       <c r="E10">
         <v>35.95412230437836</v>
@@ -2107,37 +2211,37 @@
         <v>358.8</v>
       </c>
       <c r="M10">
-        <v>23.14208330545572</v>
+        <v>22.57995945947539</v>
       </c>
       <c r="N10">
-        <v>335.6579166945443</v>
+        <v>336.2200405405246</v>
       </c>
       <c r="O10">
-        <v>41.95723958681803</v>
+        <v>42.02750506756558</v>
       </c>
       <c r="P10">
-        <v>293.7006771077262</v>
+        <v>294.192535472959</v>
       </c>
       <c r="Q10">
-        <v>303.8006771077262</v>
+        <v>304.2925354729591</v>
       </c>
       <c r="R10">
         <v>0.08695652173913043</v>
       </c>
       <c r="S10">
-        <v>0.109266784977318</v>
+        <v>0.1092371453630181</v>
       </c>
       <c r="T10">
         <v>1.236508038621795</v>
       </c>
       <c r="U10">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V10">
         <v>0.125</v>
       </c>
       <c r="W10">
-        <v>0.05043203957971733</v>
+        <v>0.04920703957971734</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2145,7 +2249,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>15.50422212486865</v>
+        <v>15.89019682005825</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2156,13 +2260,13 @@
         <v>0.09</v>
       </c>
       <c r="B11">
-        <v>0.1045326016981516</v>
+        <v>0.1043951176828507</v>
       </c>
       <c r="C11">
-        <v>4628.690345403792</v>
+        <v>4636.898692361377</v>
       </c>
       <c r="D11">
-        <v>4684.097007352277</v>
+        <v>4692.305354309861</v>
       </c>
       <c r="E11">
         <v>86.14375140976551</v>
@@ -2189,37 +2293,37 @@
         <v>358.8</v>
       </c>
       <c r="M11">
-        <v>26.03484371863768</v>
+        <v>25.40245439190981</v>
       </c>
       <c r="N11">
-        <v>332.7651562813624</v>
+        <v>333.3975456080902</v>
       </c>
       <c r="O11">
-        <v>41.59564453517029</v>
+        <v>41.67469320101127</v>
       </c>
       <c r="P11">
-        <v>291.169511746192</v>
+        <v>291.7228524070789</v>
       </c>
       <c r="Q11">
-        <v>301.2695117461921</v>
+        <v>301.8228524070789</v>
       </c>
       <c r="R11">
         <v>0.0989010989010989</v>
       </c>
       <c r="S11">
-        <v>0.1098832067428319</v>
+        <v>0.1098532792534903</v>
       </c>
       <c r="T11">
         <v>1.248517634956505</v>
       </c>
       <c r="U11">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V11">
         <v>0.125</v>
       </c>
       <c r="W11">
-        <v>0.05043203957971733</v>
+        <v>0.04920703957971734</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2227,7 +2331,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>13.78153077766102</v>
+        <v>14.12461939560733</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2238,13 +2342,13 @@
         <v>0.1</v>
       </c>
       <c r="B12">
-        <v>0.1046014480507933</v>
+        <v>0.1044867484653475</v>
       </c>
       <c r="C12">
-        <v>4573.387855164877</v>
+        <v>4579.882565160137</v>
       </c>
       <c r="D12">
-        <v>4678.984146218749</v>
+        <v>4685.478856214009</v>
       </c>
       <c r="E12">
         <v>136.3333805151528</v>
@@ -2271,37 +2375,37 @@
         <v>358.8</v>
       </c>
       <c r="M12">
-        <v>29.47969005197891</v>
+        <v>28.97779376092504</v>
       </c>
       <c r="N12">
-        <v>329.3203099480211</v>
+        <v>329.8222062390749</v>
       </c>
       <c r="O12">
-        <v>41.16503874350263</v>
+        <v>41.22777577988437</v>
       </c>
       <c r="P12">
-        <v>288.1552712045184</v>
+        <v>288.5944304591906</v>
       </c>
       <c r="Q12">
-        <v>298.2552712045185</v>
+        <v>298.6944304591906</v>
       </c>
       <c r="R12">
         <v>0.1111111111111111</v>
       </c>
       <c r="S12">
-        <v>0.1105133267698018</v>
+        <v>0.1104831050081952</v>
       </c>
       <c r="T12">
         <v>1.260794111209765</v>
       </c>
       <c r="U12">
-        <v>0.0587366166625341</v>
+        <v>0.05773661666253409</v>
       </c>
       <c r="V12">
         <v>0.125</v>
       </c>
       <c r="W12">
-        <v>0.05139453957971733</v>
+        <v>0.05051953957971733</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2309,7 +2413,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>12.17109132990747</v>
+        <v>12.38189501106264</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2320,13 +2424,13 @@
         <v>0.11</v>
       </c>
       <c r="B13">
-        <v>0.1045836694034351</v>
+        <v>0.1044602542478442</v>
       </c>
       <c r="C13">
-        <v>4524.517484564996</v>
+        <v>4531.664714506335</v>
       </c>
       <c r="D13">
-        <v>4680.303404724255</v>
+        <v>4687.450634665594</v>
       </c>
       <c r="E13">
         <v>186.5230096205399</v>
@@ -2353,37 +2457,37 @@
         <v>358.8</v>
       </c>
       <c r="M13">
-        <v>32.4276590571768</v>
+        <v>31.87557313701754</v>
       </c>
       <c r="N13">
-        <v>326.3723409428232</v>
+        <v>326.9244268629825</v>
       </c>
       <c r="O13">
-        <v>40.7965426178529</v>
+        <v>40.86555335787281</v>
       </c>
       <c r="P13">
-        <v>285.5757983249703</v>
+        <v>286.0588735051097</v>
       </c>
       <c r="Q13">
-        <v>295.6757983249703</v>
+        <v>296.1588735051097</v>
       </c>
       <c r="R13">
         <v>0.1235955056179775</v>
       </c>
       <c r="S13">
-        <v>0.1111576067973777</v>
+        <v>0.1111270841506463</v>
       </c>
       <c r="T13">
         <v>1.273346463333884</v>
       </c>
       <c r="U13">
-        <v>0.0587366166625341</v>
+        <v>0.05773661666253409</v>
       </c>
       <c r="V13">
         <v>0.125</v>
       </c>
       <c r="W13">
-        <v>0.05139453957971733</v>
+        <v>0.05051953957971733</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2391,7 +2495,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>11.06462848173406</v>
+        <v>11.25626819187513</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2402,13 +2506,13 @@
         <v>0.12</v>
       </c>
       <c r="B14">
-        <v>0.1045658907560768</v>
+        <v>0.1044337600303408</v>
       </c>
       <c r="C14">
-        <v>4475.647858115479</v>
+        <v>4483.44852410849</v>
       </c>
       <c r="D14">
-        <v>4681.623407380125</v>
+        <v>4689.424073373137</v>
       </c>
       <c r="E14">
         <v>236.7126387259271</v>
@@ -2435,37 +2539,37 @@
         <v>358.8</v>
       </c>
       <c r="M14">
-        <v>35.37562806237469</v>
+        <v>34.77335251311005</v>
       </c>
       <c r="N14">
-        <v>323.4243719376253</v>
+        <v>324.0266474868899</v>
       </c>
       <c r="O14">
-        <v>40.42804649220317</v>
+        <v>40.50333093586124</v>
       </c>
       <c r="P14">
-        <v>282.9963254454221</v>
+        <v>283.5233165510287</v>
       </c>
       <c r="Q14">
-        <v>293.0963254454222</v>
+        <v>293.6233165510287</v>
       </c>
       <c r="R14">
         <v>0.1363636363636364</v>
       </c>
       <c r="S14">
-        <v>0.111816529552853</v>
+        <v>0.1117856991826986</v>
       </c>
       <c r="T14">
         <v>1.286184096188097</v>
       </c>
       <c r="U14">
-        <v>0.0587366166625341</v>
+        <v>0.05773661666253409</v>
       </c>
       <c r="V14">
         <v>0.125</v>
       </c>
       <c r="W14">
-        <v>0.05139453957971733</v>
+        <v>0.05051953957971733</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2473,7 +2577,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>10.14257610825623</v>
+        <v>10.31824584255221</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2484,13 +2588,13 @@
         <v>0.13</v>
       </c>
       <c r="B15">
-        <v>0.1047983621087185</v>
+        <v>0.1046006408128375</v>
       </c>
       <c r="C15">
-        <v>4408.256609398753</v>
+        <v>4420.85632941165</v>
       </c>
       <c r="D15">
-        <v>4664.421787768787</v>
+        <v>4677.021507781684</v>
       </c>
       <c r="E15">
         <v>286.9022678313143</v>
@@ -2517,37 +2621,37 @@
         <v>358.8</v>
       </c>
       <c r="M15">
-        <v>39.75902045998666</v>
+        <v>38.78032269243161</v>
       </c>
       <c r="N15">
-        <v>319.0409795400134</v>
+        <v>320.0196773075684</v>
       </c>
       <c r="O15">
-        <v>39.88012244250167</v>
+        <v>40.00245966344605</v>
       </c>
       <c r="P15">
-        <v>279.1608570975117</v>
+        <v>280.0172176441223</v>
       </c>
       <c r="Q15">
-        <v>289.2608570975117</v>
+        <v>290.1172176441223</v>
       </c>
       <c r="R15">
         <v>0.1494252873563219</v>
       </c>
       <c r="S15">
-        <v>0.1124905999578796</v>
+        <v>0.1124594547902003</v>
       </c>
       <c r="T15">
         <v>1.299316847038959</v>
       </c>
       <c r="U15">
-        <v>0.0609366166625341</v>
+        <v>0.05943661666253409</v>
       </c>
       <c r="V15">
         <v>0.125</v>
       </c>
       <c r="W15">
-        <v>0.05331953957971734</v>
+        <v>0.05200703957971733</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2555,7 +2659,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>9.024367196397485</v>
+        <v>9.252114863655418</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2566,13 +2670,13 @@
         <v>0.14</v>
       </c>
       <c r="B16">
-        <v>0.1047998334613601</v>
+        <v>0.1045890215953342</v>
       </c>
       <c r="C16">
-        <v>4357.958510725405</v>
+        <v>4371.52811430664</v>
       </c>
       <c r="D16">
-        <v>4664.313318200826</v>
+        <v>4677.88292178206</v>
       </c>
       <c r="E16">
         <v>337.0918969367015</v>
@@ -2599,37 +2703,37 @@
         <v>358.8</v>
       </c>
       <c r="M16">
-        <v>42.8174066492164</v>
+        <v>41.76342443800327</v>
       </c>
       <c r="N16">
-        <v>315.9825933507836</v>
+        <v>317.0365755619968</v>
       </c>
       <c r="O16">
-        <v>39.49782416884795</v>
+        <v>39.62957194524959</v>
       </c>
       <c r="P16">
-        <v>276.4847691819356</v>
+        <v>277.4070036167471</v>
       </c>
       <c r="Q16">
-        <v>286.5847691819357</v>
+        <v>287.5070036167472</v>
       </c>
       <c r="R16">
         <v>0.1627906976744186</v>
       </c>
       <c r="S16">
-        <v>0.1131803464188369</v>
+        <v>0.1131488791327602</v>
       </c>
       <c r="T16">
         <v>1.312755010700306</v>
       </c>
       <c r="U16">
-        <v>0.0609366166625341</v>
+        <v>0.05943661666253409</v>
       </c>
       <c r="V16">
         <v>0.125</v>
       </c>
       <c r="W16">
-        <v>0.05331953957971734</v>
+        <v>0.05200703957971733</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2637,7 +2741,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>8.379769539511949</v>
+        <v>8.591249516251461</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2648,13 +2752,13 @@
         <v>0.15</v>
       </c>
       <c r="B17">
-        <v>0.1048013048140018</v>
+        <v>0.1045774023778309</v>
       </c>
       <c r="C17">
-        <v>4307.660417096784</v>
+        <v>4322.200216570605</v>
       </c>
       <c r="D17">
-        <v>4664.204853677592</v>
+        <v>4678.744653151413</v>
       </c>
       <c r="E17">
         <v>387.2815260420886</v>
@@ -2681,37 +2785,37 @@
         <v>358.8</v>
       </c>
       <c r="M17">
-        <v>45.87579283844614</v>
+        <v>44.74652618357493</v>
       </c>
       <c r="N17">
-        <v>312.9242071615539</v>
+        <v>314.0534738164251</v>
       </c>
       <c r="O17">
-        <v>39.11552589519423</v>
+        <v>39.25668422705314</v>
       </c>
       <c r="P17">
-        <v>273.8086812663596</v>
+        <v>274.7967895893719</v>
       </c>
       <c r="Q17">
-        <v>283.9086812663596</v>
+        <v>284.896789589372</v>
       </c>
       <c r="R17">
         <v>0.1764705882352941</v>
       </c>
       <c r="S17">
-        <v>0.1138863222082873</v>
+        <v>0.1138545252245569</v>
       </c>
       <c r="T17">
         <v>1.326509366447802</v>
       </c>
       <c r="U17">
-        <v>0.0609366166625341</v>
+        <v>0.05943661666253409</v>
       </c>
       <c r="V17">
         <v>0.125</v>
       </c>
       <c r="W17">
-        <v>0.05331953957971734</v>
+        <v>0.05200703957971733</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2719,7 +2823,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>7.82111823687782</v>
+        <v>8.018499548501364</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2730,13 +2834,13 @@
         <v>0.16</v>
       </c>
       <c r="B18">
-        <v>0.1050127761666436</v>
+        <v>0.1046777831603276</v>
       </c>
       <c r="C18">
-        <v>4241.933926444508</v>
+        <v>4264.576374806882</v>
       </c>
       <c r="D18">
-        <v>4648.667992130702</v>
+        <v>4671.310440493076</v>
       </c>
       <c r="E18">
         <v>437.4711551474758</v>
@@ -2763,37 +2867,37 @@
         <v>358.8</v>
       </c>
       <c r="M18">
-        <v>50.13873012620518</v>
+        <v>48.37205518169555</v>
       </c>
       <c r="N18">
-        <v>308.6612698737948</v>
+        <v>310.4279448183045</v>
       </c>
       <c r="O18">
-        <v>38.58265873422435</v>
+        <v>38.80349310228806</v>
       </c>
       <c r="P18">
-        <v>270.0786111395705</v>
+        <v>271.6244517160164</v>
       </c>
       <c r="Q18">
-        <v>280.1786111395705</v>
+        <v>281.7244517160165</v>
       </c>
       <c r="R18">
         <v>0.1904761904761905</v>
       </c>
       <c r="S18">
-        <v>0.1146091069451057</v>
+        <v>0.1145769724137772</v>
       </c>
       <c r="T18">
         <v>1.340591206855953</v>
       </c>
       <c r="U18">
-        <v>0.0624366166625341</v>
+        <v>0.0602366166625341</v>
       </c>
       <c r="V18">
         <v>0.125</v>
       </c>
       <c r="W18">
-        <v>0.05463203957971734</v>
+        <v>0.05270703957971733</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2801,7 +2905,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>7.156144543287344</v>
+        <v>7.417505802725814</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2812,13 +2916,13 @@
         <v>0.17</v>
       </c>
       <c r="B19">
-        <v>0.1050273725192853</v>
+        <v>0.1046731639428243</v>
       </c>
       <c r="C19">
-        <v>4190.675717020045</v>
+        <v>4214.728326899663</v>
       </c>
       <c r="D19">
-        <v>4647.599411811627</v>
+        <v>4671.652021691245</v>
       </c>
       <c r="E19">
         <v>487.660784252863</v>
@@ -2845,37 +2949,37 @@
         <v>358.8</v>
       </c>
       <c r="M19">
-        <v>53.272400759093</v>
+        <v>51.39530863055153</v>
       </c>
       <c r="N19">
-        <v>305.527599240907</v>
+        <v>307.4046913694485</v>
       </c>
       <c r="O19">
-        <v>38.19094990511338</v>
+        <v>38.42558642118106</v>
       </c>
       <c r="P19">
-        <v>267.3366493357937</v>
+        <v>268.9791049482674</v>
       </c>
       <c r="Q19">
-        <v>277.4366493357937</v>
+        <v>279.0791049482675</v>
       </c>
       <c r="R19">
         <v>0.2048192771084338</v>
       </c>
       <c r="S19">
-        <v>0.1153493081816064</v>
+        <v>0.1153168279690029</v>
       </c>
       <c r="T19">
         <v>1.355012368719722</v>
       </c>
       <c r="U19">
-        <v>0.0624366166625341</v>
+        <v>0.0602366166625341</v>
       </c>
       <c r="V19">
         <v>0.125</v>
       </c>
       <c r="W19">
-        <v>0.05463203957971734</v>
+        <v>0.05270703957971733</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2883,7 +2987,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>6.735194864270443</v>
+        <v>6.981181931977236</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2894,13 +2998,13 @@
         <v>0.18</v>
       </c>
       <c r="B20">
-        <v>0.105041968871927</v>
+        <v>0.104668544725321</v>
       </c>
       <c r="C20">
-        <v>4139.417998747665</v>
+        <v>4164.880328951122</v>
       </c>
       <c r="D20">
-        <v>4646.531322644633</v>
+        <v>4671.993652848091</v>
       </c>
       <c r="E20">
         <v>537.8504133582501</v>
@@ -2927,37 +3031,37 @@
         <v>358.8</v>
       </c>
       <c r="M20">
-        <v>56.40607139198082</v>
+        <v>54.41856207940749</v>
       </c>
       <c r="N20">
-        <v>302.3939286080192</v>
+        <v>304.3814379205925</v>
       </c>
       <c r="O20">
-        <v>37.7992410760024</v>
+        <v>38.04767974007407</v>
       </c>
       <c r="P20">
-        <v>264.5946875320168</v>
+        <v>266.3337581805185</v>
       </c>
       <c r="Q20">
-        <v>274.6946875320168</v>
+        <v>276.4337581805185</v>
       </c>
       <c r="R20">
         <v>0.2195121951219512</v>
       </c>
       <c r="S20">
-        <v>0.1161075631068023</v>
+        <v>0.116074728781673</v>
       </c>
       <c r="T20">
         <v>1.369785266238704</v>
       </c>
       <c r="U20">
-        <v>0.0624366166625341</v>
+        <v>0.0602366166625341</v>
       </c>
       <c r="V20">
         <v>0.125</v>
       </c>
       <c r="W20">
-        <v>0.05463203957971734</v>
+        <v>0.05270703957971733</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2965,7 +3069,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>6.361017371810973</v>
+        <v>6.593338491311835</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2976,13 +3080,13 @@
         <v>0.19</v>
       </c>
       <c r="B21">
-        <v>0.1052893152245687</v>
+        <v>0.1046639255078177</v>
       </c>
       <c r="C21">
-        <v>4071.203139210024</v>
+        <v>4115.032380972219</v>
       </c>
       <c r="D21">
-        <v>4628.50609221238</v>
+        <v>4672.335333974575</v>
       </c>
       <c r="E21">
         <v>588.0400424636375</v>
@@ -3009,45 +3113,45 @@
         <v>358.8</v>
       </c>
       <c r="M21">
-        <v>60.87478615907195</v>
+        <v>57.44181552826347</v>
       </c>
       <c r="N21">
-        <v>297.9252138409281</v>
+        <v>301.3581844717365</v>
       </c>
       <c r="O21">
-        <v>37.24065173011601</v>
+        <v>37.66977305896707</v>
       </c>
       <c r="P21">
-        <v>260.6845621108121</v>
+        <v>263.6884114127695</v>
       </c>
       <c r="Q21">
-        <v>270.7845621108121</v>
+        <v>273.7884114127695</v>
       </c>
       <c r="R21">
         <v>0.2345679012345679</v>
       </c>
       <c r="S21">
-        <v>0.1168845403758301</v>
+        <v>0.1168513431946561</v>
       </c>
       <c r="T21">
         <v>1.38492292665939</v>
       </c>
       <c r="U21">
-        <v>0.0638366166625341</v>
+        <v>0.0602366166625341</v>
       </c>
       <c r="V21">
         <v>0.125</v>
       </c>
       <c r="W21">
-        <v>0.05585703957971733</v>
+        <v>0.05270703957971733</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y21">
-        <v>5.894065879137866</v>
+        <v>6.246320675979632</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3058,13 +3162,13 @@
         <v>0.2</v>
       </c>
       <c r="B22">
-        <v>0.1053161615772104</v>
+        <v>0.1048343062903144</v>
       </c>
       <c r="C22">
-        <v>4019.065506502936</v>
+        <v>4052.272760211982</v>
       </c>
       <c r="D22">
-        <v>4626.55808861068</v>
+        <v>4659.765342319725</v>
       </c>
       <c r="E22">
         <v>638.2296715690247</v>
@@ -3091,37 +3195,37 @@
         <v>358.8</v>
       </c>
       <c r="M22">
-        <v>64.07872227270732</v>
+        <v>61.46886155922719</v>
       </c>
       <c r="N22">
-        <v>294.7212777272927</v>
+        <v>297.3311384407728</v>
       </c>
       <c r="O22">
-        <v>36.84015971591158</v>
+        <v>37.1663923050966</v>
       </c>
       <c r="P22">
-        <v>257.8811180113811</v>
+        <v>260.1647461356762</v>
       </c>
       <c r="Q22">
-        <v>267.9811180113811</v>
+        <v>270.2647461356762</v>
       </c>
       <c r="R22">
         <v>0.25</v>
       </c>
       <c r="S22">
-        <v>0.1176809420765836</v>
+        <v>0.1176473729679637</v>
       </c>
       <c r="T22">
         <v>1.400439028590593</v>
       </c>
       <c r="U22">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V22">
         <v>0.125</v>
       </c>
       <c r="W22">
-        <v>0.05585703957971733</v>
+        <v>0.05358203957971733</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3129,7 +3233,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>5.599362585180971</v>
+        <v>5.837101760121015</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3140,13 +3244,13 @@
         <v>0.21</v>
       </c>
       <c r="B23">
-        <v>0.1053430079298521</v>
+        <v>0.1048384370728111</v>
       </c>
       <c r="C23">
-        <v>3966.929512822155</v>
+        <v>4001.779218702868</v>
       </c>
       <c r="D23">
-        <v>4624.611724035285</v>
+        <v>4659.461429915998</v>
       </c>
       <c r="E23">
         <v>688.4193006744117</v>
@@ -3173,37 +3277,37 @@
         <v>358.8</v>
       </c>
       <c r="M23">
-        <v>67.28265838634267</v>
+        <v>64.54230463718854</v>
       </c>
       <c r="N23">
-        <v>291.5173416136573</v>
+        <v>294.2576953628115</v>
       </c>
       <c r="O23">
-        <v>36.43966770170717</v>
+        <v>36.78221192035144</v>
       </c>
       <c r="P23">
-        <v>255.0776739119502</v>
+        <v>257.4754834424601</v>
       </c>
       <c r="Q23">
-        <v>265.1776739119502</v>
+        <v>267.5754834424601</v>
       </c>
       <c r="R23">
         <v>0.2658227848101266</v>
       </c>
       <c r="S23">
-        <v>0.1184975058457107</v>
+        <v>0.1184635553937601</v>
       </c>
       <c r="T23">
         <v>1.416347943228915</v>
       </c>
       <c r="U23">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V23">
         <v>0.125</v>
       </c>
       <c r="W23">
-        <v>0.05585703957971733</v>
+        <v>0.05358203957971733</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3211,7 +3315,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>5.332726271600927</v>
+        <v>5.559144533448587</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3222,13 +3326,13 @@
         <v>0.22</v>
       </c>
       <c r="B24">
-        <v>0.1053698542824938</v>
+        <v>0.1048425678553078</v>
       </c>
       <c r="C24">
-        <v>3914.795156099962</v>
+        <v>3951.285716833831</v>
       </c>
       <c r="D24">
-        <v>4622.666996418479</v>
+        <v>4659.157557152348</v>
       </c>
       <c r="E24">
         <v>738.6089297797989</v>
@@ -3255,37 +3359,37 @@
         <v>358.8</v>
       </c>
       <c r="M24">
-        <v>70.48659449997804</v>
+        <v>67.61574771514989</v>
       </c>
       <c r="N24">
-        <v>288.313405500022</v>
+        <v>291.1842522848501</v>
       </c>
       <c r="O24">
-        <v>36.03917568750275</v>
+        <v>36.39803153560626</v>
       </c>
       <c r="P24">
-        <v>252.2742298125193</v>
+        <v>254.7862207492439</v>
       </c>
       <c r="Q24">
-        <v>262.3742298125193</v>
+        <v>264.8862207492439</v>
       </c>
       <c r="R24">
         <v>0.282051282051282</v>
       </c>
       <c r="S24">
-        <v>0.1193350071473794</v>
+        <v>0.1193006655740641</v>
       </c>
       <c r="T24">
         <v>1.4326647787554</v>
       </c>
       <c r="U24">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V24">
         <v>0.125</v>
       </c>
       <c r="W24">
-        <v>0.05585703957971733</v>
+        <v>0.05358203957971733</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3293,7 +3397,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>5.090329622891794</v>
+        <v>5.30645614556456</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3304,13 +3408,13 @@
         <v>0.23</v>
       </c>
       <c r="B25">
-        <v>0.1053967006351355</v>
+        <v>0.1048466986378045</v>
       </c>
       <c r="C25">
-        <v>3862.66243427212</v>
+        <v>3900.792254597114</v>
       </c>
       <c r="D25">
-        <v>4620.723903696025</v>
+        <v>4658.853724021019</v>
       </c>
       <c r="E25">
         <v>788.7985588851861</v>
@@ -3337,37 +3441,37 @@
         <v>358.8</v>
       </c>
       <c r="M25">
-        <v>73.6905306136134</v>
+        <v>70.68919079311125</v>
       </c>
       <c r="N25">
-        <v>285.1094693863866</v>
+        <v>288.1108092068887</v>
       </c>
       <c r="O25">
-        <v>35.63868367329832</v>
+        <v>36.01385115086109</v>
       </c>
       <c r="P25">
-        <v>249.4707857130883</v>
+        <v>252.0969580560277</v>
       </c>
       <c r="Q25">
-        <v>259.5707857130883</v>
+        <v>262.1969580560277</v>
       </c>
       <c r="R25">
         <v>0.2987012987012987</v>
       </c>
       <c r="S25">
-        <v>0.120194261729611</v>
+        <v>0.1201595188759345</v>
       </c>
       <c r="T25">
         <v>1.449405428191663</v>
       </c>
       <c r="U25">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V25">
         <v>0.125</v>
       </c>
       <c r="W25">
-        <v>0.05585703957971733</v>
+        <v>0.05358203957971733</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3375,7 +3479,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>4.869010943635629</v>
+        <v>5.075740660974796</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3386,13 +3490,13 @@
         <v>0.24</v>
       </c>
       <c r="B26">
-        <v>0.1054235469877772</v>
+        <v>0.1048508294203012</v>
       </c>
       <c r="C26">
-        <v>3810.531345277859</v>
+        <v>3850.298831984966</v>
       </c>
       <c r="D26">
-        <v>4618.782443807151</v>
+        <v>4658.549930514258</v>
       </c>
       <c r="E26">
         <v>838.9881879905734</v>
@@ -3419,37 +3523,37 @@
         <v>358.8</v>
       </c>
       <c r="M26">
-        <v>76.89446672724878</v>
+        <v>73.76263387107262</v>
       </c>
       <c r="N26">
-        <v>281.9055332727512</v>
+        <v>285.0373661289274</v>
       </c>
       <c r="O26">
-        <v>35.2381916590939</v>
+        <v>35.62967076611592</v>
       </c>
       <c r="P26">
-        <v>246.6673416136573</v>
+        <v>249.4076953628115</v>
       </c>
       <c r="Q26">
-        <v>256.7673416136573</v>
+        <v>259.5076953628115</v>
       </c>
       <c r="R26">
         <v>0.3157894736842105</v>
       </c>
       <c r="S26">
-        <v>0.1210761282745329</v>
+        <v>0.1210409735804856</v>
       </c>
       <c r="T26">
         <v>1.466586621034143</v>
       </c>
       <c r="U26">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V26">
         <v>0.125</v>
       </c>
       <c r="W26">
-        <v>0.05585703957971733</v>
+        <v>0.05358203957971733</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3457,7 +3561,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>4.66613548765081</v>
+        <v>4.864251466767513</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3468,13 +3572,13 @@
         <v>0.25</v>
       </c>
       <c r="B27">
-        <v>0.1060191433404189</v>
+        <v>0.1048549602027979</v>
       </c>
       <c r="C27">
-        <v>3717.685421305779</v>
+        <v>3799.805448989633</v>
       </c>
       <c r="D27">
-        <v>4576.126148940458</v>
+        <v>4658.246176624312</v>
       </c>
       <c r="E27">
         <v>889.1778170959606</v>
@@ -3501,45 +3605,45 @@
         <v>358.8</v>
       </c>
       <c r="M27">
-        <v>83.3607287327343</v>
+        <v>76.83607694903398</v>
       </c>
       <c r="N27">
-        <v>275.4392712672657</v>
+        <v>281.9639230509661</v>
       </c>
       <c r="O27">
-        <v>34.42990890840822</v>
+        <v>35.24549038137076</v>
       </c>
       <c r="P27">
-        <v>241.0093623588575</v>
+        <v>246.7184326695953</v>
       </c>
       <c r="Q27">
-        <v>251.1093623588575</v>
+        <v>256.8184326695953</v>
       </c>
       <c r="R27">
         <v>0.3333333333333333</v>
       </c>
       <c r="S27">
-        <v>0.1219815112606527</v>
+        <v>0.1219459337438248</v>
       </c>
       <c r="T27">
         <v>1.48422597901909</v>
       </c>
       <c r="U27">
-        <v>0.06643661666253409</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V27">
         <v>0.125</v>
       </c>
       <c r="W27">
-        <v>0.05813203957971733</v>
+        <v>0.05358203957971733</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y27">
-        <v>4.304185021586855</v>
+        <v>4.669681408096812</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3550,13 +3654,13 @@
         <v>0.26</v>
       </c>
       <c r="B28">
-        <v>0.1060687396930606</v>
+        <v>0.1054278409852946</v>
       </c>
       <c r="C28">
-        <v>3663.979236859331</v>
+        <v>3707.869723933817</v>
       </c>
       <c r="D28">
-        <v>4572.609593599397</v>
+        <v>4616.500080673884</v>
       </c>
       <c r="E28">
         <v>939.3674462013478</v>
@@ -3583,37 +3687,37 @@
         <v>358.8</v>
       </c>
       <c r="M28">
-        <v>86.69515788204367</v>
+        <v>83.17184591884551</v>
       </c>
       <c r="N28">
-        <v>272.1048421179563</v>
+        <v>275.6281540811545</v>
       </c>
       <c r="O28">
-        <v>34.01310526474454</v>
+        <v>34.45351926014431</v>
       </c>
       <c r="P28">
-        <v>238.0917368532118</v>
+        <v>241.1746348210102</v>
       </c>
       <c r="Q28">
-        <v>248.1917368532118</v>
+        <v>251.2746348210102</v>
       </c>
       <c r="R28">
         <v>0.3513513513513514</v>
       </c>
       <c r="S28">
-        <v>0.1229113640572082</v>
+        <v>0.1228753522899569</v>
       </c>
       <c r="T28">
         <v>1.502342076409036</v>
       </c>
       <c r="U28">
-        <v>0.06643661666253409</v>
+        <v>0.06373661666253409</v>
       </c>
       <c r="V28">
         <v>0.125</v>
       </c>
       <c r="W28">
-        <v>0.05813203957971733</v>
+        <v>0.05576953957971733</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3621,7 +3725,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>4.138639443833515</v>
+        <v>4.313959802576671</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3632,13 +3736,13 @@
         <v>0.27</v>
       </c>
       <c r="B29">
-        <v>0.1067562110457023</v>
+        <v>0.1054538467677913</v>
       </c>
       <c r="C29">
-        <v>3565.596282820292</v>
+        <v>3655.802787792491</v>
       </c>
       <c r="D29">
-        <v>4524.416268665746</v>
+        <v>4614.622773637945</v>
       </c>
       <c r="E29">
         <v>989.557075306735</v>
@@ -3665,45 +3769,45 @@
         <v>358.8</v>
       </c>
       <c r="M29">
-        <v>93.68841099313579</v>
+        <v>86.37076306957033</v>
       </c>
       <c r="N29">
-        <v>265.1115890068642</v>
+        <v>272.4292369304297</v>
       </c>
       <c r="O29">
-        <v>33.13894862585803</v>
+        <v>34.05365461630371</v>
       </c>
       <c r="P29">
-        <v>231.9726403810062</v>
+        <v>238.375582314126</v>
       </c>
       <c r="Q29">
-        <v>242.0726403810062</v>
+        <v>248.475582314126</v>
       </c>
       <c r="R29">
         <v>0.3698630136986302</v>
       </c>
       <c r="S29">
-        <v>0.1238666922728474</v>
+        <v>0.1238302343579009</v>
       </c>
       <c r="T29">
         <v>1.520954505234322</v>
       </c>
       <c r="U29">
-        <v>0.06913661666253409</v>
+        <v>0.06373661666253409</v>
       </c>
       <c r="V29">
         <v>0.125</v>
       </c>
       <c r="W29">
-        <v>0.06049453957971733</v>
+        <v>0.05576953957971733</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y29">
-        <v>3.829715929607217</v>
+        <v>4.154183513592349</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3714,13 +3818,13 @@
         <v>0.28</v>
       </c>
       <c r="B30">
-        <v>0.106829432398344</v>
+        <v>0.105479852550288</v>
       </c>
       <c r="C30">
-        <v>3510.333462637203</v>
+        <v>3603.737377850267</v>
       </c>
       <c r="D30">
-        <v>4519.343077588043</v>
+        <v>4612.746992801108</v>
       </c>
       <c r="E30">
         <v>1039.746704412122</v>
@@ -3747,45 +3851,45 @@
         <v>358.8</v>
       </c>
       <c r="M30">
-        <v>97.15835214102971</v>
+        <v>89.56968022029515</v>
       </c>
       <c r="N30">
-        <v>261.6416478589703</v>
+        <v>269.2303197797049</v>
       </c>
       <c r="O30">
-        <v>32.70520598237129</v>
+        <v>33.65378997246311</v>
       </c>
       <c r="P30">
-        <v>228.936441876599</v>
+        <v>235.5765298072418</v>
       </c>
       <c r="Q30">
-        <v>239.036441876599</v>
+        <v>245.6765298072418</v>
       </c>
       <c r="R30">
         <v>0.388888888888889</v>
       </c>
       <c r="S30">
-        <v>0.1248485573833655</v>
+        <v>0.1248116409277321</v>
       </c>
       <c r="T30">
         <v>1.540083945971422</v>
       </c>
       <c r="U30">
-        <v>0.06913661666253409</v>
+        <v>0.06373661666253409</v>
       </c>
       <c r="V30">
         <v>0.125</v>
       </c>
       <c r="W30">
-        <v>0.06049453957971733</v>
+        <v>0.05576953957971733</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y30">
-        <v>3.692940360692673</v>
+        <v>4.005819816678337</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3796,13 +3900,13 @@
         <v>0.29</v>
       </c>
       <c r="B31">
-        <v>0.1069026537509857</v>
+        <v>0.1063939833327847</v>
       </c>
       <c r="C31">
-        <v>3455.082006766997</v>
+        <v>3488.567336337824</v>
       </c>
       <c r="D31">
-        <v>4514.281250823225</v>
+        <v>4547.766580394052</v>
       </c>
       <c r="E31">
         <v>1089.936333517509</v>
@@ -3829,37 +3933,37 @@
         <v>358.8</v>
       </c>
       <c r="M31">
-        <v>100.6282932889236</v>
+        <v>97.86284472521677</v>
       </c>
       <c r="N31">
-        <v>258.1717067110764</v>
+        <v>260.9371552747832</v>
       </c>
       <c r="O31">
-        <v>32.27146333888455</v>
+        <v>32.6171444093479</v>
       </c>
       <c r="P31">
-        <v>225.9002433721919</v>
+        <v>228.3200108654353</v>
       </c>
       <c r="Q31">
-        <v>236.0002433721918</v>
+        <v>238.4200108654353</v>
       </c>
       <c r="R31">
         <v>0.4084507042253521</v>
       </c>
       <c r="S31">
-        <v>0.1258580806660108</v>
+        <v>0.1258206927530516</v>
       </c>
       <c r="T31">
         <v>1.559752244194073</v>
       </c>
       <c r="U31">
-        <v>0.06913661666253409</v>
+        <v>0.0672366166625341</v>
       </c>
       <c r="V31">
         <v>0.125</v>
       </c>
       <c r="W31">
-        <v>0.06049453957971733</v>
+        <v>0.05883203957971733</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3867,7 +3971,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>3.565597589634306</v>
+        <v>3.66635571454573</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3878,13 +3982,13 @@
         <v>0.3</v>
       </c>
       <c r="B32">
-        <v>0.1082096251036274</v>
+        <v>0.1064506141152814</v>
       </c>
       <c r="C32">
-        <v>3316.410963337217</v>
+        <v>3434.412312928666</v>
       </c>
       <c r="D32">
-        <v>4425.799836498833</v>
+        <v>4543.801186090282</v>
       </c>
       <c r="E32">
         <v>1140.125962622896</v>
@@ -3911,45 +4015,45 @@
         <v>358.8</v>
       </c>
       <c r="M32">
-        <v>111.1749721406771</v>
+        <v>101.2374255778105</v>
       </c>
       <c r="N32">
-        <v>247.6250278593229</v>
+        <v>257.5625744221895</v>
       </c>
       <c r="O32">
-        <v>30.95312848241536</v>
+        <v>32.19532180277369</v>
       </c>
       <c r="P32">
-        <v>216.6718993769075</v>
+        <v>225.3672526194158</v>
       </c>
       <c r="Q32">
-        <v>226.7718993769075</v>
+        <v>235.4672526194158</v>
       </c>
       <c r="R32">
         <v>0.4285714285714286</v>
       </c>
       <c r="S32">
-        <v>0.1268964474710174</v>
+        <v>0.1268585746305231</v>
       </c>
       <c r="T32">
         <v>1.579982493794515</v>
       </c>
       <c r="U32">
-        <v>0.0738366166625341</v>
+        <v>0.0672366166625341</v>
       </c>
       <c r="V32">
         <v>0.125</v>
       </c>
       <c r="W32">
-        <v>0.06460703957971733</v>
+        <v>0.05883203957971733</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y32">
-        <v>3.227345085780515</v>
+        <v>3.544143857394206</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3960,13 +4064,13 @@
         <v>0.31</v>
       </c>
       <c r="B33">
-        <v>0.1083239714562691</v>
+        <v>0.1072667448977781</v>
       </c>
       <c r="C33">
-        <v>3258.644856380161</v>
+        <v>3327.834071233158</v>
       </c>
       <c r="D33">
-        <v>4418.223358647164</v>
+        <v>4487.412573500161</v>
       </c>
       <c r="E33">
         <v>1190.315591728284</v>
@@ -3993,37 +4097,37 @@
         <v>358.8</v>
       </c>
       <c r="M33">
-        <v>114.8808045453664</v>
+        <v>108.9684662367518</v>
       </c>
       <c r="N33">
-        <v>243.9191954546336</v>
+        <v>249.8315337632483</v>
       </c>
       <c r="O33">
-        <v>30.4898994318292</v>
+        <v>31.22894172040603</v>
       </c>
       <c r="P33">
-        <v>213.4292960228044</v>
+        <v>218.6025920428422</v>
       </c>
       <c r="Q33">
-        <v>223.5292960228044</v>
+        <v>228.7025920428422</v>
       </c>
       <c r="R33">
         <v>0.4492753623188406</v>
       </c>
       <c r="S33">
-        <v>0.127964911864575</v>
+        <v>0.127926540040675</v>
       </c>
       <c r="T33">
         <v>1.600799127441347</v>
       </c>
       <c r="U33">
-        <v>0.0738366166625341</v>
+        <v>0.07003661666253409</v>
       </c>
       <c r="V33">
         <v>0.125</v>
       </c>
       <c r="W33">
-        <v>0.06460703957971733</v>
+        <v>0.06128203957971733</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4031,7 +4135,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>3.123237179787595</v>
+        <v>3.292695698042116</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4042,13 +4146,13 @@
         <v>0.32</v>
       </c>
       <c r="B34">
-        <v>0.1084383178089108</v>
+        <v>0.1073478756802748</v>
       </c>
       <c r="C34">
-        <v>3200.904645269775</v>
+        <v>3272.115289856565</v>
       </c>
       <c r="D34">
-        <v>4410.672776642165</v>
+        <v>4481.883421228955</v>
       </c>
       <c r="E34">
         <v>1240.505220833671</v>
@@ -4075,37 +4179,37 @@
         <v>358.8</v>
       </c>
       <c r="M34">
-        <v>118.5866369500556</v>
+        <v>112.4835780508405</v>
       </c>
       <c r="N34">
-        <v>240.2133630499444</v>
+        <v>246.3164219491595</v>
       </c>
       <c r="O34">
-        <v>30.02667038124305</v>
+        <v>30.78955274364494</v>
       </c>
       <c r="P34">
-        <v>210.1866926687014</v>
+        <v>215.5268692055145</v>
       </c>
       <c r="Q34">
-        <v>220.2866926687014</v>
+        <v>225.6268692055145</v>
       </c>
       <c r="R34">
         <v>0.4705882352941177</v>
       </c>
       <c r="S34">
-        <v>0.1290648016814724</v>
+        <v>0.1290259161981842</v>
       </c>
       <c r="T34">
         <v>1.622228015018968</v>
       </c>
       <c r="U34">
-        <v>0.0738366166625341</v>
+        <v>0.07003661666253409</v>
       </c>
       <c r="V34">
         <v>0.125</v>
       </c>
       <c r="W34">
-        <v>0.06460703957971733</v>
+        <v>0.06128203957971733</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4113,7 +4217,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>3.025636017919233</v>
+        <v>3.189798957478299</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4124,13 +4228,13 @@
         <v>0.33</v>
       </c>
       <c r="B35">
-        <v>0.1112380391615525</v>
+        <v>0.1074290064627715</v>
       </c>
       <c r="C35">
-        <v>2973.570497930229</v>
+        <v>3216.410117169646</v>
       </c>
       <c r="D35">
-        <v>4233.528258408006</v>
+        <v>4476.367877647423</v>
       </c>
       <c r="E35">
         <v>1290.694849939058</v>
@@ -4157,45 +4261,45 @@
         <v>358.8</v>
       </c>
       <c r="M35">
-        <v>137.6956665271882</v>
+        <v>115.9986898649293</v>
       </c>
       <c r="N35">
-        <v>221.1043334728118</v>
+        <v>242.8013101350707</v>
       </c>
       <c r="O35">
-        <v>27.63804168410148</v>
+        <v>30.35016376688384</v>
       </c>
       <c r="P35">
-        <v>193.4662917887104</v>
+        <v>212.4511463681869</v>
       </c>
       <c r="Q35">
-        <v>203.5662917887103</v>
+        <v>222.5511463681869</v>
       </c>
       <c r="R35">
         <v>0.4925373134328359</v>
       </c>
       <c r="S35">
-        <v>0.1301975240302176</v>
+        <v>0.130158109554425</v>
       </c>
       <c r="T35">
         <v>1.644296570882488</v>
       </c>
       <c r="U35">
-        <v>0.08313661666253409</v>
+        <v>0.07003661666253409</v>
       </c>
       <c r="V35">
         <v>0.125</v>
       </c>
       <c r="W35">
-        <v>0.07274453957971733</v>
+        <v>0.06128203957971733</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y35">
-        <v>2.605746491877829</v>
+        <v>3.09313838300926</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4206,13 +4310,13 @@
         <v>0.34</v>
       </c>
       <c r="B36">
-        <v>0.1114337605141942</v>
+        <v>0.1075101372452682</v>
       </c>
       <c r="C36">
-        <v>2911.527792175593</v>
+        <v>3160.718502992339</v>
       </c>
       <c r="D36">
-        <v>4221.675181758757</v>
+        <v>4470.865892575503</v>
       </c>
       <c r="E36">
         <v>1340.884479044445</v>
@@ -4239,45 +4343,45 @@
         <v>358.8</v>
       </c>
       <c r="M36">
-        <v>141.8682624825575</v>
+        <v>119.513801679018</v>
       </c>
       <c r="N36">
-        <v>216.9317375174425</v>
+        <v>239.286198320982</v>
       </c>
       <c r="O36">
-        <v>27.11646718968031</v>
+        <v>29.91077479012274</v>
       </c>
       <c r="P36">
-        <v>189.8152703277622</v>
+        <v>209.3754235308592</v>
       </c>
       <c r="Q36">
-        <v>199.9152703277622</v>
+        <v>219.4754235308592</v>
       </c>
       <c r="R36">
         <v>0.5151515151515152</v>
       </c>
       <c r="S36">
-        <v>0.1313645712986217</v>
+        <v>0.131324611800249</v>
       </c>
       <c r="T36">
         <v>1.667033870863084</v>
       </c>
       <c r="U36">
-        <v>0.08313661666253409</v>
+        <v>0.07003661666253409</v>
       </c>
       <c r="V36">
         <v>0.125</v>
       </c>
       <c r="W36">
-        <v>0.07274453957971733</v>
+        <v>0.06128203957971733</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y36">
-        <v>2.52910688917554</v>
+        <v>3.002163724685458</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4288,13 +4392,13 @@
         <v>0.35</v>
       </c>
       <c r="B37">
-        <v>0.1130688568668359</v>
+        <v>0.1099800180277649</v>
       </c>
       <c r="C37">
-        <v>2764.849267291212</v>
+        <v>2949.270712049904</v>
       </c>
       <c r="D37">
-        <v>4125.186285979763</v>
+        <v>4309.607730738456</v>
       </c>
       <c r="E37">
         <v>1391.074108149833</v>
@@ -4321,45 +4425,45 @@
         <v>358.8</v>
       </c>
       <c r="M37">
-        <v>154.297052425763</v>
+        <v>136.7306822388776</v>
       </c>
       <c r="N37">
-        <v>204.502947574237</v>
+        <v>222.0693177611224</v>
       </c>
       <c r="O37">
-        <v>25.56286844677962</v>
+        <v>27.75866472014031</v>
       </c>
       <c r="P37">
-        <v>178.9400791274574</v>
+        <v>194.3106530409821</v>
       </c>
       <c r="Q37">
-        <v>189.0400791274573</v>
+        <v>204.4106530409821</v>
       </c>
       <c r="R37">
         <v>0.5384615384615385</v>
       </c>
       <c r="S37">
-        <v>0.1325675277137459</v>
+        <v>0.1325270064228674</v>
       </c>
       <c r="T37">
         <v>1.690470780073852</v>
       </c>
       <c r="U37">
-        <v>0.08783661666253409</v>
+        <v>0.07783661666253411</v>
       </c>
       <c r="V37">
         <v>0.125</v>
       </c>
       <c r="W37">
-        <v>0.07685703957971733</v>
+        <v>0.06810703957971734</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y37">
-        <v>2.32538466781554</v>
+        <v>2.624136690645283</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4370,13 +4474,13 @@
         <v>0.36</v>
       </c>
       <c r="B38">
-        <v>0.1133057032194776</v>
+        <v>0.1101293988102616</v>
       </c>
       <c r="C38">
-        <v>2701.047573420367</v>
+        <v>2889.700276502635</v>
       </c>
       <c r="D38">
-        <v>4111.574221214306</v>
+        <v>4300.226924296574</v>
       </c>
       <c r="E38">
         <v>1441.263737255219</v>
@@ -4403,45 +4507,45 @@
         <v>358.8</v>
       </c>
       <c r="M38">
-        <v>158.7055396379277</v>
+        <v>140.6372731599883</v>
       </c>
       <c r="N38">
-        <v>200.0944603620723</v>
+        <v>218.1627268400117</v>
       </c>
       <c r="O38">
-        <v>25.01180754525904</v>
+        <v>27.27034085500146</v>
       </c>
       <c r="P38">
-        <v>175.0826528168133</v>
+        <v>190.8923859850102</v>
       </c>
       <c r="Q38">
-        <v>185.1826528168133</v>
+        <v>200.9923859850102</v>
       </c>
       <c r="R38">
         <v>0.5625</v>
       </c>
       <c r="S38">
-        <v>0.1338080765168428</v>
+        <v>0.1337669758774427</v>
       </c>
       <c r="T38">
         <v>1.714640092697457</v>
       </c>
       <c r="U38">
-        <v>0.08783661666253409</v>
+        <v>0.07783661666253411</v>
       </c>
       <c r="V38">
         <v>0.125</v>
       </c>
       <c r="W38">
-        <v>0.07685703957971733</v>
+        <v>0.06810703957971734</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y38">
-        <v>2.260790649265109</v>
+        <v>2.551244004794026</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4452,13 +4556,13 @@
         <v>0.37</v>
       </c>
       <c r="B39">
-        <v>0.1135425495721193</v>
+        <v>0.1115414045927583</v>
       </c>
       <c r="C39">
-        <v>2637.335416797525</v>
+        <v>2752.816348321432</v>
       </c>
       <c r="D39">
-        <v>4098.051693696851</v>
+        <v>4213.532625220758</v>
       </c>
       <c r="E39">
         <v>1491.453366360607</v>
@@ -4485,37 +4589,37 @@
         <v>358.8</v>
       </c>
       <c r="M39">
-        <v>163.1140268500923</v>
+        <v>151.7862275610065</v>
       </c>
       <c r="N39">
-        <v>195.6859731499077</v>
+        <v>207.0137724389936</v>
       </c>
       <c r="O39">
-        <v>24.46074664373846</v>
+        <v>25.87672155487419</v>
       </c>
       <c r="P39">
-        <v>171.2252265061692</v>
+        <v>181.1370508841194</v>
       </c>
       <c r="Q39">
-        <v>181.3252265061692</v>
+        <v>191.2370508841194</v>
       </c>
       <c r="R39">
         <v>0.5873015873015873</v>
       </c>
       <c r="S39">
-        <v>0.1350880078216253</v>
+        <v>0.1350463094416871</v>
       </c>
       <c r="T39">
         <v>1.739576685086891</v>
       </c>
       <c r="U39">
-        <v>0.08783661666253409</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V39">
         <v>0.125</v>
       </c>
       <c r="W39">
-        <v>0.07685703957971733</v>
+        <v>0.07151953957971734</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4523,7 +4627,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>2.199688199284971</v>
+        <v>2.363850829982515</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4534,13 +4638,13 @@
         <v>0.38</v>
       </c>
       <c r="B40">
-        <v>0.113779395924761</v>
+        <v>0.111724910375255</v>
       </c>
       <c r="C40">
-        <v>2573.711916883408</v>
+        <v>2691.61582950427</v>
       </c>
       <c r="D40">
-        <v>4084.617822888121</v>
+        <v>4202.521735508983</v>
       </c>
       <c r="E40">
         <v>1541.642995465994</v>
@@ -4567,37 +4671,37 @@
         <v>358.8</v>
       </c>
       <c r="M40">
-        <v>167.522514062257</v>
+        <v>155.8885580356283</v>
       </c>
       <c r="N40">
-        <v>191.277485937743</v>
+        <v>202.9114419643717</v>
       </c>
       <c r="O40">
-        <v>23.90968574221787</v>
+        <v>25.36393024554647</v>
       </c>
       <c r="P40">
-        <v>167.3678001955251</v>
+        <v>177.5475117188253</v>
       </c>
       <c r="Q40">
-        <v>177.4678001955251</v>
+        <v>187.6475117188253</v>
       </c>
       <c r="R40">
         <v>0.6129032258064516</v>
       </c>
       <c r="S40">
-        <v>0.1364092272330136</v>
+        <v>0.1363669118305845</v>
       </c>
       <c r="T40">
         <v>1.765317683682435</v>
       </c>
       <c r="U40">
-        <v>0.08783661666253409</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V40">
         <v>0.125</v>
       </c>
       <c r="W40">
-        <v>0.07685703957971733</v>
+        <v>0.07151953957971734</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4605,7 +4709,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>2.14180166772484</v>
+        <v>2.301644229193501</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4616,13 +4720,13 @@
         <v>0.39</v>
       </c>
       <c r="B41">
-        <v>0.1140162422774027</v>
+        <v>0.1119084161577517</v>
       </c>
       <c r="C41">
-        <v>2510.176204647043</v>
+        <v>2630.472708458874</v>
       </c>
       <c r="D41">
-        <v>4071.271739757144</v>
+        <v>4191.568243568974</v>
       </c>
       <c r="E41">
         <v>1591.832624571381</v>
@@ -4649,37 +4753,37 @@
         <v>358.8</v>
       </c>
       <c r="M41">
-        <v>171.9310012744217</v>
+        <v>159.9908885102501</v>
       </c>
       <c r="N41">
-        <v>186.8689987255783</v>
+        <v>198.8091114897499</v>
       </c>
       <c r="O41">
-        <v>23.35862484069729</v>
+        <v>24.85113893621874</v>
       </c>
       <c r="P41">
-        <v>163.510373884881</v>
+        <v>173.9579725535312</v>
       </c>
       <c r="Q41">
-        <v>173.610373884881</v>
+        <v>184.0579725535312</v>
       </c>
       <c r="R41">
         <v>0.639344262295082</v>
       </c>
       <c r="S41">
-        <v>0.1377737653136278</v>
+        <v>0.1377308126584622</v>
       </c>
       <c r="T41">
         <v>1.791902649445047</v>
       </c>
       <c r="U41">
-        <v>0.08783661666253409</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V41">
         <v>0.125</v>
       </c>
       <c r="W41">
-        <v>0.07685703957971733</v>
+        <v>0.07151953957971734</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4687,7 +4791,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>2.086883676244716</v>
+        <v>2.242627710496232</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4698,13 +4802,13 @@
         <v>0.4</v>
       </c>
       <c r="B42">
-        <v>0.1142530886300444</v>
+        <v>0.1120919219402484</v>
       </c>
       <c r="C42">
-        <v>2446.72742237835</v>
+        <v>2569.38653754571</v>
       </c>
       <c r="D42">
-        <v>4058.012586593838</v>
+        <v>4180.671701761197</v>
       </c>
       <c r="E42">
         <v>1642.022253676769</v>
@@ -4731,37 +4835,37 @@
         <v>358.8</v>
       </c>
       <c r="M42">
-        <v>176.3394884865863</v>
+        <v>164.0932189848719</v>
       </c>
       <c r="N42">
-        <v>182.4605115134137</v>
+        <v>194.7067810151281</v>
       </c>
       <c r="O42">
-        <v>22.80756393917671</v>
+        <v>24.33834762689102</v>
       </c>
       <c r="P42">
-        <v>159.652947574237</v>
+        <v>170.3684333882371</v>
       </c>
       <c r="Q42">
-        <v>169.752947574237</v>
+        <v>180.4684333882371</v>
       </c>
       <c r="R42">
         <v>0.6666666666666667</v>
       </c>
       <c r="S42">
-        <v>0.1391837879969292</v>
+        <v>0.1391401768472691</v>
       </c>
       <c r="T42">
         <v>1.819373780733079</v>
       </c>
       <c r="U42">
-        <v>0.08783661666253409</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V42">
         <v>0.125</v>
       </c>
       <c r="W42">
-        <v>0.07685703957971733</v>
+        <v>0.07151953957971734</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4769,7 +4873,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>2.034711584338598</v>
+        <v>2.186562017733826</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4780,13 +4884,13 @@
         <v>0.41</v>
       </c>
       <c r="B43">
-        <v>0.1203375599826861</v>
+        <v>0.1122754277227451</v>
       </c>
       <c r="C43">
-        <v>2083.237831965861</v>
+        <v>2508.35687376797</v>
       </c>
       <c r="D43">
-        <v>3744.712625286736</v>
+        <v>4169.831667088844</v>
       </c>
       <c r="E43">
         <v>1692.211882782156</v>
@@ -4813,45 +4917,45 @@
         <v>358.8</v>
       </c>
       <c r="M43">
-        <v>214.2897048298813</v>
+        <v>168.1955494594937</v>
       </c>
       <c r="N43">
-        <v>144.5102951701188</v>
+        <v>190.6044505405063</v>
       </c>
       <c r="O43">
-        <v>18.06378689626484</v>
+        <v>23.82555631756329</v>
       </c>
       <c r="P43">
-        <v>126.4465082738539</v>
+        <v>166.7788942229431</v>
       </c>
       <c r="Q43">
-        <v>136.5465082738539</v>
+        <v>176.878894222943</v>
       </c>
       <c r="R43">
         <v>0.6949152542372882</v>
       </c>
       <c r="S43">
-        <v>0.1406416080593255</v>
+        <v>0.1405973160933237</v>
       </c>
       <c r="T43">
         <v>1.847776136810535</v>
       </c>
       <c r="U43">
-        <v>0.1041366166625341</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V43">
         <v>0.125</v>
       </c>
       <c r="W43">
-        <v>0.09111953957971733</v>
+        <v>0.07151953957971734</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y43">
-        <v>1.674368819000621</v>
+        <v>2.133231236813489</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4862,13 +4966,13 @@
         <v>0.42</v>
       </c>
       <c r="B44">
-        <v>0.1207170313353278</v>
+        <v>0.1124589335052418</v>
       </c>
       <c r="C44">
-        <v>2015.103533986573</v>
+        <v>2447.383278711534</v>
       </c>
       <c r="D44">
-        <v>3726.767956412834</v>
+        <v>4159.047701137795</v>
       </c>
       <c r="E44">
         <v>1742.401511887542</v>
@@ -4895,45 +4999,45 @@
         <v>358.8</v>
       </c>
       <c r="M44">
-        <v>219.5162829964637</v>
+        <v>172.2978799341154</v>
       </c>
       <c r="N44">
-        <v>139.2837170035363</v>
+        <v>186.5021200658846</v>
       </c>
       <c r="O44">
-        <v>17.41046462544204</v>
+        <v>23.31276500823557</v>
       </c>
       <c r="P44">
-        <v>121.8732523780943</v>
+        <v>163.189355057649</v>
       </c>
       <c r="Q44">
-        <v>131.9732523780943</v>
+        <v>173.289355057649</v>
       </c>
       <c r="R44">
         <v>0.7241379310344827</v>
       </c>
       <c r="S44">
-        <v>0.1421496977790458</v>
+        <v>0.1421047015202767</v>
       </c>
       <c r="T44">
         <v>1.877157884476869</v>
       </c>
       <c r="U44">
-        <v>0.1041366166625341</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V44">
         <v>0.125</v>
       </c>
       <c r="W44">
-        <v>0.09111953957971733</v>
+        <v>0.07151953957971734</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y44">
-        <v>1.634502894738702</v>
+        <v>2.082440016889358</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4944,13 +5048,13 @@
         <v>0.43</v>
       </c>
       <c r="B45">
-        <v>0.1210965026879695</v>
+        <v>0.1126424392877385</v>
       </c>
       <c r="C45">
-        <v>1947.140397564565</v>
+        <v>2386.46531848587</v>
       </c>
       <c r="D45">
-        <v>3708.994449096213</v>
+        <v>4148.319370017519</v>
       </c>
       <c r="E45">
         <v>1792.59114099293</v>
@@ -4977,45 +5081,45 @@
         <v>358.8</v>
       </c>
       <c r="M45">
-        <v>224.7428611630462</v>
+        <v>176.4002104087372</v>
       </c>
       <c r="N45">
-        <v>134.0571388369538</v>
+        <v>182.3997895912628</v>
       </c>
       <c r="O45">
-        <v>16.75714235461923</v>
+        <v>22.79997369890785</v>
       </c>
       <c r="P45">
-        <v>117.2999964823346</v>
+        <v>159.5998158923549</v>
       </c>
       <c r="Q45">
-        <v>127.3999964823346</v>
+        <v>169.6998158923549</v>
       </c>
       <c r="R45">
         <v>0.7543859649122806</v>
       </c>
       <c r="S45">
-        <v>0.1437107029275282</v>
+        <v>0.1436649776639649</v>
       </c>
       <c r="T45">
         <v>1.907570570657812</v>
       </c>
       <c r="U45">
-        <v>0.1041366166625341</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V45">
         <v>0.125</v>
       </c>
       <c r="W45">
-        <v>0.09111953957971733</v>
+        <v>0.07151953957971734</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y45">
-        <v>1.59649119951222</v>
+        <v>2.034011179287281</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5026,13 +5130,13 @@
         <v>0.44</v>
       </c>
       <c r="B46">
-        <v>0.1214759740406113</v>
+        <v>0.1182929450702352</v>
       </c>
       <c r="C46">
-        <v>1879.345985439187</v>
+        <v>2031.02673857025</v>
       </c>
       <c r="D46">
-        <v>3691.389666076223</v>
+        <v>3843.070419207286</v>
       </c>
       <c r="E46">
         <v>1842.780770098317</v>
@@ -5059,37 +5163,37 @@
         <v>358.8</v>
       </c>
       <c r="M46">
-        <v>229.9694393296286</v>
+        <v>211.8610211484049</v>
       </c>
       <c r="N46">
-        <v>128.8305606703714</v>
+        <v>146.9389788515951</v>
       </c>
       <c r="O46">
-        <v>16.10382008379642</v>
+        <v>18.36737235644938</v>
       </c>
       <c r="P46">
-        <v>112.7267405865749</v>
+        <v>128.5716064951457</v>
       </c>
       <c r="Q46">
-        <v>122.8267405865749</v>
+        <v>138.6716064951457</v>
       </c>
       <c r="R46">
         <v>0.7857142857142857</v>
       </c>
       <c r="S46">
-        <v>0.145327458259885</v>
+        <v>0.145280977955642</v>
       </c>
       <c r="T46">
         <v>1.93906942420236</v>
       </c>
       <c r="U46">
-        <v>0.1041366166625341</v>
+        <v>0.0959366166625341</v>
       </c>
       <c r="V46">
         <v>0.125</v>
       </c>
       <c r="W46">
-        <v>0.09111953957971733</v>
+        <v>0.08394453957971734</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5097,7 +5201,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>1.560207308614215</v>
+        <v>1.693563063441797</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5108,13 +5212,13 @@
         <v>0.45</v>
       </c>
       <c r="B47">
-        <v>0.1218554453932529</v>
+        <v>0.1186007008527319</v>
       </c>
       <c r="C47">
-        <v>1811.717906405123</v>
+        <v>1965.496515693221</v>
       </c>
       <c r="D47">
-        <v>3673.951216147546</v>
+        <v>3827.729825435644</v>
       </c>
       <c r="E47">
         <v>1892.970399203704</v>
@@ -5141,37 +5245,37 @@
         <v>358.8</v>
       </c>
       <c r="M47">
-        <v>235.1960174962111</v>
+        <v>216.6760443563232</v>
       </c>
       <c r="N47">
-        <v>123.6039825037889</v>
+        <v>142.1239556436768</v>
       </c>
       <c r="O47">
-        <v>15.45049781297361</v>
+        <v>17.7654944554596</v>
       </c>
       <c r="P47">
-        <v>108.1534846908153</v>
+        <v>124.3584611882172</v>
       </c>
       <c r="Q47">
-        <v>118.2534846908153</v>
+        <v>134.4584611882172</v>
       </c>
       <c r="R47">
         <v>0.8181818181818181</v>
       </c>
       <c r="S47">
-        <v>0.1470030046952366</v>
+        <v>0.1469557418942892</v>
       </c>
       <c r="T47">
         <v>1.971713690603073</v>
       </c>
       <c r="U47">
-        <v>0.1041366166625341</v>
+        <v>0.0959366166625341</v>
       </c>
       <c r="V47">
         <v>0.125</v>
       </c>
       <c r="W47">
-        <v>0.09111953957971733</v>
+        <v>0.08394453957971734</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5179,7 +5283,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>1.525536035089455</v>
+        <v>1.655928328698646</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5190,13 +5294,13 @@
         <v>0.46</v>
       </c>
       <c r="B48">
-        <v>0.1496532314107427</v>
+        <v>0.1189084566352286</v>
       </c>
       <c r="C48">
-        <v>816.9918058023213</v>
+        <v>1900.088277652163</v>
       </c>
       <c r="D48">
-        <v>2729.414744650132</v>
+        <v>3812.511216499974</v>
       </c>
       <c r="E48">
         <v>1943.160028309091</v>
@@ -5223,45 +5327,45 @@
         <v>358.8</v>
       </c>
       <c r="M48">
-        <v>391.4130758634404</v>
+        <v>221.4910675642415</v>
       </c>
       <c r="N48">
-        <v>-32.61307586344043</v>
+        <v>137.3089324357585</v>
       </c>
       <c r="O48">
-        <v>-4.076634482930054</v>
+        <v>17.16361655446981</v>
       </c>
       <c r="P48">
-        <v>-28.53644138051038</v>
+        <v>120.1453158812887</v>
       </c>
       <c r="Q48">
-        <v>-18.43644138051037</v>
+        <v>130.2453158812887</v>
       </c>
       <c r="R48">
         <v>0.8518518518518519</v>
       </c>
       <c r="S48">
-        <v>0.1492638829973987</v>
+        <v>0.1486925341269603</v>
       </c>
       <c r="T48">
-        <v>2.015761836353139</v>
+        <v>2.005567003907516</v>
       </c>
       <c r="U48">
-        <v>0.1695366166625341</v>
+        <v>0.0959366166625341</v>
       </c>
       <c r="V48">
-        <v>0.1145848280644759</v>
+        <v>0.125</v>
       </c>
       <c r="W48">
-        <v>0.1501102925916247</v>
+        <v>0.08394453957971734</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y48">
-        <v>0.9166786245158075</v>
+        <v>1.619929886770414</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5272,13 +5376,13 @@
         <v>0.47</v>
       </c>
       <c r="B49">
-        <v>0.150890597577368</v>
+        <v>0.1192162124177253</v>
       </c>
       <c r="C49">
-        <v>735.9204825315442</v>
+        <v>1834.800575216459</v>
       </c>
       <c r="D49">
-        <v>2698.533050484742</v>
+        <v>3797.413143169656</v>
       </c>
       <c r="E49">
         <v>1993.349657414479</v>
@@ -5305,45 +5409,45 @@
         <v>358.8</v>
       </c>
       <c r="M49">
-        <v>399.9220557735152</v>
+        <v>226.3060907721598</v>
       </c>
       <c r="N49">
-        <v>-41.12205577351517</v>
+        <v>132.4939092278402</v>
       </c>
       <c r="O49">
-        <v>-5.140256971689396</v>
+        <v>16.56173865348002</v>
       </c>
       <c r="P49">
-        <v>-35.98179880182578</v>
+        <v>115.9321705743601</v>
       </c>
       <c r="Q49">
-        <v>-25.88179880182577</v>
+        <v>126.0321705743601</v>
       </c>
       <c r="R49">
         <v>0.8867924528301887</v>
       </c>
       <c r="S49">
-        <v>0.1512160317331986</v>
+        <v>0.1504948656891663</v>
       </c>
       <c r="T49">
-        <v>2.053795078548481</v>
+        <v>2.040697800732882</v>
       </c>
       <c r="U49">
-        <v>0.1695366166625341</v>
+        <v>0.0959366166625341</v>
       </c>
       <c r="V49">
-        <v>0.1121468529992743</v>
+        <v>0.125</v>
       </c>
       <c r="W49">
-        <v>0.1505236186356866</v>
+        <v>0.08394453957971734</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y49">
-        <v>0.8971748239941947</v>
+        <v>1.585463293434874</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5354,13 +5458,13 @@
         <v>0.48</v>
       </c>
       <c r="B50">
-        <v>0.1521279637439933</v>
+        <v>0.119523968200222</v>
       </c>
       <c r="C50">
-        <v>655.5401568080706</v>
+        <v>1769.631982021551</v>
       </c>
       <c r="D50">
-        <v>2668.342353866655</v>
+        <v>3782.434179080135</v>
       </c>
       <c r="E50">
         <v>2043.539286519866</v>
@@ -5387,45 +5491,45 @@
         <v>358.8</v>
       </c>
       <c r="M50">
-        <v>408.43103568359</v>
+        <v>231.1211139800781</v>
       </c>
       <c r="N50">
-        <v>-49.63103568358997</v>
+        <v>127.6788860199219</v>
       </c>
       <c r="O50">
-        <v>-6.203879460448746</v>
+        <v>15.95986075249024</v>
       </c>
       <c r="P50">
-        <v>-43.42715622314122</v>
+        <v>111.7190252674316</v>
       </c>
       <c r="Q50">
-        <v>-33.32715622314122</v>
+        <v>121.8190252674316</v>
       </c>
       <c r="R50">
         <v>0.923076923076923</v>
       </c>
       <c r="S50">
-        <v>0.1532432631126832</v>
+        <v>0.1523665176960724</v>
       </c>
       <c r="T50">
-        <v>2.093291137751336</v>
+        <v>2.077179782051531</v>
       </c>
       <c r="U50">
-        <v>0.1695366166625341</v>
+        <v>0.0959366166625341</v>
       </c>
       <c r="V50">
-        <v>0.1098104602284561</v>
+        <v>0.125</v>
       </c>
       <c r="W50">
-        <v>0.1509197227612459</v>
+        <v>0.08394453957971734</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y50">
-        <v>0.878483681827649</v>
+        <v>1.552432808154981</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5436,13 +5540,13 @@
         <v>0.49</v>
       </c>
       <c r="B51">
-        <v>0.1533653299106186</v>
+        <v>0.1198317239827187</v>
       </c>
       <c r="C51">
-        <v>575.8278929675575</v>
+        <v>1704.58109411974</v>
       </c>
       <c r="D51">
-        <v>2638.819719131529</v>
+        <v>3767.572920283712</v>
       </c>
       <c r="E51">
         <v>2093.728915625253</v>
@@ -5469,45 +5573,45 @@
         <v>358.8</v>
       </c>
       <c r="M51">
-        <v>416.9400155936648</v>
+        <v>235.9361371879964</v>
       </c>
       <c r="N51">
-        <v>-58.14001559366477</v>
+        <v>122.8638628120036</v>
       </c>
       <c r="O51">
-        <v>-7.267501949208096</v>
+        <v>15.35798285150045</v>
       </c>
       <c r="P51">
-        <v>-50.87251364445667</v>
+        <v>107.5058799605031</v>
       </c>
       <c r="Q51">
-        <v>-40.77251364445667</v>
+        <v>117.6058799605031</v>
       </c>
       <c r="R51">
         <v>0.9607843137254901</v>
       </c>
       <c r="S51">
-        <v>0.1553499937619515</v>
+        <v>0.1543115678208964</v>
       </c>
       <c r="T51">
-        <v>2.13433606202097</v>
+        <v>2.115092429304244</v>
       </c>
       <c r="U51">
-        <v>0.1695366166625341</v>
+        <v>0.0959366166625341</v>
       </c>
       <c r="V51">
-        <v>0.1075694304278754</v>
+        <v>0.125</v>
       </c>
       <c r="W51">
-        <v>0.1512996593714763</v>
+        <v>0.08394453957971734</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y51">
-        <v>0.8605554434230031</v>
+        <v>1.520750505947736</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5518,13 +5622,13 @@
         <v>0.5</v>
       </c>
       <c r="B52">
-        <v>0.154602696077244</v>
+        <v>0.145834823466311</v>
       </c>
       <c r="C52">
-        <v>496.7617592821007</v>
+        <v>715.3835100035139</v>
       </c>
       <c r="D52">
-        <v>2609.94321455146</v>
+        <v>2828.564965272873</v>
       </c>
       <c r="E52">
         <v>2143.91854473064</v>
@@ -5551,37 +5655,37 @@
         <v>358.8</v>
       </c>
       <c r="M52">
-        <v>425.4489955037396</v>
+        <v>383.2897070552144</v>
       </c>
       <c r="N52">
-        <v>-66.64899550373957</v>
+        <v>-24.48970705521435</v>
       </c>
       <c r="O52">
-        <v>-8.331124437967446</v>
+        <v>-3.061213381901794</v>
       </c>
       <c r="P52">
-        <v>-58.31787106577212</v>
+        <v>-21.42849367331256</v>
       </c>
       <c r="Q52">
-        <v>-48.21787106577212</v>
+        <v>-11.32849367331256</v>
       </c>
       <c r="R52">
         <v>1</v>
       </c>
       <c r="S52">
-        <v>0.1575409936371905</v>
+        <v>0.1568052484153245</v>
       </c>
       <c r="T52">
-        <v>2.17702278326139</v>
+        <v>2.163698905574898</v>
       </c>
       <c r="U52">
-        <v>0.1695366166625341</v>
+        <v>0.1527366166625341</v>
       </c>
       <c r="V52">
-        <v>0.1054180418193179</v>
+        <v>0.1170133170143783</v>
       </c>
       <c r="W52">
-        <v>0.1516643985172974</v>
+        <v>0.1348643985172974</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5589,7 +5693,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.8433443345545431</v>
+        <v>0.9361065361150267</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5600,13 +5704,13 @@
         <v>0.51</v>
       </c>
       <c r="B53">
-        <v>0.1558400622438693</v>
+        <v>0.1469041896329363</v>
       </c>
       <c r="C53">
-        <v>418.3207736246322</v>
+        <v>636.4962280912005</v>
       </c>
       <c r="D53">
-        <v>2581.691857999378</v>
+        <v>2799.867312465947</v>
       </c>
       <c r="E53">
         <v>2194.108173836027</v>
@@ -5633,37 +5737,37 @@
         <v>358.8</v>
       </c>
       <c r="M53">
-        <v>433.9579754138144</v>
+        <v>390.9555011963186</v>
       </c>
       <c r="N53">
-        <v>-75.15797541381437</v>
+        <v>-32.1555011963186</v>
       </c>
       <c r="O53">
-        <v>-9.394746926726796</v>
+        <v>-4.019437649539825</v>
       </c>
       <c r="P53">
-        <v>-65.76322848708757</v>
+        <v>-28.13606354677877</v>
       </c>
       <c r="Q53">
-        <v>-55.66322848708757</v>
+        <v>-18.03606354677877</v>
       </c>
       <c r="R53">
         <v>1.040816326530612</v>
       </c>
       <c r="S53">
-        <v>0.1598214220787659</v>
+        <v>0.1590706616482903</v>
       </c>
       <c r="T53">
-        <v>2.221451819654479</v>
+        <v>2.207856026096835</v>
       </c>
       <c r="U53">
-        <v>0.1695366166625341</v>
+        <v>0.1527366166625341</v>
       </c>
       <c r="V53">
-        <v>0.1033510213914881</v>
+        <v>0.1147189382493905</v>
       </c>
       <c r="W53">
-        <v>0.152014834167204</v>
+        <v>0.135214834167204</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5671,7 +5775,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.8268081711319049</v>
+        <v>0.9177515059951242</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5682,13 +5786,13 @@
         <v>0.52</v>
       </c>
       <c r="B54">
-        <v>0.1570774284104947</v>
+        <v>0.1479735557995617</v>
       </c>
       <c r="C54">
-        <v>340.4848526244677</v>
+        <v>558.185410709249</v>
       </c>
       <c r="D54">
-        <v>2554.045566104601</v>
+        <v>2771.746124189382</v>
       </c>
       <c r="E54">
         <v>2244.297802941414</v>
@@ -5715,37 +5819,37 @@
         <v>358.8</v>
       </c>
       <c r="M54">
-        <v>442.4669553238892</v>
+        <v>398.6212953374229</v>
       </c>
       <c r="N54">
-        <v>-83.66695532388917</v>
+        <v>-39.8212953374229</v>
       </c>
       <c r="O54">
-        <v>-10.45836941548615</v>
+        <v>-4.977661917177862</v>
       </c>
       <c r="P54">
-        <v>-73.20858590840302</v>
+        <v>-34.84363342024503</v>
       </c>
       <c r="Q54">
-        <v>-63.10858590840302</v>
+        <v>-24.74363342024503</v>
       </c>
       <c r="R54">
         <v>1.083333333333333</v>
       </c>
       <c r="S54">
-        <v>0.1621968683720735</v>
+        <v>0.1614304670992964</v>
       </c>
       <c r="T54">
-        <v>2.267732065897281</v>
+        <v>2.253853026640519</v>
       </c>
       <c r="U54">
-        <v>0.1695366166625341</v>
+        <v>0.1527366166625341</v>
       </c>
       <c r="V54">
-        <v>0.1013635017493441</v>
+        <v>0.1125128048215176</v>
       </c>
       <c r="W54">
-        <v>0.1523517915228834</v>
+        <v>0.1355517915228835</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5753,7 +5857,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.8109080139947529</v>
+        <v>0.9001024385721411</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5764,13 +5868,13 @@
         <v>0.53</v>
       </c>
       <c r="B55">
-        <v>0.1867126363030572</v>
+        <v>0.149042921966187</v>
       </c>
       <c r="C55">
-        <v>-231.0406243743337</v>
+        <v>480.4338609692131</v>
       </c>
       <c r="D55">
-        <v>2032.709718211187</v>
+        <v>2744.184203554734</v>
       </c>
       <c r="E55">
         <v>2294.487432046802</v>
@@ -5797,45 +5901,45 @@
         <v>358.8</v>
       </c>
       <c r="M55">
-        <v>589.8305631169281</v>
+        <v>406.2870894785272</v>
       </c>
       <c r="N55">
-        <v>-231.0305631169281</v>
+        <v>-47.4870894785272</v>
       </c>
       <c r="O55">
-        <v>-28.87882038961602</v>
+        <v>-5.935886184815899</v>
       </c>
       <c r="P55">
-        <v>-202.1517427273121</v>
+        <v>-41.5512032937113</v>
       </c>
       <c r="Q55">
-        <v>-192.0517427273121</v>
+        <v>-31.45120329371129</v>
       </c>
       <c r="R55">
         <v>1.127659574468085</v>
       </c>
       <c r="S55">
-        <v>0.1662305075415583</v>
+        <v>0.1638906898035367</v>
       </c>
       <c r="T55">
-        <v>2.346318483339889</v>
+        <v>2.301807346356275</v>
       </c>
       <c r="U55">
-        <v>0.2217366166625341</v>
+        <v>0.1527366166625341</v>
       </c>
       <c r="V55">
-        <v>0.07603878605915666</v>
+        <v>0.1103899217116777</v>
       </c>
       <c r="W55">
-        <v>0.2048760335066504</v>
+        <v>0.1358760335066504</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y55">
-        <v>0.6083102884732533</v>
+        <v>0.8831193736934214</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5846,13 +5950,13 @@
         <v>0.54</v>
       </c>
       <c r="B56">
-        <v>0.1884720024696825</v>
+        <v>0.1501122881328123</v>
       </c>
       <c r="C56">
-        <v>-305.5680550217476</v>
+        <v>403.2250592632677</v>
       </c>
       <c r="D56">
-        <v>2008.371916669161</v>
+        <v>2717.165030954176</v>
       </c>
       <c r="E56">
         <v>2344.677061152189</v>
@@ -5879,45 +5983,45 @@
         <v>358.8</v>
       </c>
       <c r="M56">
-        <v>600.9594416663042</v>
+        <v>413.9528836196315</v>
       </c>
       <c r="N56">
-        <v>-242.1594416663042</v>
+        <v>-55.1528836196315</v>
       </c>
       <c r="O56">
-        <v>-30.26993020828802</v>
+        <v>-6.894110452453937</v>
       </c>
       <c r="P56">
-        <v>-211.8895114580162</v>
+        <v>-48.25877316717756</v>
       </c>
       <c r="Q56">
-        <v>-201.7895114580162</v>
+        <v>-38.15877316717756</v>
       </c>
       <c r="R56">
         <v>1.173913043478261</v>
       </c>
       <c r="S56">
-        <v>0.1688485620533313</v>
+        <v>0.1664578787123093</v>
       </c>
       <c r="T56">
-        <v>2.397325406890756</v>
+        <v>2.351846636494455</v>
       </c>
       <c r="U56">
-        <v>0.2217366166625341</v>
+        <v>0.1527366166625341</v>
       </c>
       <c r="V56">
-        <v>0.0746306603913945</v>
+        <v>0.1083456639022022</v>
       </c>
       <c r="W56">
-        <v>0.2051882665280557</v>
+        <v>0.1361882665280557</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y56">
-        <v>0.597045283131156</v>
+        <v>0.8667653112176172</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5928,13 +6032,13 @@
         <v>0.55</v>
       </c>
       <c r="B57">
-        <v>0.1902313686363079</v>
+        <v>0.1511816542994377</v>
       </c>
       <c r="C57">
-        <v>-379.5195839671233</v>
+        <v>326.5431302468537</v>
       </c>
       <c r="D57">
-        <v>1984.610016829172</v>
+        <v>2690.672731043149</v>
       </c>
       <c r="E57">
         <v>2394.866690257576</v>
@@ -5961,45 +6065,45 @@
         <v>358.8</v>
       </c>
       <c r="M57">
-        <v>612.0883202156801</v>
+        <v>421.6186777607358</v>
       </c>
       <c r="N57">
-        <v>-253.2883202156801</v>
+        <v>-62.8186777607358</v>
       </c>
       <c r="O57">
-        <v>-31.66104002696002</v>
+        <v>-7.852334720091974</v>
       </c>
       <c r="P57">
-        <v>-221.6272801887201</v>
+        <v>-54.96634304064382</v>
       </c>
       <c r="Q57">
-        <v>-211.5272801887201</v>
+        <v>-44.86634304064382</v>
       </c>
       <c r="R57">
         <v>1.222222222222223</v>
       </c>
       <c r="S57">
-        <v>0.1715829745434054</v>
+        <v>0.1691391649059162</v>
       </c>
       <c r="T57">
-        <v>2.450599304821662</v>
+        <v>2.40410989508322</v>
       </c>
       <c r="U57">
-        <v>0.2217366166625341</v>
+        <v>0.1527366166625341</v>
       </c>
       <c r="V57">
-        <v>0.07327373929336915</v>
+        <v>0.1063757427403439</v>
       </c>
       <c r="W57">
-        <v>0.2054891456214099</v>
+        <v>0.1364891456214098</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y57">
-        <v>0.5861899143469532</v>
+        <v>0.8510059419227515</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6010,13 +6114,13 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1919907348029332</v>
+        <v>0.152251020466063</v>
       </c>
       <c r="C58">
-        <v>-452.9154134015525</v>
+        <v>250.3728117341875</v>
       </c>
       <c r="D58">
-        <v>1961.40381650013</v>
+        <v>2664.69204163587</v>
       </c>
       <c r="E58">
         <v>2445.056319362963</v>
@@ -6043,45 +6147,45 @@
         <v>358.8</v>
       </c>
       <c r="M58">
-        <v>623.2171987650562</v>
+        <v>429.2844719018401</v>
       </c>
       <c r="N58">
-        <v>-264.4171987650562</v>
+        <v>-70.4844719018401</v>
       </c>
       <c r="O58">
-        <v>-33.05214984563202</v>
+        <v>-8.810558987730012</v>
       </c>
       <c r="P58">
-        <v>-231.3650489194242</v>
+        <v>-61.67391291411008</v>
       </c>
       <c r="Q58">
-        <v>-221.2650489194242</v>
+        <v>-51.57391291411008</v>
       </c>
       <c r="R58">
         <v>1.272727272727273</v>
       </c>
       <c r="S58">
-        <v>0.174441678510301</v>
+        <v>0.171942327744687</v>
       </c>
       <c r="T58">
-        <v>2.506294743567609</v>
+        <v>2.458748756335112</v>
       </c>
       <c r="U58">
-        <v>0.2217366166625341</v>
+        <v>0.1527366166625341</v>
       </c>
       <c r="V58">
-        <v>0.0719652796631304</v>
+        <v>0.1044761759056949</v>
       </c>
       <c r="W58">
-        <v>0.2057792790328585</v>
+        <v>0.1367792790328585</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y58">
-        <v>0.5757222373050432</v>
+        <v>0.8358094072455595</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6092,13 +6196,13 @@
         <v>0.5700000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1937501009695586</v>
+        <v>0.1533203866326884</v>
       </c>
       <c r="C59">
-        <v>-525.7748115340432</v>
+        <v>174.6994253785601</v>
       </c>
       <c r="D59">
-        <v>1938.734047473027</v>
+        <v>2639.20828438563</v>
       </c>
       <c r="E59">
         <v>2495.24594846835</v>
@@ -6125,45 +6229,45 @@
         <v>358.8</v>
       </c>
       <c r="M59">
-        <v>634.3460773144323</v>
+        <v>436.9502660429444</v>
       </c>
       <c r="N59">
-        <v>-275.5460773144322</v>
+        <v>-78.15026604294439</v>
       </c>
       <c r="O59">
-        <v>-34.44325966430403</v>
+        <v>-9.768783255368049</v>
       </c>
       <c r="P59">
-        <v>-241.1028176501282</v>
+        <v>-68.38148278757635</v>
       </c>
       <c r="Q59">
-        <v>-231.0028176501282</v>
+        <v>-58.28148278757634</v>
       </c>
       <c r="R59">
         <v>1.325581395348838</v>
       </c>
       <c r="S59">
-        <v>0.177433345452401</v>
+        <v>0.1748758702503774</v>
       </c>
       <c r="T59">
-        <v>2.564580667836623</v>
+        <v>2.515928959970812</v>
       </c>
       <c r="U59">
-        <v>0.2217366166625341</v>
+        <v>0.1527366166625341</v>
       </c>
       <c r="V59">
-        <v>0.07070273089711057</v>
+        <v>0.1026432605389284</v>
       </c>
       <c r="W59">
-        <v>0.2060592323246072</v>
+        <v>0.1370592323246072</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y59">
-        <v>0.5656218471768846</v>
+        <v>0.8211460843114269</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6174,13 +6278,13 @@
         <v>0.58</v>
       </c>
       <c r="B60">
-        <v>0.1955094671361838</v>
+        <v>0.1543897527993137</v>
       </c>
       <c r="C60">
-        <v>-598.1161659493132</v>
+        <v>99.50884901911286</v>
       </c>
       <c r="D60">
-        <v>1916.582322163143</v>
+        <v>2614.207337131569</v>
       </c>
       <c r="E60">
         <v>2545.435577573737</v>
@@ -6207,45 +6311,45 @@
         <v>358.8</v>
       </c>
       <c r="M60">
-        <v>645.4749558638081</v>
+        <v>444.6160601840486</v>
       </c>
       <c r="N60">
-        <v>-286.6749558638081</v>
+        <v>-85.81606018404858</v>
       </c>
       <c r="O60">
-        <v>-35.83436948297601</v>
+        <v>-10.72700752300607</v>
       </c>
       <c r="P60">
-        <v>-250.8405863808321</v>
+        <v>-75.0890526610425</v>
       </c>
       <c r="Q60">
-        <v>-240.7405863808321</v>
+        <v>-64.98905266104251</v>
       </c>
       <c r="R60">
         <v>1.380952380952381</v>
       </c>
       <c r="S60">
-        <v>0.1805674727250771</v>
+        <v>0.1779491052563387</v>
       </c>
       <c r="T60">
-        <v>2.625642112308922</v>
+        <v>2.575832030446307</v>
       </c>
       <c r="U60">
-        <v>0.2217366166625341</v>
+        <v>0.1527366166625341</v>
       </c>
       <c r="V60">
-        <v>0.06948371829543627</v>
+        <v>0.1008735491503262</v>
       </c>
       <c r="W60">
-        <v>0.2063295320545714</v>
+        <v>0.1373295320545714</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y60">
-        <v>0.5558697463634902</v>
+        <v>0.8069883932026093</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6256,13 +6360,13 @@
         <v>0.59</v>
       </c>
       <c r="B61">
-        <v>0.1972688333028092</v>
+        <v>0.1882200217202431</v>
       </c>
       <c r="C61">
-        <v>-669.9570333489555</v>
+        <v>-553.4686002891781</v>
       </c>
       <c r="D61">
-        <v>1894.931083868888</v>
+        <v>2011.419516928666</v>
       </c>
       <c r="E61">
         <v>2595.625206679124</v>
@@ -6289,37 +6393,37 @@
         <v>358.8</v>
       </c>
       <c r="M61">
-        <v>656.6038344131841</v>
+        <v>612.1860126549165</v>
       </c>
       <c r="N61">
-        <v>-297.8038344131841</v>
+        <v>-253.3860126549164</v>
       </c>
       <c r="O61">
-        <v>-37.22547930164801</v>
+        <v>-31.67325158186456</v>
       </c>
       <c r="P61">
-        <v>-260.5783551115361</v>
+        <v>-221.7127610730519</v>
       </c>
       <c r="Q61">
-        <v>-250.4783551115361</v>
+        <v>-211.6127610730519</v>
       </c>
       <c r="R61">
         <v>1.439024390243902</v>
       </c>
       <c r="S61">
-        <v>0.1838544842549571</v>
+        <v>0.1833695779560154</v>
       </c>
       <c r="T61">
-        <v>2.689682163828652</v>
+        <v>2.681487132483537</v>
       </c>
       <c r="U61">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V61">
-        <v>0.06830602815483565</v>
+        <v>0.07326204629454924</v>
       </c>
       <c r="W61">
-        <v>0.2065906690818251</v>
+        <v>0.191590669081825</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6327,7 +6431,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.5464482252386852</v>
+        <v>0.5860963703563939</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6338,13 +6442,13 @@
         <v>0.6</v>
       </c>
       <c r="B62">
-        <v>0.1990281994694345</v>
+        <v>0.1898293878868684</v>
       </c>
       <c r="C62">
-        <v>-741.3141859587613</v>
+        <v>-625.4824429787614</v>
       </c>
       <c r="D62">
-        <v>1873.763560364469</v>
+        <v>1989.595303344469</v>
       </c>
       <c r="E62">
         <v>2645.814835784512</v>
@@ -6371,37 +6475,37 @@
         <v>358.8</v>
       </c>
       <c r="M62">
-        <v>667.7327129625602</v>
+        <v>622.5620467677116</v>
       </c>
       <c r="N62">
-        <v>-308.9327129625602</v>
+        <v>-263.7620467677116</v>
       </c>
       <c r="O62">
-        <v>-38.61658912032002</v>
+        <v>-32.97025584596395</v>
       </c>
       <c r="P62">
-        <v>-270.3161238422401</v>
+        <v>-230.7917909217477</v>
       </c>
       <c r="Q62">
-        <v>-260.2161238422401</v>
+        <v>-220.6917909217477</v>
       </c>
       <c r="R62">
         <v>1.5</v>
       </c>
       <c r="S62">
-        <v>0.187305846361331</v>
+        <v>0.1868088174049158</v>
       </c>
       <c r="T62">
-        <v>2.756924217924368</v>
+        <v>2.748524310795626</v>
       </c>
       <c r="U62">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V62">
-        <v>0.06716759435225506</v>
+        <v>0.0720410121896401</v>
       </c>
       <c r="W62">
-        <v>0.2068431015415035</v>
+        <v>0.1918431015415035</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6409,7 +6513,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.5373407548180404</v>
+        <v>0.5763280975171208</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6420,13 +6524,13 @@
         <v>0.61</v>
       </c>
       <c r="B63">
-        <v>0.2007875656360599</v>
+        <v>0.1914387540534938</v>
       </c>
       <c r="C63">
-        <v>-812.2036548600304</v>
+        <v>-697.0277768600599</v>
       </c>
       <c r="D63">
-        <v>1853.063720568588</v>
+        <v>1968.239598568558</v>
       </c>
       <c r="E63">
         <v>2696.004464889899</v>
@@ -6453,37 +6557,37 @@
         <v>358.8</v>
       </c>
       <c r="M63">
-        <v>678.8615915119361</v>
+        <v>632.9380808805068</v>
       </c>
       <c r="N63">
-        <v>-320.0615915119361</v>
+        <v>-274.1380808805068</v>
       </c>
       <c r="O63">
-        <v>-40.00769893899201</v>
+        <v>-34.26726011006335</v>
       </c>
       <c r="P63">
-        <v>-280.0538925729441</v>
+        <v>-239.8708207704435</v>
       </c>
       <c r="Q63">
-        <v>-269.9538925729441</v>
+        <v>-229.7708207704435</v>
       </c>
       <c r="R63">
         <v>1.564102564102564</v>
       </c>
       <c r="S63">
-        <v>0.190934201396237</v>
+        <v>0.190424428107606</v>
       </c>
       <c r="T63">
-        <v>2.827614582486532</v>
+        <v>2.818999293123719</v>
       </c>
       <c r="U63">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V63">
-        <v>0.06606648624811973</v>
+        <v>0.07086001198980993</v>
       </c>
       <c r="W63">
-        <v>0.2070872575270942</v>
+        <v>0.1920872575270942</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6595,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.5285318899849578</v>
+        <v>0.5668800959184794</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6502,13 +6606,13 @@
         <v>0.62</v>
       </c>
       <c r="B64">
-        <v>0.2025469318026852</v>
+        <v>0.1930481202201191</v>
       </c>
       <c r="C64">
-        <v>-882.6407704801122</v>
+        <v>-768.1195282078852</v>
       </c>
       <c r="D64">
-        <v>1832.816234053893</v>
+        <v>1947.33747632612</v>
       </c>
       <c r="E64">
         <v>2746.194093995286</v>
@@ -6535,37 +6639,37 @@
         <v>358.8</v>
       </c>
       <c r="M64">
-        <v>689.9904700613122</v>
+        <v>643.314114993302</v>
       </c>
       <c r="N64">
-        <v>-331.1904700613122</v>
+        <v>-284.514114993302</v>
       </c>
       <c r="O64">
-        <v>-41.39880875766402</v>
+        <v>-35.56426437416275</v>
       </c>
       <c r="P64">
-        <v>-289.7916613036481</v>
+        <v>-248.9498506191393</v>
       </c>
       <c r="Q64">
-        <v>-279.6916613036481</v>
+        <v>-238.8498506191393</v>
       </c>
       <c r="R64">
         <v>1.631578947368421</v>
       </c>
       <c r="S64">
-        <v>0.1947535224856116</v>
+        <v>0.1942303341104377</v>
       </c>
       <c r="T64">
-        <v>2.902025492551967</v>
+        <v>2.893183485048028</v>
       </c>
       <c r="U64">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V64">
-        <v>0.06500089776024683</v>
+        <v>0.06971710857061944</v>
       </c>
       <c r="W64">
-        <v>0.2073235375131497</v>
+        <v>0.1923235375131497</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6677,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.5200071820819746</v>
+        <v>0.5577368685649555</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6584,13 +6688,13 @@
         <v>0.63</v>
       </c>
       <c r="B65">
-        <v>0.2043062979693105</v>
+        <v>0.1946574863867445</v>
       </c>
       <c r="C65">
-        <v>-952.6402004571337</v>
+        <v>-838.7719959092342</v>
       </c>
       <c r="D65">
-        <v>1813.006433182259</v>
+        <v>1926.874637730158</v>
       </c>
       <c r="E65">
         <v>2796.383723100673</v>
@@ -6617,37 +6721,37 @@
         <v>358.8</v>
       </c>
       <c r="M65">
-        <v>701.1193486106881</v>
+        <v>653.6901491060972</v>
       </c>
       <c r="N65">
-        <v>-342.3193486106881</v>
+        <v>-294.8901491060972</v>
       </c>
       <c r="O65">
-        <v>-42.78991857633601</v>
+        <v>-36.86126863826215</v>
       </c>
       <c r="P65">
-        <v>-299.5294300343521</v>
+        <v>-258.0288804678351</v>
       </c>
       <c r="Q65">
-        <v>-289.4294300343521</v>
+        <v>-247.9288804678351</v>
       </c>
       <c r="R65">
         <v>1.702702702702703</v>
       </c>
       <c r="S65">
-        <v>0.1987792933636011</v>
+        <v>0.1982419647620712</v>
       </c>
       <c r="T65">
-        <v>2.98045861397229</v>
+        <v>2.971377633292569</v>
       </c>
       <c r="U65">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V65">
-        <v>0.06396913747833816</v>
+        <v>0.06861048779965723</v>
       </c>
       <c r="W65">
-        <v>0.2075523165472669</v>
+        <v>0.1925523165472669</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6759,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.5117530998267052</v>
+        <v>0.5488839023972578</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6666,13 +6770,13 @@
         <v>0.64</v>
       </c>
       <c r="B66">
-        <v>0.2060656641359359</v>
+        <v>0.1962668525533698</v>
       </c>
       <c r="C66">
-        <v>-1022.215985075431</v>
+        <v>-908.9988840838105</v>
       </c>
       <c r="D66">
-        <v>1793.620277669348</v>
+        <v>1906.837378660969</v>
       </c>
       <c r="E66">
         <v>2846.57335220606</v>
@@ -6699,37 +6803,37 @@
         <v>358.8</v>
       </c>
       <c r="M66">
-        <v>712.2482271600642</v>
+        <v>664.0661832188924</v>
       </c>
       <c r="N66">
-        <v>-353.4482271600642</v>
+        <v>-305.2661832188924</v>
       </c>
       <c r="O66">
-        <v>-44.18102839500802</v>
+        <v>-38.15827290236155</v>
       </c>
       <c r="P66">
-        <v>-309.2671987650562</v>
+        <v>-267.1079103165309</v>
       </c>
       <c r="Q66">
-        <v>-299.1671987650561</v>
+        <v>-257.0079103165309</v>
       </c>
       <c r="R66">
         <v>1.777777777777778</v>
       </c>
       <c r="S66">
-        <v>0.2030287181792567</v>
+        <v>0.2024764637832398</v>
       </c>
       <c r="T66">
-        <v>3.063249131027077</v>
+        <v>3.053915900884029</v>
       </c>
       <c r="U66">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V66">
-        <v>0.06296961970523911</v>
+        <v>0.06753844892778758</v>
       </c>
       <c r="W66">
-        <v>0.2077739462365679</v>
+        <v>0.1927739462365679</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6841,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.503756957641913</v>
+        <v>0.5403075914223008</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6748,13 +6852,13 @@
         <v>0.65</v>
       </c>
       <c r="B67">
-        <v>0.2276082901649551</v>
+        <v>0.1978762187199952</v>
       </c>
       <c r="C67">
-        <v>-1280.054710293981</v>
+        <v>-978.8133326902012</v>
       </c>
       <c r="D67">
-        <v>1585.971181556186</v>
+        <v>1887.212559159966</v>
       </c>
       <c r="E67">
         <v>2896.762981311448</v>
@@ -6781,45 +6885,45 @@
         <v>358.8</v>
       </c>
       <c r="M67">
-        <v>821.2468824649452</v>
+        <v>674.4422173316876</v>
       </c>
       <c r="N67">
-        <v>-462.4468824649452</v>
+        <v>-315.6422173316876</v>
       </c>
       <c r="O67">
-        <v>-57.80586030811815</v>
+        <v>-39.45527716646095</v>
       </c>
       <c r="P67">
-        <v>-404.641022156827</v>
+        <v>-276.1869401652266</v>
       </c>
       <c r="Q67">
-        <v>-394.541022156827</v>
+        <v>-266.0869401652266</v>
       </c>
       <c r="R67">
         <v>1.857142857142857</v>
       </c>
       <c r="S67">
-        <v>0.2083302811626464</v>
+        <v>0.2069529341770467</v>
       </c>
       <c r="T67">
-        <v>3.166538201815268</v>
+        <v>3.141170640909288</v>
       </c>
       <c r="U67">
-        <v>0.2517366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V67">
-        <v>0.0546120794582309</v>
+        <v>0.06649939586736009</v>
       </c>
       <c r="W67">
-        <v>0.2379887565508136</v>
+        <v>0.1929887565508136</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y67">
-        <v>0.4368966356658472</v>
+        <v>0.5319951669388807</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6830,13 +6934,13 @@
         <v>0.66</v>
       </c>
       <c r="B68">
-        <v>0.2296676563315804</v>
+        <v>0.1994855848866205</v>
       </c>
       <c r="C68">
-        <v>-1347.60434163463</v>
+        <v>-1048.22794626135</v>
       </c>
       <c r="D68">
-        <v>1568.611179320924</v>
+        <v>1867.987574694204</v>
       </c>
       <c r="E68">
         <v>2946.952610416835</v>
@@ -6863,45 +6967,45 @@
         <v>358.8</v>
       </c>
       <c r="M68">
-        <v>833.8814498874829</v>
+        <v>684.8182514444828</v>
       </c>
       <c r="N68">
-        <v>-475.0814498874828</v>
+        <v>-326.0182514444828</v>
       </c>
       <c r="O68">
-        <v>-59.38518123593536</v>
+        <v>-40.75228143056035</v>
       </c>
       <c r="P68">
-        <v>-415.6962686515475</v>
+        <v>-285.2659700139225</v>
       </c>
       <c r="Q68">
-        <v>-405.5962686515475</v>
+        <v>-275.1659700139224</v>
       </c>
       <c r="R68">
         <v>1.941176470588236</v>
       </c>
       <c r="S68">
-        <v>0.2131105835497831</v>
+        <v>0.2116927263587246</v>
       </c>
       <c r="T68">
-        <v>3.259671678339247</v>
+        <v>3.233558012700737</v>
       </c>
       <c r="U68">
-        <v>0.2517366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V68">
-        <v>0.05378462370886376</v>
+        <v>0.06549182926330918</v>
       </c>
       <c r="W68">
-        <v>0.2381970574615973</v>
+        <v>0.1931970574615972</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y68">
-        <v>0.4302769896709101</v>
+        <v>0.5239346341064735</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6912,13 +7016,13 @@
         <v>0.67</v>
       </c>
       <c r="B69">
-        <v>0.2317270224982058</v>
+        <v>0.2010949510532459</v>
       </c>
       <c r="C69">
-        <v>-1414.778043559505</v>
+        <v>-1117.254820901377</v>
       </c>
       <c r="D69">
-        <v>1551.627106501437</v>
+        <v>1849.150329159565</v>
       </c>
       <c r="E69">
         <v>2997.142239522222</v>
@@ -6945,45 +7049,45 @@
         <v>358.8</v>
       </c>
       <c r="M69">
-        <v>846.5160173100204</v>
+        <v>695.194285557278</v>
       </c>
       <c r="N69">
-        <v>-487.7160173100204</v>
+        <v>-336.394285557278</v>
       </c>
       <c r="O69">
-        <v>-60.96450216375255</v>
+        <v>-42.04928569465975</v>
       </c>
       <c r="P69">
-        <v>-426.7515151462678</v>
+        <v>-294.3449998626182</v>
       </c>
       <c r="Q69">
-        <v>-416.6515151462678</v>
+        <v>-284.2449998626182</v>
       </c>
       <c r="R69">
         <v>2.030303030303031</v>
       </c>
       <c r="S69">
-        <v>0.2181806012331099</v>
+        <v>0.2167197786726253</v>
       </c>
       <c r="T69">
-        <v>3.358449607985891</v>
+        <v>3.331544619146214</v>
       </c>
       <c r="U69">
-        <v>0.2517366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V69">
-        <v>0.05298186813111953</v>
+        <v>0.06451433927430456</v>
       </c>
       <c r="W69">
-        <v>0.2383991404347456</v>
+        <v>0.1933991404347455</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y69">
-        <v>0.4238549450489563</v>
+        <v>0.5161147141944364</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6994,13 +7098,13 @@
         <v>0.68</v>
       </c>
       <c r="B70">
-        <v>0.2337863886648311</v>
+        <v>0.2027043172198712</v>
       </c>
       <c r="C70">
-        <v>-1481.587896350562</v>
+        <v>-1185.905569665245</v>
       </c>
       <c r="D70">
-        <v>1535.006882815766</v>
+        <v>1830.689209501083</v>
       </c>
       <c r="E70">
         <v>3047.331868627609</v>
@@ -7027,45 +7131,45 @@
         <v>358.8</v>
       </c>
       <c r="M70">
-        <v>859.1505847325581</v>
+        <v>705.5703196700732</v>
       </c>
       <c r="N70">
-        <v>-500.350584732558</v>
+        <v>-346.7703196700732</v>
       </c>
       <c r="O70">
-        <v>-62.54382309156976</v>
+        <v>-43.34628995875915</v>
       </c>
       <c r="P70">
-        <v>-437.8067616409883</v>
+        <v>-303.4240297113141</v>
       </c>
       <c r="Q70">
-        <v>-427.7067616409882</v>
+        <v>-293.324029711314</v>
       </c>
       <c r="R70">
         <v>2.125</v>
       </c>
       <c r="S70">
-        <v>0.2235674950216445</v>
+        <v>0.2220610217561448</v>
       </c>
       <c r="T70">
-        <v>3.46340115823545</v>
+        <v>3.435655388494533</v>
       </c>
       <c r="U70">
-        <v>0.2517366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V70">
-        <v>0.05220272301154424</v>
+        <v>0.06356559899085891</v>
       </c>
       <c r="W70">
-        <v>0.2385952797910365</v>
+        <v>0.1935952797910365</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y70">
-        <v>0.417621784092354</v>
+        <v>0.5085247919268712</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7076,13 +7180,13 @@
         <v>0.6900000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2358457548314565</v>
+        <v>0.2043136833864965</v>
       </c>
       <c r="C71">
-        <v>-1548.045468184343</v>
+        <v>-1254.191346433188</v>
       </c>
       <c r="D71">
-        <v>1518.738940087373</v>
+        <v>1812.593061838528</v>
       </c>
       <c r="E71">
         <v>3097.521497732997</v>
@@ -7109,45 +7213,45 @@
         <v>358.8</v>
       </c>
       <c r="M71">
-        <v>871.7851521550957</v>
+        <v>715.9463537828684</v>
       </c>
       <c r="N71">
-        <v>-512.9851521550956</v>
+        <v>-357.1463537828684</v>
       </c>
       <c r="O71">
-        <v>-64.12314401938696</v>
+        <v>-44.64329422285855</v>
       </c>
       <c r="P71">
-        <v>-448.8620081357087</v>
+        <v>-312.5030595600098</v>
       </c>
       <c r="Q71">
-        <v>-438.7620081357087</v>
+        <v>-302.4030595600098</v>
       </c>
       <c r="R71">
         <v>2.225806451612904</v>
       </c>
       <c r="S71">
-        <v>0.2293019303449234</v>
+        <v>0.2277468611676334</v>
       </c>
       <c r="T71">
-        <v>3.575123776243045</v>
+        <v>3.546482981671776</v>
       </c>
       <c r="U71">
-        <v>0.2517366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V71">
-        <v>0.05144616180847839</v>
+        <v>0.062644358425774</v>
       </c>
       <c r="W71">
-        <v>0.2387857339485945</v>
+        <v>0.1937857339485945</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y71">
-        <v>0.4115692944678271</v>
+        <v>0.501154867406192</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7158,13 +7262,13 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2379051209980818</v>
+        <v>0.2307919871595789</v>
       </c>
       <c r="C72">
-        <v>-1614.161841983765</v>
+        <v>-1557.931627821986</v>
       </c>
       <c r="D72">
-        <v>1502.812195393338</v>
+        <v>1559.042409555118</v>
       </c>
       <c r="E72">
         <v>3147.711126838384</v>
@@ -7191,37 +7295,37 @@
         <v>358.8</v>
       </c>
       <c r="M72">
-        <v>884.4197195776334</v>
+        <v>849.2869792038623</v>
       </c>
       <c r="N72">
-        <v>-525.6197195776333</v>
+        <v>-490.4869792038623</v>
       </c>
       <c r="O72">
-        <v>-65.70246494720416</v>
+        <v>-61.31087240048279</v>
       </c>
       <c r="P72">
-        <v>-459.9172546304292</v>
+        <v>-429.1761068033795</v>
       </c>
       <c r="Q72">
-        <v>-449.8172546304291</v>
+        <v>-419.0761068033795</v>
       </c>
       <c r="R72">
         <v>2.333333333333334</v>
       </c>
       <c r="S72">
-        <v>0.2354186613564208</v>
+        <v>0.2350415485614113</v>
       </c>
       <c r="T72">
-        <v>3.69429456878448</v>
+        <v>3.688670016571013</v>
       </c>
       <c r="U72">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V72">
-        <v>0.05071121663978583</v>
+        <v>0.05280900461001208</v>
       </c>
       <c r="W72">
-        <v>0.2389707465587936</v>
+        <v>0.2289707465587936</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7333,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.4056897331182867</v>
+        <v>0.4224720368800967</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7240,13 +7344,13 @@
         <v>0.71</v>
       </c>
       <c r="B73">
-        <v>0.2399644871647071</v>
+        <v>0.2327513533262042</v>
       </c>
       <c r="C73">
-        <v>-1679.9476405979</v>
+        <v>-1624.093850434228</v>
       </c>
       <c r="D73">
-        <v>1487.21602588459</v>
+        <v>1543.069816048261</v>
       </c>
       <c r="E73">
         <v>3197.90075594377</v>
@@ -7273,37 +7377,37 @@
         <v>358.8</v>
       </c>
       <c r="M73">
-        <v>897.0542870001708</v>
+        <v>861.4196503353459</v>
       </c>
       <c r="N73">
-        <v>-538.2542870001707</v>
+        <v>-502.6196503353459</v>
       </c>
       <c r="O73">
-        <v>-67.28178587502134</v>
+        <v>-62.82745629191823</v>
       </c>
       <c r="P73">
-        <v>-470.9725011251494</v>
+        <v>-439.7921940434276</v>
       </c>
       <c r="Q73">
-        <v>-460.8725011251494</v>
+        <v>-429.6921940434276</v>
       </c>
       <c r="R73">
         <v>2.448275862068965</v>
       </c>
       <c r="S73">
-        <v>0.2419572358859525</v>
+        <v>0.2415671192014599</v>
       </c>
       <c r="T73">
-        <v>3.821684036673599</v>
+        <v>3.815865534383805</v>
       </c>
       <c r="U73">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V73">
-        <v>0.04999697415190153</v>
+        <v>0.05206521581268798</v>
       </c>
       <c r="W73">
-        <v>0.2391505475461702</v>
+        <v>0.2291505475461702</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7415,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.3999757932152124</v>
+        <v>0.4165217265015039</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7322,13 +7426,13 @@
         <v>0.72</v>
       </c>
       <c r="B74">
-        <v>0.2420238533313325</v>
+        <v>0.2347107194928296</v>
       </c>
       <c r="C74">
-        <v>-1745.413050429982</v>
+        <v>-1689.932109474265</v>
       </c>
       <c r="D74">
-        <v>1471.940245157895</v>
+        <v>1527.421186113612</v>
       </c>
       <c r="E74">
         <v>3248.090385049158</v>
@@ -7355,37 +7459,37 @@
         <v>358.8</v>
       </c>
       <c r="M74">
-        <v>909.6888544227085</v>
+        <v>873.5523214668297</v>
       </c>
       <c r="N74">
-        <v>-550.8888544227084</v>
+        <v>-514.7523214668297</v>
       </c>
       <c r="O74">
-        <v>-68.86110680283855</v>
+        <v>-64.34404018335371</v>
       </c>
       <c r="P74">
-        <v>-482.0277476198698</v>
+        <v>-450.408281283476</v>
       </c>
       <c r="Q74">
-        <v>-471.9277476198698</v>
+        <v>-440.3082812834759</v>
       </c>
       <c r="R74">
         <v>2.571428571428571</v>
       </c>
       <c r="S74">
-        <v>0.248962851453308</v>
+        <v>0.2485588020300835</v>
       </c>
       <c r="T74">
-        <v>3.958172752269084</v>
+        <v>3.952146446326084</v>
       </c>
       <c r="U74">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V74">
-        <v>0.04930257173312513</v>
+        <v>0.05134208781528953</v>
       </c>
       <c r="W74">
-        <v>0.2393253540616753</v>
+        <v>0.2293253540616753</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7497,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.3944205738650011</v>
+        <v>0.4107367025223162</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7404,13 +7508,13 @@
         <v>0.73</v>
       </c>
       <c r="B75">
-        <v>0.2440832194979577</v>
+        <v>0.2366700856594549</v>
       </c>
       <c r="C75">
-        <v>-1810.567843624045</v>
+        <v>-1755.456162161689</v>
       </c>
       <c r="D75">
-        <v>1456.975081069219</v>
+        <v>1512.086762531575</v>
       </c>
       <c r="E75">
         <v>3298.280014154545</v>
@@ -7437,37 +7541,37 @@
         <v>358.8</v>
       </c>
       <c r="M75">
-        <v>922.3234218452461</v>
+        <v>885.6849925983134</v>
       </c>
       <c r="N75">
-        <v>-563.523421845246</v>
+        <v>-526.8849925983134</v>
       </c>
       <c r="O75">
-        <v>-70.44042773065576</v>
+        <v>-65.86062407478917</v>
       </c>
       <c r="P75">
-        <v>-493.0829941145903</v>
+        <v>-461.0243685235242</v>
       </c>
       <c r="Q75">
-        <v>-482.9829941145903</v>
+        <v>-450.9243685235242</v>
       </c>
       <c r="R75">
         <v>2.703703703703703</v>
       </c>
       <c r="S75">
-        <v>0.2564874015071342</v>
+        <v>0.2560683872904569</v>
       </c>
       <c r="T75">
-        <v>4.104771743093865</v>
+        <v>4.098522240634457</v>
       </c>
       <c r="U75">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V75">
-        <v>0.04862719403815081</v>
+        <v>0.05063877154384721</v>
       </c>
       <c r="W75">
-        <v>0.2394953713575775</v>
+        <v>0.2294953713575775</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7579,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.3890175523052065</v>
+        <v>0.4051101723507777</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7486,13 +7590,13 @@
         <v>0.74</v>
       </c>
       <c r="B76">
-        <v>0.2461425856645831</v>
+        <v>0.2386294518260803</v>
       </c>
       <c r="C76">
-        <v>-1875.421398911772</v>
+        <v>-1820.675377783391</v>
       </c>
       <c r="D76">
-        <v>1442.311154886879</v>
+        <v>1497.057176015261</v>
       </c>
       <c r="E76">
         <v>3348.469643259932</v>
@@ -7519,37 +7623,37 @@
         <v>358.8</v>
       </c>
       <c r="M76">
-        <v>934.9579892677837</v>
+        <v>897.8176637297971</v>
       </c>
       <c r="N76">
-        <v>-576.1579892677837</v>
+        <v>-539.0176637297971</v>
       </c>
       <c r="O76">
-        <v>-72.01974865847296</v>
+        <v>-67.37720796622463</v>
       </c>
       <c r="P76">
-        <v>-504.1382406093107</v>
+        <v>-471.6404557635724</v>
       </c>
       <c r="Q76">
-        <v>-494.0382406093107</v>
+        <v>-461.5404557635724</v>
       </c>
       <c r="R76">
         <v>2.846153846153846</v>
       </c>
       <c r="S76">
-        <v>0.2645907631035624</v>
+        <v>0.2641556329554745</v>
       </c>
       <c r="T76">
-        <v>4.262647579366706</v>
+        <v>4.256157711428091</v>
       </c>
       <c r="U76">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V76">
-        <v>0.04797006979439201</v>
+        <v>0.04995446382028171</v>
       </c>
       <c r="W76">
-        <v>0.2396607935914283</v>
+        <v>0.2296607935914282</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7661,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.383760558355136</v>
+        <v>0.3996357105622538</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7568,13 +7672,13 @@
         <v>0.75</v>
       </c>
       <c r="B77">
-        <v>0.2482019518312085</v>
+        <v>0.2405888179927056</v>
       </c>
       <c r="C77">
-        <v>-1939.982721212984</v>
+        <v>-1885.598756783354</v>
       </c>
       <c r="D77">
-        <v>1427.939461691056</v>
+        <v>1482.323426120685</v>
       </c>
       <c r="E77">
         <v>3398.65927236532</v>
@@ -7601,37 +7705,37 @@
         <v>358.8</v>
       </c>
       <c r="M77">
-        <v>947.5925566903214</v>
+        <v>909.950334861281</v>
       </c>
       <c r="N77">
-        <v>-588.7925566903214</v>
+        <v>-551.150334861281</v>
       </c>
       <c r="O77">
-        <v>-73.59906958629017</v>
+        <v>-68.89379185766012</v>
       </c>
       <c r="P77">
-        <v>-515.1934871040312</v>
+        <v>-482.2565430036208</v>
       </c>
       <c r="Q77">
-        <v>-505.0934871040312</v>
+        <v>-472.1565430036208</v>
       </c>
       <c r="R77">
         <v>3</v>
       </c>
       <c r="S77">
-        <v>0.273342393627705</v>
+        <v>0.2728898582736934</v>
       </c>
       <c r="T77">
-        <v>4.433153482541375</v>
+        <v>4.426404019885214</v>
       </c>
       <c r="U77">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V77">
-        <v>0.04733046886380012</v>
+        <v>0.04928840430267795</v>
       </c>
       <c r="W77">
-        <v>0.2398218045657096</v>
+        <v>0.2298218045657096</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7743,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.3786437509104009</v>
+        <v>0.3943072344214237</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7650,13 +7754,13 @@
         <v>0.76</v>
       </c>
       <c r="B78">
-        <v>0.2502613179978338</v>
+        <v>0.2425481841593309</v>
       </c>
       <c r="C78">
-        <v>-2004.260460075855</v>
+        <v>-1950.234948736173</v>
       </c>
       <c r="D78">
-        <v>1413.851351933572</v>
+        <v>1467.876863273253</v>
       </c>
       <c r="E78">
         <v>3448.848901470707</v>
@@ -7683,37 +7787,37 @@
         <v>358.8</v>
       </c>
       <c r="M78">
-        <v>960.2271241128591</v>
+        <v>922.0830059927648</v>
       </c>
       <c r="N78">
-        <v>-601.427124112859</v>
+        <v>-563.2830059927649</v>
       </c>
       <c r="O78">
-        <v>-75.17839051410738</v>
+        <v>-70.41037574909561</v>
       </c>
       <c r="P78">
-        <v>-526.2487335987516</v>
+        <v>-492.8726302436693</v>
       </c>
       <c r="Q78">
-        <v>-516.1487335987516</v>
+        <v>-482.7726302436693</v>
       </c>
       <c r="R78">
         <v>3.166666666666667</v>
       </c>
       <c r="S78">
-        <v>0.282823326695526</v>
+        <v>0.282351935701764</v>
       </c>
       <c r="T78">
-        <v>4.617868210980599</v>
+        <v>4.610837520713766</v>
       </c>
       <c r="U78">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V78">
-        <v>0.04670769953664484</v>
+        <v>0.04863987266711639</v>
       </c>
       <c r="W78">
-        <v>0.2399785784090889</v>
+        <v>0.2299785784090889</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7825,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.3736615962931589</v>
+        <v>0.3891189813369311</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7732,13 +7836,13 @@
         <v>0.77</v>
       </c>
       <c r="B79">
-        <v>0.2523206841644592</v>
+        <v>0.2445075503259563</v>
       </c>
       <c r="C79">
-        <v>-2068.262927036207</v>
+        <v>-2014.5922692797</v>
       </c>
       <c r="D79">
-        <v>1400.038514078607</v>
+        <v>1453.709171835113</v>
       </c>
       <c r="E79">
         <v>3499.038530576094</v>
@@ -7765,37 +7869,37 @@
         <v>358.8</v>
       </c>
       <c r="M79">
-        <v>972.8616915353966</v>
+        <v>934.2156771242485</v>
       </c>
       <c r="N79">
-        <v>-614.0616915353967</v>
+        <v>-575.4156771242485</v>
       </c>
       <c r="O79">
-        <v>-76.75771144192458</v>
+        <v>-71.92695964053107</v>
       </c>
       <c r="P79">
-        <v>-537.3039800934721</v>
+        <v>-503.4887174837174</v>
       </c>
       <c r="Q79">
-        <v>-527.2039800934721</v>
+        <v>-493.3887174837174</v>
       </c>
       <c r="R79">
         <v>3.347826086956522</v>
       </c>
       <c r="S79">
-        <v>0.2931286887257663</v>
+        <v>0.2926368024714059</v>
       </c>
       <c r="T79">
-        <v>4.818645089718887</v>
+        <v>4.811308717266536</v>
       </c>
       <c r="U79">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V79">
-        <v>0.04610110603616895</v>
+        <v>0.04800818600910189</v>
       </c>
       <c r="W79">
-        <v>0.2401312802045882</v>
+        <v>0.2301312802045882</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7907,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.3688088482893515</v>
+        <v>0.3840654880728152</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7814,13 +7918,13 @@
         <v>0.78</v>
       </c>
       <c r="B80">
-        <v>0.2543800503310845</v>
+        <v>0.2464669164925816</v>
       </c>
       <c r="C80">
-        <v>-2131.998111969074</v>
+        <v>-2078.678716076486</v>
       </c>
       <c r="D80">
-        <v>1386.492958251127</v>
+        <v>1439.812354143715</v>
       </c>
       <c r="E80">
         <v>3549.228159681481</v>
@@ -7847,37 +7951,37 @@
         <v>358.8</v>
       </c>
       <c r="M80">
-        <v>985.4962589579343</v>
+        <v>946.3483482557323</v>
       </c>
       <c r="N80">
-        <v>-626.6962589579343</v>
+        <v>-587.5483482557322</v>
       </c>
       <c r="O80">
-        <v>-78.33703236974179</v>
+        <v>-73.44354353196653</v>
       </c>
       <c r="P80">
-        <v>-548.3592265881925</v>
+        <v>-514.1048047237657</v>
       </c>
       <c r="Q80">
-        <v>-538.2592265881925</v>
+        <v>-504.0048047237657</v>
       </c>
       <c r="R80">
         <v>3.545454545454546</v>
       </c>
       <c r="S80">
-        <v>0.3043709018496647</v>
+        <v>0.3038566571291972</v>
       </c>
       <c r="T80">
-        <v>5.037674411978835</v>
+        <v>5.030004568051381</v>
       </c>
       <c r="U80">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V80">
-        <v>0.04551006621519241</v>
+        <v>0.04739269644488264</v>
       </c>
       <c r="W80">
-        <v>0.2402800665694337</v>
+        <v>0.2302800665694337</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7989,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.3640805297215393</v>
+        <v>0.3791415715590611</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7896,13 +8000,13 @@
         <v>0.79</v>
       </c>
       <c r="B81">
-        <v>0.2564394164977098</v>
+        <v>0.248426282659207</v>
       </c>
       <c r="C81">
-        <v>-2195.473698500145</v>
+        <v>-2142.501983868381</v>
       </c>
       <c r="D81">
-        <v>1373.207000825443</v>
+        <v>1426.178715457207</v>
       </c>
       <c r="E81">
         <v>3599.417788786869</v>
@@ -7929,37 +8033,37 @@
         <v>358.8</v>
       </c>
       <c r="M81">
-        <v>998.1308263804719</v>
+        <v>958.4810193872161</v>
       </c>
       <c r="N81">
-        <v>-639.330826380472</v>
+        <v>-599.6810193872161</v>
       </c>
       <c r="O81">
-        <v>-79.916353297559</v>
+        <v>-74.96012742340201</v>
       </c>
       <c r="P81">
-        <v>-559.414473082913</v>
+        <v>-524.7208919638141</v>
       </c>
       <c r="Q81">
-        <v>-549.314473082913</v>
+        <v>-514.6208919638141</v>
       </c>
       <c r="R81">
         <v>3.761904761904763</v>
       </c>
       <c r="S81">
-        <v>0.316683801937744</v>
+        <v>0.3161450693734447</v>
       </c>
       <c r="T81">
-        <v>5.277563669692113</v>
+        <v>5.269528595101447</v>
       </c>
       <c r="U81">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V81">
-        <v>0.04493398942765833</v>
+        <v>0.04679278889494742</v>
       </c>
       <c r="W81">
-        <v>0.2404250861908653</v>
+        <v>0.2304250861908653</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +8071,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3594719154212666</v>
+        <v>0.3743423111595793</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7978,13 +8082,13 @@
         <v>0.8</v>
       </c>
       <c r="B82">
-        <v>0.2584987826643352</v>
+        <v>0.2503856488258323</v>
       </c>
       <c r="C82">
-        <v>-2258.697078539548</v>
+        <v>-2206.069478683843</v>
       </c>
       <c r="D82">
-        <v>1360.173249891428</v>
+        <v>1412.800849747132</v>
       </c>
       <c r="E82">
         <v>3649.607417892256</v>
@@ -8011,37 +8115,37 @@
         <v>358.8</v>
       </c>
       <c r="M82">
-        <v>1010.76539380301</v>
+        <v>970.6136905186997</v>
       </c>
       <c r="N82">
-        <v>-651.9653938030096</v>
+        <v>-611.8136905186998</v>
       </c>
       <c r="O82">
-        <v>-81.49567422537621</v>
+        <v>-76.47671131483747</v>
       </c>
       <c r="P82">
-        <v>-570.4697195776334</v>
+        <v>-535.3369792038623</v>
       </c>
       <c r="Q82">
-        <v>-560.3697195776334</v>
+        <v>-525.2369792038622</v>
       </c>
       <c r="R82">
         <v>4.000000000000001</v>
       </c>
       <c r="S82">
-        <v>0.3302279920346312</v>
+        <v>0.3296623228421169</v>
       </c>
       <c r="T82">
-        <v>5.541441853176719</v>
+        <v>5.533005024856519</v>
       </c>
       <c r="U82">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V82">
-        <v>0.0443723145598126</v>
+        <v>0.04620787903376058</v>
       </c>
       <c r="W82">
-        <v>0.2405664803217612</v>
+        <v>0.2305664803217612</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8153,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.3549785164785008</v>
+        <v>0.3696630322700846</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8060,13 +8164,13 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2605581488309605</v>
+        <v>0.2523450149924577</v>
       </c>
       <c r="C83">
-        <v>-2321.675365995726</v>
+        <v>-2269.388331253078</v>
       </c>
       <c r="D83">
-        <v>1347.384591540636</v>
+        <v>1399.671626283284</v>
       </c>
       <c r="E83">
         <v>3699.797046997643</v>
@@ -8093,37 +8197,37 @@
         <v>358.8</v>
       </c>
       <c r="M83">
-        <v>1023.399961225547</v>
+        <v>982.7463616501835</v>
       </c>
       <c r="N83">
-        <v>-664.5999612255471</v>
+        <v>-623.9463616501835</v>
       </c>
       <c r="O83">
-        <v>-83.07499515319338</v>
+        <v>-77.99329520627293</v>
       </c>
       <c r="P83">
-        <v>-581.5249660723537</v>
+        <v>-545.9530664439105</v>
       </c>
       <c r="Q83">
-        <v>-571.4249660723536</v>
+        <v>-535.8530664439105</v>
       </c>
       <c r="R83">
         <v>4.263157894736843</v>
       </c>
       <c r="S83">
-        <v>0.3451978863522435</v>
+        <v>0.3446024450969651</v>
       </c>
       <c r="T83">
-        <v>5.833096687554442</v>
+        <v>5.824215815638441</v>
       </c>
       <c r="U83">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V83">
-        <v>0.04382450820722233</v>
+        <v>0.04563741139136847</v>
       </c>
       <c r="W83">
-        <v>0.2407043832395485</v>
+        <v>0.2307043832395485</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8235,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3505960656577787</v>
+        <v>0.3650992911309477</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8142,13 +8246,13 @@
         <v>0.8200000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2626175149975859</v>
+        <v>0.254304381159083</v>
       </c>
       <c r="C84">
-        <v>-2384.415409722882</v>
+        <v>-2332.465409682049</v>
       </c>
       <c r="D84">
-        <v>1334.834176918868</v>
+        <v>1386.784176959701</v>
       </c>
       <c r="E84">
         <v>3749.98667610303</v>
@@ -8175,37 +8279,37 @@
         <v>358.8</v>
       </c>
       <c r="M84">
-        <v>1036.034528648085</v>
+        <v>994.8790327816673</v>
       </c>
       <c r="N84">
-        <v>-677.234528648085</v>
+        <v>-636.0790327816674</v>
       </c>
       <c r="O84">
-        <v>-84.65431608101062</v>
+        <v>-79.50987909770842</v>
       </c>
       <c r="P84">
-        <v>-592.5802125670743</v>
+        <v>-556.5691536839589</v>
       </c>
       <c r="Q84">
-        <v>-582.4802125670743</v>
+        <v>-546.4691536839589</v>
       </c>
       <c r="R84">
         <v>4.555555555555557</v>
       </c>
       <c r="S84">
-        <v>0.3618311022607014</v>
+        <v>0.3612025809356855</v>
       </c>
       <c r="T84">
-        <v>6.1571576146408</v>
+        <v>6.147783360951689</v>
       </c>
       <c r="U84">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V84">
-        <v>0.04329006298518302</v>
+        <v>0.04508085759391275</v>
       </c>
       <c r="W84">
-        <v>0.2408389226715361</v>
+        <v>0.2308389226715361</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8317,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3463205038814642</v>
+        <v>0.3606468607513019</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8224,13 +8328,13 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2646768811642112</v>
+        <v>0.2562637473257083</v>
       </c>
       <c r="C85">
-        <v>-2446.923805751486</v>
+        <v>-2395.30733143271</v>
       </c>
       <c r="D85">
-        <v>1322.515409995651</v>
+        <v>1374.131884314427</v>
       </c>
       <c r="E85">
         <v>3800.176305208417</v>
@@ -8257,37 +8361,37 @@
         <v>358.8</v>
       </c>
       <c r="M85">
-        <v>1048.669096070622</v>
+        <v>1007.011703913151</v>
       </c>
       <c r="N85">
-        <v>-689.8690960706224</v>
+        <v>-648.211703913151</v>
       </c>
       <c r="O85">
-        <v>-86.2336370088278</v>
+        <v>-81.02646298914388</v>
       </c>
       <c r="P85">
-        <v>-603.6354590617946</v>
+        <v>-567.1852409240072</v>
       </c>
       <c r="Q85">
-        <v>-593.5354590617945</v>
+        <v>-557.0852409240072</v>
       </c>
       <c r="R85">
         <v>4.882352941176473</v>
       </c>
       <c r="S85">
-        <v>0.3804211670995662</v>
+        <v>0.3797556739319023</v>
       </c>
       <c r="T85">
-        <v>6.519343356678495</v>
+        <v>6.509417676301789</v>
       </c>
       <c r="U85">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V85">
-        <v>0.04276849596126516</v>
+        <v>0.04453771473133549</v>
       </c>
       <c r="W85">
-        <v>0.2409702201895</v>
+        <v>0.2309702201894999</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8399,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3421479676901212</v>
+        <v>0.3563017178506839</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8306,13 +8410,13 @@
         <v>0.84</v>
       </c>
       <c r="B86">
-        <v>0.2667362473308366</v>
+        <v>0.2582231134923337</v>
       </c>
       <c r="C86">
-        <v>-2509.206908847757</v>
+        <v>-2457.920474653357</v>
       </c>
       <c r="D86">
-        <v>1310.421936004766</v>
+        <v>1361.708370199166</v>
       </c>
       <c r="E86">
         <v>3850.365934313804</v>
@@ -8339,37 +8443,37 @@
         <v>358.8</v>
       </c>
       <c r="M86">
-        <v>1061.30366349316</v>
+        <v>1019.144375044635</v>
       </c>
       <c r="N86">
-        <v>-702.5036634931598</v>
+        <v>-660.3443750446345</v>
       </c>
       <c r="O86">
-        <v>-87.81295793664498</v>
+        <v>-82.54304688057931</v>
       </c>
       <c r="P86">
-        <v>-614.6907055565148</v>
+        <v>-577.8013281640551</v>
       </c>
       <c r="Q86">
-        <v>-604.5907055565148</v>
+        <v>-567.7013281640551</v>
       </c>
       <c r="R86">
         <v>5.249999999999999</v>
       </c>
       <c r="S86">
-        <v>0.4013349900432889</v>
+        <v>0.400627903552646</v>
       </c>
       <c r="T86">
-        <v>6.926802316470897</v>
+        <v>6.916256281070646</v>
       </c>
       <c r="U86">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V86">
-        <v>0.04225934719982154</v>
+        <v>0.04400750384167675</v>
       </c>
       <c r="W86">
-        <v>0.2410983915760837</v>
+        <v>0.2310983915760837</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8481,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3380747775985723</v>
+        <v>0.3520600307334141</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8388,13 +8492,13 @@
         <v>0.85</v>
       </c>
       <c r="B87">
-        <v>0.2687956134974619</v>
+        <v>0.260182479658959</v>
       </c>
       <c r="C87">
-        <v>-2571.270843444669</v>
+        <v>-2520.310988899863</v>
       </c>
       <c r="D87">
-        <v>1298.547630513241</v>
+        <v>1349.507485058047</v>
       </c>
       <c r="E87">
         <v>3900.555563419191</v>
@@ -8421,37 +8525,37 @@
         <v>358.8</v>
       </c>
       <c r="M87">
-        <v>1073.938230915697</v>
+        <v>1031.277046176118</v>
       </c>
       <c r="N87">
-        <v>-715.1382309156975</v>
+        <v>-672.4770461761184</v>
       </c>
       <c r="O87">
-        <v>-89.39227886446218</v>
+        <v>-84.0596307720148</v>
       </c>
       <c r="P87">
-        <v>-625.7459520512352</v>
+        <v>-588.4174154041036</v>
       </c>
       <c r="Q87">
-        <v>-615.6459520512352</v>
+        <v>-578.3174154041036</v>
       </c>
       <c r="R87">
         <v>5.666666666666666</v>
       </c>
       <c r="S87">
-        <v>0.4250373227128416</v>
+        <v>0.4242830971228224</v>
       </c>
       <c r="T87">
-        <v>7.388589137568958</v>
+        <v>7.377340033142024</v>
       </c>
       <c r="U87">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V87">
-        <v>0.0417621784092354</v>
+        <v>0.0434897685023629</v>
       </c>
       <c r="W87">
-        <v>0.2412235471653361</v>
+        <v>0.2312235471653361</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8563,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3340974272738831</v>
+        <v>0.3479181480189032</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8470,13 +8574,13 @@
         <v>0.86</v>
       </c>
       <c r="B88">
-        <v>0.2708549796640872</v>
+        <v>0.2621418458255843</v>
       </c>
       <c r="C88">
-        <v>-2633.121513983981</v>
+        <v>-2582.484805285649</v>
       </c>
       <c r="D88">
-        <v>1286.886589079317</v>
+        <v>1337.523297777648</v>
       </c>
       <c r="E88">
         <v>3950.745192524578</v>
@@ -8503,37 +8607,37 @@
         <v>358.8</v>
       </c>
       <c r="M88">
-        <v>1086.572798338235</v>
+        <v>1043.409717307602</v>
       </c>
       <c r="N88">
-        <v>-727.7727983382351</v>
+        <v>-684.6097173076021</v>
       </c>
       <c r="O88">
-        <v>-90.97159979227939</v>
+        <v>-85.57621466345026</v>
       </c>
       <c r="P88">
-        <v>-636.8011985459557</v>
+        <v>-599.0335026441518</v>
       </c>
       <c r="Q88">
-        <v>-626.7011985459557</v>
+        <v>-588.9335026441518</v>
       </c>
       <c r="R88">
         <v>6.142857142857142</v>
       </c>
       <c r="S88">
-        <v>0.4521257029066159</v>
+        <v>0.4513176040601669</v>
       </c>
       <c r="T88">
-        <v>7.916345504538168</v>
+        <v>7.904292892652167</v>
       </c>
       <c r="U88">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V88">
-        <v>0.04127657168354661</v>
+        <v>0.04298407351977729</v>
       </c>
       <c r="W88">
-        <v>0.2413457921594895</v>
+        <v>0.2313457921594895</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8645,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3302125734683728</v>
+        <v>0.3438725881582182</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8552,13 +8656,13 @@
         <v>0.87</v>
       </c>
       <c r="B89">
-        <v>0.2729143458307126</v>
+        <v>0.2641012119922097</v>
       </c>
       <c r="C89">
-        <v>-2694.764614706002</v>
+        <v>-2644.447646095618</v>
       </c>
       <c r="D89">
-        <v>1275.433117462683</v>
+        <v>1325.750086073067</v>
       </c>
       <c r="E89">
         <v>4000.934821629965</v>
@@ -8585,37 +8689,37 @@
         <v>358.8</v>
       </c>
       <c r="M89">
-        <v>1099.207365760773</v>
+        <v>1055.542388439086</v>
       </c>
       <c r="N89">
-        <v>-740.4073657607728</v>
+        <v>-696.742388439086</v>
       </c>
       <c r="O89">
-        <v>-92.5509207200966</v>
+        <v>-87.09279855488575</v>
       </c>
       <c r="P89">
-        <v>-647.8564450406761</v>
+        <v>-609.6495898842002</v>
       </c>
       <c r="Q89">
-        <v>-637.7564450406761</v>
+        <v>-599.5495898842001</v>
       </c>
       <c r="R89">
         <v>6.692307692307692</v>
       </c>
       <c r="S89">
-        <v>0.4833815262071249</v>
+        <v>0.4825112659109489</v>
       </c>
       <c r="T89">
-        <v>8.525295158733412</v>
+        <v>8.512315422856181</v>
       </c>
       <c r="U89">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V89">
-        <v>0.04080212833086217</v>
+        <v>0.04249000370920513</v>
       </c>
       <c r="W89">
-        <v>0.2414652269238923</v>
+        <v>0.2314652269238923</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8727,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3264170266468973</v>
+        <v>0.339920029673641</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8634,13 +8738,13 @@
         <v>0.88</v>
       </c>
       <c r="B90">
-        <v>0.2749737119973379</v>
+        <v>0.266060578158835</v>
       </c>
       <c r="C90">
-        <v>-2756.205638921191</v>
+        <v>-2706.205033896753</v>
       </c>
       <c r="D90">
-        <v>1264.181722352881</v>
+        <v>1314.182327377319</v>
       </c>
       <c r="E90">
         <v>4051.124450735353</v>
@@ -8667,37 +8771,37 @@
         <v>358.8</v>
       </c>
       <c r="M90">
-        <v>1111.84193318331</v>
+        <v>1067.67505957057</v>
       </c>
       <c r="N90">
-        <v>-753.0419331833104</v>
+        <v>-708.8750595705696</v>
       </c>
       <c r="O90">
-        <v>-94.13024164791381</v>
+        <v>-88.60938244632121</v>
       </c>
       <c r="P90">
-        <v>-658.9116915353966</v>
+        <v>-620.2656771242484</v>
       </c>
       <c r="Q90">
-        <v>-648.8116915353966</v>
+        <v>-610.1656771242484</v>
       </c>
       <c r="R90">
         <v>7.333333333333334</v>
       </c>
       <c r="S90">
-        <v>0.519846653391052</v>
+        <v>0.5189038714035281</v>
       </c>
       <c r="T90">
-        <v>9.235736421961198</v>
+        <v>9.221675041427531</v>
       </c>
       <c r="U90">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V90">
-        <v>0.04033846778164783</v>
+        <v>0.04200716275796416</v>
       </c>
       <c r="W90">
-        <v>0.2415819472618314</v>
+        <v>0.2315819472618315</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8809,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3227077422531826</v>
+        <v>0.3360573020637132</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8716,13 +8820,13 @@
         <v>0.89</v>
       </c>
       <c r="B91">
-        <v>0.2770330781639632</v>
+        <v>0.2680199443254603</v>
       </c>
       <c r="C91">
-        <v>-2817.449887795292</v>
+        <v>-2767.762300175893</v>
       </c>
       <c r="D91">
-        <v>1253.127102584167</v>
+        <v>1302.814690203566</v>
       </c>
       <c r="E91">
         <v>4101.31407984074</v>
@@ -8749,37 +8853,37 @@
         <v>358.8</v>
       </c>
       <c r="M91">
-        <v>1124.476500605848</v>
+        <v>1079.807730702053</v>
       </c>
       <c r="N91">
-        <v>-765.6765006058481</v>
+        <v>-721.0077307020533</v>
       </c>
       <c r="O91">
-        <v>-95.70956257573101</v>
+        <v>-90.12596633775667</v>
       </c>
       <c r="P91">
-        <v>-669.966938030117</v>
+        <v>-630.8817643642967</v>
       </c>
       <c r="Q91">
-        <v>-659.866938030117</v>
+        <v>-620.7817643642967</v>
       </c>
       <c r="R91">
         <v>8.090909090909092</v>
       </c>
       <c r="S91">
-        <v>0.5629418036993293</v>
+        <v>0.5619133142583943</v>
       </c>
       <c r="T91">
-        <v>10.07534882395767</v>
+        <v>10.06000913610276</v>
       </c>
       <c r="U91">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V91">
-        <v>0.03988522657061808</v>
+        <v>0.04153517216517805</v>
       </c>
       <c r="W91">
-        <v>0.2416960446708281</v>
+        <v>0.2316960446708281</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8891,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3190818125649445</v>
+        <v>0.3322813773214244</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8798,13 +8902,13 @@
         <v>0.9</v>
       </c>
       <c r="B92">
-        <v>0.2790924443305886</v>
+        <v>0.2699793104920857</v>
       </c>
       <c r="C92">
-        <v>-2878.502478677547</v>
+        <v>-2829.124593533046</v>
       </c>
       <c r="D92">
-        <v>1242.2641408073</v>
+        <v>1291.6420259518</v>
       </c>
       <c r="E92">
         <v>4151.503708946128</v>
@@ -8831,37 +8935,37 @@
         <v>358.8</v>
       </c>
       <c r="M92">
-        <v>1137.111068028385</v>
+        <v>1091.940401833537</v>
       </c>
       <c r="N92">
-        <v>-778.3110680283855</v>
+        <v>-733.1404018335372</v>
       </c>
       <c r="O92">
-        <v>-97.28888350354819</v>
+        <v>-91.64255022919215</v>
       </c>
       <c r="P92">
-        <v>-681.0221845248374</v>
+        <v>-641.4978516043451</v>
       </c>
       <c r="Q92">
-        <v>-670.9221845248373</v>
+        <v>-631.3978516043451</v>
       </c>
       <c r="R92">
         <v>9.000000000000002</v>
       </c>
       <c r="S92">
-        <v>0.6146559840692625</v>
+        <v>0.6135246456842337</v>
       </c>
       <c r="T92">
-        <v>11.08288370635344</v>
+        <v>11.06601004971304</v>
       </c>
       <c r="U92">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V92">
-        <v>0.0394420573865001</v>
+        <v>0.04107367025223162</v>
       </c>
       <c r="W92">
-        <v>0.2418076065818471</v>
+        <v>0.231807606581847</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8973,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3155364590920008</v>
+        <v>0.3285893620178529</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8880,13 +8984,13 @@
         <v>0.91</v>
       </c>
       <c r="B93">
-        <v>0.2811518104972139</v>
+        <v>0.2719386766587111</v>
       </c>
       <c r="C93">
-        <v>-2939.368352999453</v>
+        <v>-2890.296887456705</v>
       </c>
       <c r="D93">
-        <v>1231.587895590781</v>
+        <v>1280.659361133529</v>
       </c>
       <c r="E93">
         <v>4201.693338051515</v>
@@ -8913,37 +9017,37 @@
         <v>358.8</v>
       </c>
       <c r="M93">
-        <v>1149.745635450923</v>
+        <v>1104.073072965021</v>
       </c>
       <c r="N93">
-        <v>-790.9456354509232</v>
+        <v>-745.2730729650209</v>
       </c>
       <c r="O93">
-        <v>-98.8682044313654</v>
+        <v>-93.15913412062761</v>
       </c>
       <c r="P93">
-        <v>-692.0774310195578</v>
+        <v>-652.1139388443933</v>
       </c>
       <c r="Q93">
-        <v>-681.9774310195578</v>
+        <v>-642.0139388443932</v>
       </c>
       <c r="R93">
         <v>10.11111111111111</v>
       </c>
       <c r="S93">
-        <v>0.6778622045214028</v>
+        <v>0.6766051618713709</v>
       </c>
       <c r="T93">
-        <v>12.3143152292816</v>
+        <v>12.29556672190338</v>
       </c>
       <c r="U93">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V93">
-        <v>0.03900862818445065</v>
+        <v>0.04062231123847084</v>
       </c>
       <c r="W93">
-        <v>0.2419167165827337</v>
+        <v>0.2319167165827337</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +9055,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3120690254756051</v>
+        <v>0.3249784899077667</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8962,13 +9066,13 @@
         <v>0.92</v>
       </c>
       <c r="B94">
-        <v>0.2832111766638393</v>
+        <v>0.2738980428253364</v>
       </c>
       <c r="C94">
-        <v>-3000.052283769703</v>
+        <v>-2951.283987705831</v>
       </c>
       <c r="D94">
-        <v>1221.093593925918</v>
+        <v>1269.86188998979</v>
       </c>
       <c r="E94">
         <v>4251.882967156902</v>
@@ -8995,37 +9099,37 @@
         <v>358.8</v>
       </c>
       <c r="M94">
-        <v>1162.380202873461</v>
+        <v>1116.205744096505</v>
       </c>
       <c r="N94">
-        <v>-803.5802028734608</v>
+        <v>-757.4057440965046</v>
       </c>
       <c r="O94">
-        <v>-100.4475253591826</v>
+        <v>-94.67571801206307</v>
       </c>
       <c r="P94">
-        <v>-703.1326775142783</v>
+        <v>-662.7300260844415</v>
       </c>
       <c r="Q94">
-        <v>-693.0326775142782</v>
+        <v>-652.6300260844415</v>
       </c>
       <c r="R94">
         <v>11.50000000000001</v>
       </c>
       <c r="S94">
-        <v>0.7568699800865784</v>
+        <v>0.7554558071052925</v>
       </c>
       <c r="T94">
-        <v>13.8536046329418</v>
+        <v>13.8325125621413</v>
       </c>
       <c r="U94">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V94">
-        <v>0.03858462135635879</v>
+        <v>0.04018076437718311</v>
       </c>
       <c r="W94">
-        <v>0.2420234546270794</v>
+        <v>0.2320234546270794</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9137,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3086769708508703</v>
+        <v>0.3214461150174649</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9044,13 +9148,13 @@
         <v>0.93</v>
       </c>
       <c r="B95">
-        <v>0.2852705428304646</v>
+        <v>0.2758574089919618</v>
       </c>
       <c r="C95">
-        <v>-3060.558882689169</v>
+        <v>-3012.090539321528</v>
       </c>
       <c r="D95">
-        <v>1210.77662411184</v>
+        <v>1259.24496747948</v>
       </c>
       <c r="E95">
         <v>4302.072596262289</v>
@@ -9077,37 +9181,37 @@
         <v>358.8</v>
       </c>
       <c r="M95">
-        <v>1175.014770295998</v>
+        <v>1128.338415227988</v>
       </c>
       <c r="N95">
-        <v>-816.2147702959985</v>
+        <v>-769.5384152279885</v>
       </c>
       <c r="O95">
-        <v>-102.0268462869998</v>
+        <v>-96.19230190349856</v>
       </c>
       <c r="P95">
-        <v>-714.1879240089987</v>
+        <v>-673.3461133244899</v>
       </c>
       <c r="Q95">
-        <v>-704.0879240089987</v>
+        <v>-663.2461133244899</v>
       </c>
       <c r="R95">
         <v>13.2857142857143</v>
       </c>
       <c r="S95">
-        <v>0.8584514058132324</v>
+        <v>0.8568352081203343</v>
       </c>
       <c r="T95">
-        <v>15.83269100907635</v>
+        <v>15.80858578530435</v>
       </c>
       <c r="U95">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V95">
-        <v>0.03816973295467752</v>
+        <v>0.03974871314732092</v>
       </c>
       <c r="W95">
-        <v>0.2421278972296112</v>
+        <v>0.2321278972296112</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9219,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.30535786363742</v>
+        <v>0.3179897051785674</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9126,13 +9230,13 @@
         <v>0.9400000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2873299089970899</v>
+        <v>0.277816775158587</v>
       </c>
       <c r="C96">
-        <v>-3120.892606908223</v>
+        <v>-3072.721033289899</v>
       </c>
       <c r="D96">
-        <v>1200.632528998172</v>
+        <v>1248.804102616496</v>
       </c>
       <c r="E96">
         <v>4352.262225367676</v>
@@ -9159,37 +9263,37 @@
         <v>358.8</v>
       </c>
       <c r="M96">
-        <v>1187.649337718536</v>
+        <v>1140.471086359472</v>
       </c>
       <c r="N96">
-        <v>-828.8493377185362</v>
+        <v>-781.6710863594722</v>
       </c>
       <c r="O96">
-        <v>-103.606167214817</v>
+        <v>-97.70888579493402</v>
       </c>
       <c r="P96">
-        <v>-725.2431705037192</v>
+        <v>-683.9622005645381</v>
       </c>
       <c r="Q96">
-        <v>-715.1431705037191</v>
+        <v>-673.8622005645381</v>
       </c>
       <c r="R96">
         <v>15.66666666666668</v>
       </c>
       <c r="S96">
-        <v>0.9938933067821046</v>
+        <v>0.9920077428070568</v>
       </c>
       <c r="T96">
-        <v>18.47147284392241</v>
+        <v>18.44335008285508</v>
       </c>
       <c r="U96">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V96">
-        <v>0.03776367196579796</v>
+        <v>0.03932585449681751</v>
       </c>
       <c r="W96">
-        <v>0.2422301176491103</v>
+        <v>0.2322301176491103</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9301,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3021093757263836</v>
+        <v>0.3146068359745401</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9208,13 +9312,13 @@
         <v>0.9500000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2893892751637153</v>
+        <v>0.2797761413252124</v>
       </c>
       <c r="C97">
-        <v>-3181.057765447206</v>
+        <v>-3133.179812876162</v>
       </c>
       <c r="D97">
-        <v>1190.656999564577</v>
+        <v>1238.534952135622</v>
       </c>
       <c r="E97">
         <v>4402.451854473064</v>
@@ -9241,37 +9345,37 @@
         <v>358.8</v>
       </c>
       <c r="M97">
-        <v>1200.283905141074</v>
+        <v>1152.603757490956</v>
       </c>
       <c r="N97">
-        <v>-841.483905141074</v>
+        <v>-793.8037574909561</v>
       </c>
       <c r="O97">
-        <v>-105.1854881426343</v>
+        <v>-99.22546968636951</v>
       </c>
       <c r="P97">
-        <v>-736.2984169984397</v>
+        <v>-694.5782878045866</v>
       </c>
       <c r="Q97">
-        <v>-726.1984169984397</v>
+        <v>-684.4782878045866</v>
       </c>
       <c r="R97">
         <v>19.00000000000003</v>
       </c>
       <c r="S97">
-        <v>1.183511968138526</v>
+        <v>1.181249291368469</v>
       </c>
       <c r="T97">
-        <v>22.16576741270691</v>
+        <v>22.1320200994261</v>
       </c>
       <c r="U97">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V97">
-        <v>0.03736615962931587</v>
+        <v>0.03891189813369311</v>
       </c>
       <c r="W97">
-        <v>0.242330186059778</v>
+        <v>0.232330186059778</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9383,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.298929277034527</v>
+        <v>0.3112951850695449</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9290,13 +9394,13 @@
         <v>0.96</v>
       </c>
       <c r="B98">
-        <v>0.2914486413303407</v>
+        <v>0.2817355074918377</v>
       </c>
       <c r="C98">
-        <v>-3241.05852529945</v>
+        <v>-3193.471079648788</v>
       </c>
       <c r="D98">
-        <v>1180.84586881772</v>
+        <v>1228.433314468382</v>
       </c>
       <c r="E98">
         <v>4452.641483578451</v>
@@ -9323,37 +9427,37 @@
         <v>358.8</v>
       </c>
       <c r="M98">
-        <v>1212.918472563611</v>
+        <v>1164.73642862244</v>
       </c>
       <c r="N98">
-        <v>-854.1184725636115</v>
+        <v>-805.9364286224397</v>
       </c>
       <c r="O98">
-        <v>-106.7648090704514</v>
+        <v>-100.742053577805</v>
       </c>
       <c r="P98">
-        <v>-747.3536634931601</v>
+        <v>-705.1943750446347</v>
       </c>
       <c r="Q98">
-        <v>-737.25366349316</v>
+        <v>-695.0943750446347</v>
       </c>
       <c r="R98">
         <v>23.99999999999998</v>
       </c>
       <c r="S98">
-        <v>1.467939960173155</v>
+        <v>1.465111614210583</v>
       </c>
       <c r="T98">
-        <v>27.70720926588357</v>
+        <v>27.66502512428257</v>
       </c>
       <c r="U98">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V98">
-        <v>0.03697692879984384</v>
+        <v>0.03850656586146715</v>
       </c>
       <c r="W98">
-        <v>0.24242816971189</v>
+        <v>0.23242816971189</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9465,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2958154303987507</v>
+        <v>0.3080525268917371</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9372,13 +9476,13 @@
         <v>0.97</v>
       </c>
       <c r="B99">
-        <v>0.293508007496966</v>
+        <v>0.2836948736584631</v>
       </c>
       <c r="C99">
-        <v>-3300.898917235043</v>
+        <v>-3253.598899211244</v>
       </c>
       <c r="D99">
-        <v>1171.195105987513</v>
+        <v>1218.495124011313</v>
       </c>
       <c r="E99">
         <v>4502.831112683838</v>
@@ -9405,37 +9509,37 @@
         <v>358.8</v>
       </c>
       <c r="M99">
-        <v>1225.553039986149</v>
+        <v>1176.869099753923</v>
       </c>
       <c r="N99">
-        <v>-866.7530399861489</v>
+        <v>-818.0690997539234</v>
       </c>
       <c r="O99">
-        <v>-108.3441299982686</v>
+        <v>-102.2586374692404</v>
       </c>
       <c r="P99">
-        <v>-758.4089099878803</v>
+        <v>-715.810462284683</v>
       </c>
       <c r="Q99">
-        <v>-748.3089099878803</v>
+        <v>-705.710462284683</v>
       </c>
       <c r="R99">
         <v>32.33333333333331</v>
       </c>
       <c r="S99">
-        <v>1.941986613564207</v>
+        <v>1.938215485614111</v>
       </c>
       <c r="T99">
-        <v>36.94294568784476</v>
+        <v>36.88670016571009</v>
       </c>
       <c r="U99">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V99">
-        <v>0.03659572334829906</v>
+        <v>0.03810959095567883</v>
       </c>
       <c r="W99">
-        <v>0.2425241330825152</v>
+        <v>0.2325241330825152</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9547,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2927657867863924</v>
+        <v>0.3048767276454306</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9454,13 +9558,13 @@
         <v>0.98</v>
       </c>
       <c r="B100">
-        <v>0.2955673736635913</v>
+        <v>0.2856542398250884</v>
       </c>
       <c r="C100">
-        <v>-3360.582841322297</v>
+        <v>-3313.567206657719</v>
       </c>
       <c r="D100">
-        <v>1161.700811005647</v>
+        <v>1208.716445670225</v>
       </c>
       <c r="E100">
         <v>4553.020741789225</v>
@@ -9487,37 +9591,37 @@
         <v>358.8</v>
       </c>
       <c r="M100">
-        <v>1238.187607408687</v>
+        <v>1189.001770885407</v>
       </c>
       <c r="N100">
-        <v>-879.3876074086866</v>
+        <v>-830.2017708854071</v>
       </c>
       <c r="O100">
-        <v>-109.9234509260858</v>
+        <v>-103.7752213606759</v>
       </c>
       <c r="P100">
-        <v>-769.4641564826007</v>
+        <v>-726.4265495247312</v>
       </c>
       <c r="Q100">
-        <v>-759.3641564826007</v>
+        <v>-716.3265495247311</v>
       </c>
       <c r="R100">
         <v>48.99999999999996</v>
       </c>
       <c r="S100">
-        <v>2.890079920346309</v>
+        <v>2.884423228421166</v>
       </c>
       <c r="T100">
-        <v>55.41441853176714</v>
+        <v>55.33005024856514</v>
       </c>
       <c r="U100">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V100">
-        <v>0.03622229759984703</v>
+        <v>0.03772071757858007</v>
       </c>
       <c r="W100">
-        <v>0.2426181380170052</v>
+        <v>0.2326181380170052</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,7 +9629,7 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2897783807987762</v>
+        <v>0.3017657406286405</v>
       </c>
       <c r="Z100">
         <v>0</v>
@@ -9536,13 +9640,13 @@
         <v>0.99</v>
       </c>
       <c r="B101">
-        <v>0.2976267398302167</v>
+        <v>0.2876136059917138</v>
       </c>
       <c r="C101">
-        <v>-3420.114072182816</v>
+        <v>-3373.379811768256</v>
       </c>
       <c r="D101">
-        <v>1152.359209250516</v>
+        <v>1199.093469665075</v>
       </c>
       <c r="E101">
         <v>4603.210370894612</v>
@@ -9569,37 +9673,37 @@
         <v>358.8</v>
       </c>
       <c r="M101">
-        <v>1250.822174831224</v>
+        <v>1201.134442016891</v>
       </c>
       <c r="N101">
-        <v>-892.0221748312242</v>
+        <v>-842.334442016891</v>
       </c>
       <c r="O101">
-        <v>-111.502771853903</v>
+        <v>-105.2918052521114</v>
       </c>
       <c r="P101">
-        <v>-780.5194029773212</v>
+        <v>-737.0426367647797</v>
       </c>
       <c r="Q101">
-        <v>-770.4194029773212</v>
+        <v>-726.9426367647796</v>
       </c>
       <c r="R101">
         <v>98.99999999999991</v>
       </c>
       <c r="S101">
-        <v>5.734359840692619</v>
+        <v>5.723046456842332</v>
       </c>
       <c r="T101">
-        <v>110.8288370635343</v>
+        <v>110.6601004971303</v>
       </c>
       <c r="U101">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V101">
-        <v>0.03585641580590918</v>
+        <v>0.03733970022930148</v>
       </c>
       <c r="W101">
-        <v>0.2427102438619095</v>
+        <v>0.2327102438619095</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
@@ -9607,7 +9711,7 @@
         </is>
       </c>
       <c r="Y101">
-        <v>0.2868513264472734</v>
+        <v>0.2987176018344118</v>
       </c>
       <c r="Z101">
         <v>0</v>

--- a/research/traditional_assets/database/data/ireland/ireland_drugs_biotechnology.xlsx
+++ b/research/traditional_assets/database/data/ireland/ireland_drugs_biotechnology.xlsx
@@ -1382,7 +1382,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1519,22 +1519,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1047516906403805</v>
+        <v>0.1047120714228772</v>
       </c>
       <c r="C2">
-        <v>5062.151926770843</v>
+        <v>5014.88682884293</v>
       </c>
       <c r="D2">
-        <v>4665.851926770843</v>
+        <v>4668.776457948317</v>
       </c>
       <c r="E2">
-        <v>-365.5629105387191</v>
+        <v>-315.373281433332</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>50.18962910538718</v>
       </c>
       <c r="G2">
         <v>396.3</v>
@@ -1555,28 +1555,28 @@
         <v>358.8</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>2.822494932434423</v>
       </c>
       <c r="N2">
-        <v>358.8</v>
+        <v>355.9775050675656</v>
       </c>
       <c r="O2">
-        <v>44.85</v>
+        <v>44.4971881334457</v>
       </c>
       <c r="P2">
-        <v>313.95</v>
+        <v>311.4803169341199</v>
       </c>
       <c r="Q2">
-        <v>324.05</v>
+        <v>321.5803169341199</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1047516906403805</v>
+        <v>0.1052727283101818</v>
       </c>
       <c r="T2">
-        <v>1.149078177305102</v>
+        <v>1.159234171296435</v>
       </c>
       <c r="U2">
         <v>0.0562366166625341</v>
@@ -1593,7 +1593,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>127.121574560466</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1601,22 +1601,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1047120714228772</v>
+        <v>0.1046724522053738</v>
       </c>
       <c r="C3">
-        <v>5014.88682884293</v>
+        <v>4967.625399375574</v>
       </c>
       <c r="D3">
-        <v>4668.776457948317</v>
+        <v>4671.704657586348</v>
       </c>
       <c r="E3">
-        <v>-315.373281433332</v>
+        <v>-265.1836523279447</v>
       </c>
       <c r="F3">
-        <v>50.18962910538718</v>
+        <v>100.3792582107744</v>
       </c>
       <c r="G3">
         <v>396.3</v>
@@ -1637,28 +1637,28 @@
         <v>358.8</v>
       </c>
       <c r="M3">
-        <v>2.822494932434423</v>
+        <v>5.644989864868847</v>
       </c>
       <c r="N3">
-        <v>355.9775050675656</v>
+        <v>353.1550101351312</v>
       </c>
       <c r="O3">
-        <v>44.4971881334457</v>
+        <v>44.1443762668914</v>
       </c>
       <c r="P3">
-        <v>311.4803169341199</v>
+        <v>309.0106338682398</v>
       </c>
       <c r="Q3">
-        <v>321.5803169341199</v>
+        <v>319.1106338682398</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1052727283101818</v>
+        <v>0.1058043994018158</v>
       </c>
       <c r="T3">
-        <v>1.159234171296435</v>
+        <v>1.169597430471265</v>
       </c>
       <c r="U3">
         <v>0.0562366166625341</v>
@@ -1675,7 +1675,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>127.121574560466</v>
+        <v>63.56078728023301</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1683,22 +1683,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1046724522053738</v>
+        <v>0.1046328329878706</v>
       </c>
       <c r="C4">
-        <v>4967.625399375574</v>
+        <v>4920.367645275541</v>
       </c>
       <c r="D4">
-        <v>4671.704657586348</v>
+        <v>4674.636532591702</v>
       </c>
       <c r="E4">
-        <v>-265.1836523279447</v>
+        <v>-214.9940232225576</v>
       </c>
       <c r="F4">
-        <v>100.3792582107744</v>
+        <v>150.5688873161616</v>
       </c>
       <c r="G4">
         <v>396.3</v>
@@ -1719,28 +1719,28 @@
         <v>358.8</v>
       </c>
       <c r="M4">
-        <v>5.644989864868847</v>
+        <v>8.467484797303269</v>
       </c>
       <c r="N4">
-        <v>353.1550101351312</v>
+        <v>350.3325152026968</v>
       </c>
       <c r="O4">
-        <v>44.1443762668914</v>
+        <v>43.79156440033709</v>
       </c>
       <c r="P4">
-        <v>309.0106338682398</v>
+        <v>306.5409508023596</v>
       </c>
       <c r="Q4">
-        <v>319.1106338682398</v>
+        <v>316.6409508023597</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1058043994018158</v>
+        <v>0.106347032783999</v>
       </c>
       <c r="T4">
-        <v>1.169597430471265</v>
+        <v>1.180174365092998</v>
       </c>
       <c r="U4">
         <v>0.0562366166625341</v>
@@ -1757,7 +1757,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>63.56078728023301</v>
+        <v>42.37385818682201</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1765,22 +1765,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1046328329878706</v>
+        <v>0.1045932137703673</v>
       </c>
       <c r="C5">
-        <v>4920.367645275541</v>
+        <v>4873.113573466957</v>
       </c>
       <c r="D5">
-        <v>4674.636532591702</v>
+        <v>4677.572089888506</v>
       </c>
       <c r="E5">
-        <v>-214.9940232225576</v>
+        <v>-164.8043941171704</v>
       </c>
       <c r="F5">
-        <v>150.5688873161616</v>
+        <v>200.7585164215487</v>
       </c>
       <c r="G5">
         <v>396.3</v>
@@ -1801,28 +1801,28 @@
         <v>358.8</v>
       </c>
       <c r="M5">
-        <v>8.467484797303269</v>
+        <v>11.28997972973769</v>
       </c>
       <c r="N5">
-        <v>350.3325152026968</v>
+        <v>347.5100202702623</v>
       </c>
       <c r="O5">
-        <v>43.79156440033709</v>
+        <v>43.43875253378279</v>
       </c>
       <c r="P5">
-        <v>306.5409508023596</v>
+        <v>304.0712677364795</v>
       </c>
       <c r="Q5">
-        <v>316.6409508023597</v>
+        <v>314.1712677364795</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.106347032783999</v>
+        <v>0.106900971028311</v>
       </c>
       <c r="T5">
-        <v>1.180174365092998</v>
+        <v>1.190971652519351</v>
       </c>
       <c r="U5">
         <v>0.0562366166625341</v>
@@ -1839,7 +1839,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>42.37385818682201</v>
+        <v>31.7803936401165</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1847,22 +1847,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1045932137703673</v>
+        <v>0.1045535945528639</v>
       </c>
       <c r="C6">
-        <v>4873.113573466957</v>
+        <v>4825.863190891351</v>
       </c>
       <c r="D6">
-        <v>4677.572089888506</v>
+        <v>4680.511336418287</v>
       </c>
       <c r="E6">
-        <v>-164.8043941171704</v>
+        <v>-114.6147650117832</v>
       </c>
       <c r="F6">
-        <v>200.7585164215487</v>
+        <v>250.9481455269359</v>
       </c>
       <c r="G6">
         <v>396.3</v>
@@ -1883,28 +1883,28 @@
         <v>358.8</v>
       </c>
       <c r="M6">
-        <v>11.28997972973769</v>
+        <v>14.11247466217212</v>
       </c>
       <c r="N6">
-        <v>347.5100202702623</v>
+        <v>344.6875253378279</v>
       </c>
       <c r="O6">
-        <v>43.43875253378279</v>
+        <v>43.08594066722848</v>
       </c>
       <c r="P6">
-        <v>304.0712677364795</v>
+        <v>301.6015846705994</v>
       </c>
       <c r="Q6">
-        <v>314.1712677364795</v>
+        <v>311.7015846705994</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.106900971028311</v>
+        <v>0.107466571130398</v>
       </c>
       <c r="T6">
-        <v>1.190971652519351</v>
+        <v>1.201996251259942</v>
       </c>
       <c r="U6">
         <v>0.0562366166625341</v>
@@ -1921,7 +1921,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>31.7803936401165</v>
+        <v>25.4243149120932</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1929,22 +1929,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1045535945528639</v>
+        <v>0.1045139753353607</v>
       </c>
       <c r="C7">
-        <v>4825.863190891351</v>
+        <v>4778.6165045077</v>
       </c>
       <c r="D7">
-        <v>4680.511336418287</v>
+        <v>4683.454279140024</v>
       </c>
       <c r="E7">
-        <v>-114.6147650117832</v>
+        <v>-64.42513590639595</v>
       </c>
       <c r="F7">
-        <v>250.9481455269359</v>
+        <v>301.1377746323232</v>
       </c>
       <c r="G7">
         <v>396.3</v>
@@ -1965,28 +1965,28 @@
         <v>358.8</v>
       </c>
       <c r="M7">
-        <v>14.11247466217212</v>
+        <v>16.93496959460654</v>
       </c>
       <c r="N7">
-        <v>344.6875253378279</v>
+        <v>341.8650304053934</v>
       </c>
       <c r="O7">
-        <v>43.08594066722848</v>
+        <v>42.73312880067418</v>
       </c>
       <c r="P7">
-        <v>301.6015846705994</v>
+        <v>299.1319016047192</v>
       </c>
       <c r="Q7">
-        <v>311.7015846705994</v>
+        <v>309.2319016047193</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.107466571130398</v>
+        <v>0.1080442052772102</v>
       </c>
       <c r="T7">
-        <v>1.201996251259942</v>
+        <v>1.213255415931185</v>
       </c>
       <c r="U7">
         <v>0.0562366166625341</v>
@@ -2003,7 +2003,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>25.4243149120932</v>
+        <v>21.186929093411</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2011,22 +2011,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1045139753353607</v>
+        <v>0.1044743561178574</v>
       </c>
       <c r="C8">
-        <v>4778.6165045077</v>
+        <v>4731.373521292508</v>
       </c>
       <c r="D8">
-        <v>4683.454279140024</v>
+        <v>4686.400925030218</v>
       </c>
       <c r="E8">
-        <v>-64.42513590639601</v>
+        <v>-14.23550680100885</v>
       </c>
       <c r="F8">
-        <v>301.1377746323231</v>
+        <v>351.3274037377103</v>
       </c>
       <c r="G8">
         <v>396.3</v>
@@ -2047,28 +2047,28 @@
         <v>358.8</v>
       </c>
       <c r="M8">
-        <v>16.93496959460654</v>
+        <v>19.75746452704096</v>
       </c>
       <c r="N8">
-        <v>341.8650304053935</v>
+        <v>339.0425354729591</v>
       </c>
       <c r="O8">
-        <v>42.73312880067419</v>
+        <v>42.38031693411988</v>
       </c>
       <c r="P8">
-        <v>299.1319016047193</v>
+        <v>296.6622185388392</v>
       </c>
       <c r="Q8">
-        <v>309.2319016047193</v>
+        <v>306.7622185388392</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1080442052772102</v>
+        <v>0.1086342616637389</v>
       </c>
       <c r="T8">
-        <v>1.213255415931185</v>
+        <v>1.224756713176003</v>
       </c>
       <c r="U8">
         <v>0.0562366166625341</v>
@@ -2085,7 +2085,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>21.186929093411</v>
+        <v>18.16022493720943</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2093,22 +2093,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1044743561178573</v>
+        <v>0.1044347369003541</v>
       </c>
       <c r="C9">
-        <v>4731.373521292508</v>
+        <v>4684.134248239835</v>
       </c>
       <c r="D9">
-        <v>4686.400925030219</v>
+        <v>4689.351281082932</v>
       </c>
       <c r="E9">
-        <v>-14.2355068010088</v>
+        <v>35.95412230437836</v>
       </c>
       <c r="F9">
-        <v>351.3274037377103</v>
+        <v>401.5170328430975</v>
       </c>
       <c r="G9">
         <v>396.3</v>
@@ -2129,28 +2129,28 @@
         <v>358.8</v>
       </c>
       <c r="M9">
-        <v>19.75746452704097</v>
+        <v>22.57995945947539</v>
       </c>
       <c r="N9">
-        <v>339.0425354729591</v>
+        <v>336.2200405405246</v>
       </c>
       <c r="O9">
-        <v>42.38031693411988</v>
+        <v>42.02750506756558</v>
       </c>
       <c r="P9">
-        <v>296.6622185388392</v>
+        <v>294.192535472959</v>
       </c>
       <c r="Q9">
-        <v>306.7622185388392</v>
+        <v>304.2925354729591</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1086342616637389</v>
+        <v>0.1092371453630181</v>
       </c>
       <c r="T9">
-        <v>1.224756713176003</v>
+        <v>1.236508038621795</v>
       </c>
       <c r="U9">
         <v>0.0562366166625341</v>
@@ -2167,7 +2167,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>18.16022493720943</v>
+        <v>15.89019682005825</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2175,22 +2175,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1044347369003541</v>
+        <v>0.1043951176828507</v>
       </c>
       <c r="C10">
-        <v>4684.134248239835</v>
+        <v>4636.898692361377</v>
       </c>
       <c r="D10">
-        <v>4689.351281082932</v>
+        <v>4692.305354309861</v>
       </c>
       <c r="E10">
-        <v>35.95412230437836</v>
+        <v>86.14375140976551</v>
       </c>
       <c r="F10">
-        <v>401.5170328430975</v>
+        <v>451.7066619484846</v>
       </c>
       <c r="G10">
         <v>396.3</v>
@@ -2211,28 +2211,28 @@
         <v>358.8</v>
       </c>
       <c r="M10">
-        <v>22.57995945947539</v>
+        <v>25.40245439190981</v>
       </c>
       <c r="N10">
-        <v>336.2200405405246</v>
+        <v>333.3975456080902</v>
       </c>
       <c r="O10">
-        <v>42.02750506756558</v>
+        <v>41.67469320101127</v>
       </c>
       <c r="P10">
-        <v>294.192535472959</v>
+        <v>291.7228524070789</v>
       </c>
       <c r="Q10">
-        <v>304.2925354729591</v>
+        <v>301.8228524070789</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1092371453630181</v>
+        <v>0.1098532792534903</v>
       </c>
       <c r="T10">
-        <v>1.236508038621795</v>
+        <v>1.248517634956505</v>
       </c>
       <c r="U10">
         <v>0.0562366166625341</v>
@@ -2249,7 +2249,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>15.89019682005825</v>
+        <v>14.12461939560733</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2257,22 +2257,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1043951176828507</v>
+        <v>0.1044867484653475</v>
       </c>
       <c r="C11">
-        <v>4636.898692361377</v>
+        <v>4579.882565160137</v>
       </c>
       <c r="D11">
-        <v>4692.305354309861</v>
+        <v>4685.478856214009</v>
       </c>
       <c r="E11">
-        <v>86.14375140976551</v>
+        <v>136.3333805151527</v>
       </c>
       <c r="F11">
-        <v>451.7066619484846</v>
+        <v>501.8962910538718</v>
       </c>
       <c r="G11">
         <v>396.3</v>
@@ -2293,45 +2293,45 @@
         <v>358.8</v>
       </c>
       <c r="M11">
-        <v>25.40245439190981</v>
+        <v>28.97779376092504</v>
       </c>
       <c r="N11">
-        <v>333.3975456080902</v>
+        <v>329.822206239075</v>
       </c>
       <c r="O11">
-        <v>41.67469320101127</v>
+        <v>41.22777577988438</v>
       </c>
       <c r="P11">
-        <v>291.7228524070789</v>
+        <v>288.5944304591906</v>
       </c>
       <c r="Q11">
-        <v>301.8228524070789</v>
+        <v>298.6944304591906</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1098532792534903</v>
+        <v>0.1104831050081952</v>
       </c>
       <c r="T11">
-        <v>1.248517634956505</v>
+        <v>1.260794111209765</v>
       </c>
       <c r="U11">
-        <v>0.0562366166625341</v>
+        <v>0.05773661666253409</v>
       </c>
       <c r="V11">
         <v>0.125</v>
       </c>
       <c r="W11">
-        <v>0.04920703957971734</v>
+        <v>0.05051953957971733</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y11">
-        <v>14.12461939560733</v>
+        <v>12.38189501106265</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2339,22 +2339,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1044867484653475</v>
+        <v>0.1044602542478442</v>
       </c>
       <c r="C12">
-        <v>4579.882565160137</v>
+        <v>4531.664714506335</v>
       </c>
       <c r="D12">
-        <v>4685.478856214009</v>
+        <v>4687.450634665594</v>
       </c>
       <c r="E12">
-        <v>136.3333805151528</v>
+        <v>186.5230096205399</v>
       </c>
       <c r="F12">
-        <v>501.8962910538719</v>
+        <v>552.085920159259</v>
       </c>
       <c r="G12">
         <v>396.3</v>
@@ -2375,28 +2375,28 @@
         <v>358.8</v>
       </c>
       <c r="M12">
-        <v>28.97779376092504</v>
+        <v>31.87557313701754</v>
       </c>
       <c r="N12">
-        <v>329.8222062390749</v>
+        <v>326.9244268629825</v>
       </c>
       <c r="O12">
-        <v>41.22777577988437</v>
+        <v>40.86555335787281</v>
       </c>
       <c r="P12">
-        <v>288.5944304591906</v>
+        <v>286.0588735051097</v>
       </c>
       <c r="Q12">
-        <v>298.6944304591906</v>
+        <v>296.1588735051097</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1104831050081952</v>
+        <v>0.1111270841506463</v>
       </c>
       <c r="T12">
-        <v>1.260794111209765</v>
+        <v>1.273346463333884</v>
       </c>
       <c r="U12">
         <v>0.05773661666253409</v>
@@ -2413,7 +2413,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>12.38189501106264</v>
+        <v>11.25626819187513</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2421,22 +2421,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1044602542478442</v>
+        <v>0.1044337600303408</v>
       </c>
       <c r="C13">
-        <v>4531.664714506335</v>
+        <v>4483.44852410849</v>
       </c>
       <c r="D13">
-        <v>4687.450634665594</v>
+        <v>4689.424073373137</v>
       </c>
       <c r="E13">
-        <v>186.5230096205399</v>
+        <v>236.7126387259271</v>
       </c>
       <c r="F13">
-        <v>552.085920159259</v>
+        <v>602.2755492646462</v>
       </c>
       <c r="G13">
         <v>396.3</v>
@@ -2457,28 +2457,28 @@
         <v>358.8</v>
       </c>
       <c r="M13">
-        <v>31.87557313701754</v>
+        <v>34.77335251311005</v>
       </c>
       <c r="N13">
-        <v>326.9244268629825</v>
+        <v>324.0266474868899</v>
       </c>
       <c r="O13">
-        <v>40.86555335787281</v>
+        <v>40.50333093586124</v>
       </c>
       <c r="P13">
-        <v>286.0588735051097</v>
+        <v>283.5233165510287</v>
       </c>
       <c r="Q13">
-        <v>296.1588735051097</v>
+        <v>293.6233165510287</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1111270841506463</v>
+        <v>0.1117856991826986</v>
       </c>
       <c r="T13">
-        <v>1.273346463333884</v>
+        <v>1.286184096188097</v>
       </c>
       <c r="U13">
         <v>0.05773661666253409</v>
@@ -2495,7 +2495,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>11.25626819187513</v>
+        <v>10.31824584255221</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2503,22 +2503,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1044337600303408</v>
+        <v>0.1046006408128375</v>
       </c>
       <c r="C14">
-        <v>4483.44852410849</v>
+        <v>4420.85632941165</v>
       </c>
       <c r="D14">
-        <v>4689.424073373137</v>
+        <v>4677.021507781684</v>
       </c>
       <c r="E14">
-        <v>236.7126387259271</v>
+        <v>286.9022678313143</v>
       </c>
       <c r="F14">
-        <v>602.2755492646462</v>
+        <v>652.4651783700334</v>
       </c>
       <c r="G14">
         <v>396.3</v>
@@ -2539,45 +2539,45 @@
         <v>358.8</v>
       </c>
       <c r="M14">
-        <v>34.77335251311005</v>
+        <v>38.78032269243161</v>
       </c>
       <c r="N14">
-        <v>324.0266474868899</v>
+        <v>320.0196773075684</v>
       </c>
       <c r="O14">
-        <v>40.50333093586124</v>
+        <v>40.00245966344605</v>
       </c>
       <c r="P14">
-        <v>283.5233165510287</v>
+        <v>280.0172176441223</v>
       </c>
       <c r="Q14">
-        <v>293.6233165510287</v>
+        <v>290.1172176441223</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1117856991826986</v>
+        <v>0.1124594547902003</v>
       </c>
       <c r="T14">
-        <v>1.286184096188097</v>
+        <v>1.299316847038959</v>
       </c>
       <c r="U14">
-        <v>0.05773661666253409</v>
+        <v>0.05943661666253409</v>
       </c>
       <c r="V14">
         <v>0.125</v>
       </c>
       <c r="W14">
-        <v>0.05051953957971733</v>
+        <v>0.05200703957971733</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y14">
-        <v>10.31824584255221</v>
+        <v>9.252114863655418</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2585,22 +2585,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1046006408128375</v>
+        <v>0.1045890215953342</v>
       </c>
       <c r="C15">
-        <v>4420.85632941165</v>
+        <v>4371.52811430664</v>
       </c>
       <c r="D15">
-        <v>4677.021507781684</v>
+        <v>4677.88292178206</v>
       </c>
       <c r="E15">
-        <v>286.9022678313143</v>
+        <v>337.0918969367015</v>
       </c>
       <c r="F15">
-        <v>652.4651783700334</v>
+        <v>702.6548074754206</v>
       </c>
       <c r="G15">
         <v>396.3</v>
@@ -2621,28 +2621,28 @@
         <v>358.8</v>
       </c>
       <c r="M15">
-        <v>38.78032269243161</v>
+        <v>41.76342443800327</v>
       </c>
       <c r="N15">
-        <v>320.0196773075684</v>
+        <v>317.0365755619968</v>
       </c>
       <c r="O15">
-        <v>40.00245966344605</v>
+        <v>39.62957194524959</v>
       </c>
       <c r="P15">
-        <v>280.0172176441223</v>
+        <v>277.4070036167471</v>
       </c>
       <c r="Q15">
-        <v>290.1172176441223</v>
+        <v>287.5070036167472</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1124594547902003</v>
+        <v>0.1131488791327602</v>
       </c>
       <c r="T15">
-        <v>1.299316847038959</v>
+        <v>1.312755010700306</v>
       </c>
       <c r="U15">
         <v>0.05943661666253409</v>
@@ -2659,7 +2659,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>9.252114863655418</v>
+        <v>8.591249516251461</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2667,22 +2667,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1045890215953342</v>
+        <v>0.1045774023778309</v>
       </c>
       <c r="C16">
-        <v>4371.52811430664</v>
+        <v>4322.200216570603</v>
       </c>
       <c r="D16">
-        <v>4677.88292178206</v>
+        <v>4678.744653151411</v>
       </c>
       <c r="E16">
-        <v>337.0918969367015</v>
+        <v>387.2815260420887</v>
       </c>
       <c r="F16">
-        <v>702.6548074754206</v>
+        <v>752.8444365808078</v>
       </c>
       <c r="G16">
         <v>396.3</v>
@@ -2703,28 +2703,28 @@
         <v>358.8</v>
       </c>
       <c r="M16">
-        <v>41.76342443800327</v>
+        <v>44.74652618357494</v>
       </c>
       <c r="N16">
-        <v>317.0365755619968</v>
+        <v>314.0534738164251</v>
       </c>
       <c r="O16">
-        <v>39.62957194524959</v>
+        <v>39.25668422705314</v>
       </c>
       <c r="P16">
-        <v>277.4070036167471</v>
+        <v>274.7967895893719</v>
       </c>
       <c r="Q16">
-        <v>287.5070036167472</v>
+        <v>284.896789589372</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1131488791327602</v>
+        <v>0.1138545252245569</v>
       </c>
       <c r="T16">
-        <v>1.312755010700306</v>
+        <v>1.326509366447802</v>
       </c>
       <c r="U16">
         <v>0.05943661666253409</v>
@@ -2741,7 +2741,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>8.591249516251461</v>
+        <v>8.018499548501364</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2749,22 +2749,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1045774023778309</v>
+        <v>0.1046777831603276</v>
       </c>
       <c r="C17">
-        <v>4322.200216570605</v>
+        <v>4264.576374806882</v>
       </c>
       <c r="D17">
-        <v>4678.744653151413</v>
+        <v>4671.310440493076</v>
       </c>
       <c r="E17">
-        <v>387.2815260420886</v>
+        <v>437.4711551474758</v>
       </c>
       <c r="F17">
-        <v>752.8444365808077</v>
+        <v>803.0340656861949</v>
       </c>
       <c r="G17">
         <v>396.3</v>
@@ -2785,45 +2785,45 @@
         <v>358.8</v>
       </c>
       <c r="M17">
-        <v>44.74652618357493</v>
+        <v>48.37205518169555</v>
       </c>
       <c r="N17">
-        <v>314.0534738164251</v>
+        <v>310.4279448183045</v>
       </c>
       <c r="O17">
-        <v>39.25668422705314</v>
+        <v>38.80349310228806</v>
       </c>
       <c r="P17">
-        <v>274.7967895893719</v>
+        <v>271.6244517160164</v>
       </c>
       <c r="Q17">
-        <v>284.896789589372</v>
+        <v>281.7244517160165</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1138545252245569</v>
+        <v>0.1145769724137772</v>
       </c>
       <c r="T17">
-        <v>1.326509366447802</v>
+        <v>1.340591206855953</v>
       </c>
       <c r="U17">
-        <v>0.05943661666253409</v>
+        <v>0.0602366166625341</v>
       </c>
       <c r="V17">
         <v>0.125</v>
       </c>
       <c r="W17">
-        <v>0.05200703957971733</v>
+        <v>0.05270703957971733</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y17">
-        <v>8.018499548501364</v>
+        <v>7.417505802725814</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2831,22 +2831,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1046777831603276</v>
+        <v>0.1046731639428243</v>
       </c>
       <c r="C18">
-        <v>4264.576374806882</v>
+        <v>4214.728326899663</v>
       </c>
       <c r="D18">
-        <v>4671.310440493076</v>
+        <v>4671.652021691245</v>
       </c>
       <c r="E18">
-        <v>437.4711551474758</v>
+        <v>487.660784252863</v>
       </c>
       <c r="F18">
-        <v>803.0340656861949</v>
+        <v>853.2236947915821</v>
       </c>
       <c r="G18">
         <v>396.3</v>
@@ -2867,28 +2867,28 @@
         <v>358.8</v>
       </c>
       <c r="M18">
-        <v>48.37205518169555</v>
+        <v>51.39530863055153</v>
       </c>
       <c r="N18">
-        <v>310.4279448183045</v>
+        <v>307.4046913694485</v>
       </c>
       <c r="O18">
-        <v>38.80349310228806</v>
+        <v>38.42558642118106</v>
       </c>
       <c r="P18">
-        <v>271.6244517160164</v>
+        <v>268.9791049482674</v>
       </c>
       <c r="Q18">
-        <v>281.7244517160165</v>
+        <v>279.0791049482675</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1145769724137772</v>
+        <v>0.1153168279690029</v>
       </c>
       <c r="T18">
-        <v>1.340591206855953</v>
+        <v>1.355012368719722</v>
       </c>
       <c r="U18">
         <v>0.0602366166625341</v>
@@ -2905,7 +2905,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>7.417505802725814</v>
+        <v>6.981181931977236</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2913,22 +2913,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1046731639428243</v>
+        <v>0.104668544725321</v>
       </c>
       <c r="C19">
-        <v>4214.728326899663</v>
+        <v>4164.880328951122</v>
       </c>
       <c r="D19">
-        <v>4671.652021691245</v>
+        <v>4671.993652848092</v>
       </c>
       <c r="E19">
-        <v>487.660784252863</v>
+        <v>537.8504133582503</v>
       </c>
       <c r="F19">
-        <v>853.2236947915821</v>
+        <v>903.4133238969695</v>
       </c>
       <c r="G19">
         <v>396.3</v>
@@ -2949,28 +2949,28 @@
         <v>358.8</v>
       </c>
       <c r="M19">
-        <v>51.39530863055153</v>
+        <v>54.41856207940751</v>
       </c>
       <c r="N19">
-        <v>307.4046913694485</v>
+        <v>304.3814379205925</v>
       </c>
       <c r="O19">
-        <v>38.42558642118106</v>
+        <v>38.04767974007406</v>
       </c>
       <c r="P19">
-        <v>268.9791049482674</v>
+        <v>266.3337581805184</v>
       </c>
       <c r="Q19">
-        <v>279.0791049482675</v>
+        <v>276.4337581805185</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1153168279690029</v>
+        <v>0.116074728781673</v>
       </c>
       <c r="T19">
-        <v>1.355012368719722</v>
+        <v>1.369785266238704</v>
       </c>
       <c r="U19">
         <v>0.0602366166625341</v>
@@ -2987,7 +2987,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>6.981181931977236</v>
+        <v>6.593338491311832</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2995,22 +2995,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.104668544725321</v>
+        <v>0.1046639255078177</v>
       </c>
       <c r="C20">
-        <v>4164.880328951122</v>
+        <v>4115.032380972219</v>
       </c>
       <c r="D20">
-        <v>4671.993652848091</v>
+        <v>4672.335333974575</v>
       </c>
       <c r="E20">
-        <v>537.8504133582501</v>
+        <v>588.0400424636375</v>
       </c>
       <c r="F20">
-        <v>903.4133238969692</v>
+        <v>953.6029530023566</v>
       </c>
       <c r="G20">
         <v>396.3</v>
@@ -3031,28 +3031,28 @@
         <v>358.8</v>
       </c>
       <c r="M20">
-        <v>54.41856207940749</v>
+        <v>57.44181552826347</v>
       </c>
       <c r="N20">
-        <v>304.3814379205925</v>
+        <v>301.3581844717365</v>
       </c>
       <c r="O20">
-        <v>38.04767974007407</v>
+        <v>37.66977305896707</v>
       </c>
       <c r="P20">
-        <v>266.3337581805185</v>
+        <v>263.6884114127695</v>
       </c>
       <c r="Q20">
-        <v>276.4337581805185</v>
+        <v>273.7884114127695</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.116074728781673</v>
+        <v>0.1168513431946561</v>
       </c>
       <c r="T20">
-        <v>1.369785266238704</v>
+        <v>1.38492292665939</v>
       </c>
       <c r="U20">
         <v>0.0602366166625341</v>
@@ -3069,7 +3069,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>6.593338491311835</v>
+        <v>6.246320675979632</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3077,22 +3077,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1046639255078177</v>
+        <v>0.1048343062903144</v>
       </c>
       <c r="C21">
-        <v>4115.032380972219</v>
+        <v>4052.272760211982</v>
       </c>
       <c r="D21">
-        <v>4672.335333974575</v>
+        <v>4659.765342319725</v>
       </c>
       <c r="E21">
-        <v>588.0400424636375</v>
+        <v>638.2296715690247</v>
       </c>
       <c r="F21">
-        <v>953.6029530023566</v>
+        <v>1003.792582107744</v>
       </c>
       <c r="G21">
         <v>396.3</v>
@@ -3113,45 +3113,45 @@
         <v>358.8</v>
       </c>
       <c r="M21">
-        <v>57.44181552826347</v>
+        <v>61.46886155922719</v>
       </c>
       <c r="N21">
-        <v>301.3581844717365</v>
+        <v>297.3311384407728</v>
       </c>
       <c r="O21">
-        <v>37.66977305896707</v>
+        <v>37.1663923050966</v>
       </c>
       <c r="P21">
-        <v>263.6884114127695</v>
+        <v>260.1647461356762</v>
       </c>
       <c r="Q21">
-        <v>273.7884114127695</v>
+        <v>270.2647461356762</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1168513431946561</v>
+        <v>0.1176473729679637</v>
       </c>
       <c r="T21">
-        <v>1.38492292665939</v>
+        <v>1.400439028590593</v>
       </c>
       <c r="U21">
-        <v>0.0602366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V21">
         <v>0.125</v>
       </c>
       <c r="W21">
-        <v>0.05270703957971733</v>
+        <v>0.05358203957971733</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y21">
-        <v>6.246320675979632</v>
+        <v>5.837101760121015</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3159,22 +3159,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1048343062903144</v>
+        <v>0.1048384370728111</v>
       </c>
       <c r="C22">
-        <v>4052.272760211982</v>
+        <v>4001.779218702868</v>
       </c>
       <c r="D22">
-        <v>4659.765342319725</v>
+        <v>4659.461429915998</v>
       </c>
       <c r="E22">
-        <v>638.2296715690247</v>
+        <v>688.4193006744119</v>
       </c>
       <c r="F22">
-        <v>1003.792582107744</v>
+        <v>1053.982211213131</v>
       </c>
       <c r="G22">
         <v>396.3</v>
@@ -3195,28 +3195,28 @@
         <v>358.8</v>
       </c>
       <c r="M22">
-        <v>61.46886155922719</v>
+        <v>64.54230463718855</v>
       </c>
       <c r="N22">
-        <v>297.3311384407728</v>
+        <v>294.2576953628114</v>
       </c>
       <c r="O22">
-        <v>37.1663923050966</v>
+        <v>36.78221192035143</v>
       </c>
       <c r="P22">
-        <v>260.1647461356762</v>
+        <v>257.47548344246</v>
       </c>
       <c r="Q22">
-        <v>270.2647461356762</v>
+        <v>267.57548344246</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1176473729679637</v>
+        <v>0.1184635553937601</v>
       </c>
       <c r="T22">
-        <v>1.400439028590593</v>
+        <v>1.416347943228916</v>
       </c>
       <c r="U22">
         <v>0.0612366166625341</v>
@@ -3233,7 +3233,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>5.837101760121015</v>
+        <v>5.559144533448585</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3241,22 +3241,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1048384370728111</v>
+        <v>0.1048425678553078</v>
       </c>
       <c r="C23">
-        <v>4001.779218702868</v>
+        <v>3951.285716833831</v>
       </c>
       <c r="D23">
-        <v>4659.461429915998</v>
+        <v>4659.157557152348</v>
       </c>
       <c r="E23">
-        <v>688.4193006744117</v>
+        <v>738.6089297797989</v>
       </c>
       <c r="F23">
-        <v>1053.982211213131</v>
+        <v>1104.171840318518</v>
       </c>
       <c r="G23">
         <v>396.3</v>
@@ -3277,28 +3277,28 @@
         <v>358.8</v>
       </c>
       <c r="M23">
-        <v>64.54230463718854</v>
+        <v>67.61574771514989</v>
       </c>
       <c r="N23">
-        <v>294.2576953628115</v>
+        <v>291.1842522848501</v>
       </c>
       <c r="O23">
-        <v>36.78221192035144</v>
+        <v>36.39803153560626</v>
       </c>
       <c r="P23">
-        <v>257.4754834424601</v>
+        <v>254.7862207492439</v>
       </c>
       <c r="Q23">
-        <v>267.5754834424601</v>
+        <v>264.8862207492439</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1184635553937601</v>
+        <v>0.1193006655740641</v>
       </c>
       <c r="T23">
-        <v>1.416347943228915</v>
+        <v>1.4326647787554</v>
       </c>
       <c r="U23">
         <v>0.0612366166625341</v>
@@ -3315,7 +3315,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>5.559144533448587</v>
+        <v>5.30645614556456</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3323,22 +3323,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1048425678553078</v>
+        <v>0.1048466986378045</v>
       </c>
       <c r="C24">
-        <v>3951.285716833831</v>
+        <v>3900.792254597114</v>
       </c>
       <c r="D24">
-        <v>4659.157557152348</v>
+        <v>4658.853724021019</v>
       </c>
       <c r="E24">
-        <v>738.6089297797989</v>
+        <v>788.7985588851861</v>
       </c>
       <c r="F24">
-        <v>1104.171840318518</v>
+        <v>1154.361469423905</v>
       </c>
       <c r="G24">
         <v>396.3</v>
@@ -3359,28 +3359,28 @@
         <v>358.8</v>
       </c>
       <c r="M24">
-        <v>67.61574771514989</v>
+        <v>70.68919079311125</v>
       </c>
       <c r="N24">
-        <v>291.1842522848501</v>
+        <v>288.1108092068887</v>
       </c>
       <c r="O24">
-        <v>36.39803153560626</v>
+        <v>36.01385115086109</v>
       </c>
       <c r="P24">
-        <v>254.7862207492439</v>
+        <v>252.0969580560277</v>
       </c>
       <c r="Q24">
-        <v>264.8862207492439</v>
+        <v>262.1969580560277</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1193006655740641</v>
+        <v>0.1201595188759345</v>
       </c>
       <c r="T24">
-        <v>1.4326647787554</v>
+        <v>1.449405428191663</v>
       </c>
       <c r="U24">
         <v>0.0612366166625341</v>
@@ -3397,7 +3397,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>5.30645614556456</v>
+        <v>5.075740660974796</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3405,22 +3405,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1048466986378045</v>
+        <v>0.1048508294203012</v>
       </c>
       <c r="C25">
-        <v>3900.792254597114</v>
+        <v>3850.298831984964</v>
       </c>
       <c r="D25">
-        <v>4658.853724021019</v>
+        <v>4658.549930514257</v>
       </c>
       <c r="E25">
-        <v>788.7985588851861</v>
+        <v>838.9881879905736</v>
       </c>
       <c r="F25">
-        <v>1154.361469423905</v>
+        <v>1204.551098529293</v>
       </c>
       <c r="G25">
         <v>396.3</v>
@@ -3441,28 +3441,28 @@
         <v>358.8</v>
       </c>
       <c r="M25">
-        <v>70.68919079311125</v>
+        <v>73.76263387107264</v>
       </c>
       <c r="N25">
-        <v>288.1108092068887</v>
+        <v>285.0373661289274</v>
       </c>
       <c r="O25">
-        <v>36.01385115086109</v>
+        <v>35.62967076611592</v>
       </c>
       <c r="P25">
-        <v>252.0969580560277</v>
+        <v>249.4076953628115</v>
       </c>
       <c r="Q25">
-        <v>262.1969580560277</v>
+        <v>259.5076953628115</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1201595188759345</v>
+        <v>0.1210409735804856</v>
       </c>
       <c r="T25">
-        <v>1.449405428191663</v>
+        <v>1.466586621034144</v>
       </c>
       <c r="U25">
         <v>0.0612366166625341</v>
@@ -3479,7 +3479,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>5.075740660974796</v>
+        <v>4.864251466767511</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3487,22 +3487,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1048508294203012</v>
+        <v>0.1048549602027979</v>
       </c>
       <c r="C26">
-        <v>3850.298831984966</v>
+        <v>3799.805448989633</v>
       </c>
       <c r="D26">
-        <v>4658.549930514258</v>
+        <v>4658.246176624312</v>
       </c>
       <c r="E26">
-        <v>838.9881879905734</v>
+        <v>889.1778170959606</v>
       </c>
       <c r="F26">
-        <v>1204.551098529292</v>
+        <v>1254.74072763468</v>
       </c>
       <c r="G26">
         <v>396.3</v>
@@ -3523,28 +3523,28 @@
         <v>358.8</v>
       </c>
       <c r="M26">
-        <v>73.76263387107262</v>
+        <v>76.83607694903398</v>
       </c>
       <c r="N26">
-        <v>285.0373661289274</v>
+        <v>281.9639230509661</v>
       </c>
       <c r="O26">
-        <v>35.62967076611592</v>
+        <v>35.24549038137076</v>
       </c>
       <c r="P26">
-        <v>249.4076953628115</v>
+        <v>246.7184326695953</v>
       </c>
       <c r="Q26">
-        <v>259.5076953628115</v>
+        <v>256.8184326695953</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1210409735804856</v>
+        <v>0.1219459337438248</v>
       </c>
       <c r="T26">
-        <v>1.466586621034143</v>
+        <v>1.48422597901909</v>
       </c>
       <c r="U26">
         <v>0.0612366166625341</v>
@@ -3561,7 +3561,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>4.864251466767513</v>
+        <v>4.669681408096812</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3569,22 +3569,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1048549602027979</v>
+        <v>0.1054278409852946</v>
       </c>
       <c r="C27">
-        <v>3799.805448989633</v>
+        <v>3707.869723933817</v>
       </c>
       <c r="D27">
-        <v>4658.246176624312</v>
+        <v>4616.500080673884</v>
       </c>
       <c r="E27">
-        <v>889.1778170959606</v>
+        <v>939.3674462013478</v>
       </c>
       <c r="F27">
-        <v>1254.74072763468</v>
+        <v>1304.930356740067</v>
       </c>
       <c r="G27">
         <v>396.3</v>
@@ -3605,45 +3605,45 @@
         <v>358.8</v>
       </c>
       <c r="M27">
-        <v>76.83607694903398</v>
+        <v>83.17184591884551</v>
       </c>
       <c r="N27">
-        <v>281.9639230509661</v>
+        <v>275.6281540811545</v>
       </c>
       <c r="O27">
-        <v>35.24549038137076</v>
+        <v>34.45351926014431</v>
       </c>
       <c r="P27">
-        <v>246.7184326695953</v>
+        <v>241.1746348210102</v>
       </c>
       <c r="Q27">
-        <v>256.8184326695953</v>
+        <v>251.2746348210102</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1219459337438248</v>
+        <v>0.1228753522899569</v>
       </c>
       <c r="T27">
-        <v>1.48422597901909</v>
+        <v>1.502342076409036</v>
       </c>
       <c r="U27">
-        <v>0.0612366166625341</v>
+        <v>0.06373661666253409</v>
       </c>
       <c r="V27">
         <v>0.125</v>
       </c>
       <c r="W27">
-        <v>0.05358203957971733</v>
+        <v>0.05576953957971733</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y27">
-        <v>4.669681408096812</v>
+        <v>4.313959802576671</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3651,22 +3651,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1054278409852946</v>
+        <v>0.1054538467677913</v>
       </c>
       <c r="C28">
-        <v>3707.869723933817</v>
+        <v>3655.802787792491</v>
       </c>
       <c r="D28">
-        <v>4616.500080673884</v>
+        <v>4614.622773637945</v>
       </c>
       <c r="E28">
-        <v>939.3674462013478</v>
+        <v>989.557075306735</v>
       </c>
       <c r="F28">
-        <v>1304.930356740067</v>
+        <v>1355.119985845454</v>
       </c>
       <c r="G28">
         <v>396.3</v>
@@ -3687,28 +3687,28 @@
         <v>358.8</v>
       </c>
       <c r="M28">
-        <v>83.17184591884551</v>
+        <v>86.37076306957033</v>
       </c>
       <c r="N28">
-        <v>275.6281540811545</v>
+        <v>272.4292369304297</v>
       </c>
       <c r="O28">
-        <v>34.45351926014431</v>
+        <v>34.05365461630371</v>
       </c>
       <c r="P28">
-        <v>241.1746348210102</v>
+        <v>238.375582314126</v>
       </c>
       <c r="Q28">
-        <v>251.2746348210102</v>
+        <v>248.475582314126</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1228753522899569</v>
+        <v>0.1238302343579009</v>
       </c>
       <c r="T28">
-        <v>1.502342076409036</v>
+        <v>1.520954505234322</v>
       </c>
       <c r="U28">
         <v>0.06373661666253409</v>
@@ -3725,7 +3725,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>4.313959802576671</v>
+        <v>4.154183513592349</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3733,22 +3733,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1054538467677913</v>
+        <v>0.105479852550288</v>
       </c>
       <c r="C29">
-        <v>3655.802787792491</v>
+        <v>3603.737377850267</v>
       </c>
       <c r="D29">
-        <v>4614.622773637945</v>
+        <v>4612.746992801108</v>
       </c>
       <c r="E29">
-        <v>989.557075306735</v>
+        <v>1039.746704412122</v>
       </c>
       <c r="F29">
-        <v>1355.119985845454</v>
+        <v>1405.309614950841</v>
       </c>
       <c r="G29">
         <v>396.3</v>
@@ -3769,28 +3769,28 @@
         <v>358.8</v>
       </c>
       <c r="M29">
-        <v>86.37076306957033</v>
+        <v>89.56968022029515</v>
       </c>
       <c r="N29">
-        <v>272.4292369304297</v>
+        <v>269.2303197797049</v>
       </c>
       <c r="O29">
-        <v>34.05365461630371</v>
+        <v>33.65378997246311</v>
       </c>
       <c r="P29">
-        <v>238.375582314126</v>
+        <v>235.5765298072418</v>
       </c>
       <c r="Q29">
-        <v>248.475582314126</v>
+        <v>245.6765298072418</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1238302343579009</v>
+        <v>0.1248116409277321</v>
       </c>
       <c r="T29">
-        <v>1.520954505234322</v>
+        <v>1.540083945971422</v>
       </c>
       <c r="U29">
         <v>0.06373661666253409</v>
@@ -3807,7 +3807,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>4.154183513592349</v>
+        <v>4.005819816678337</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3815,22 +3815,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.105479852550288</v>
+        <v>0.1063939833327847</v>
       </c>
       <c r="C30">
-        <v>3603.737377850267</v>
+        <v>3488.567336337823</v>
       </c>
       <c r="D30">
-        <v>4612.746992801108</v>
+        <v>4547.766580394051</v>
       </c>
       <c r="E30">
-        <v>1039.746704412122</v>
+        <v>1089.936333517509</v>
       </c>
       <c r="F30">
-        <v>1405.309614950841</v>
+        <v>1455.499244056228</v>
       </c>
       <c r="G30">
         <v>396.3</v>
@@ -3851,45 +3851,45 @@
         <v>358.8</v>
       </c>
       <c r="M30">
-        <v>89.56968022029515</v>
+        <v>97.86284472521679</v>
       </c>
       <c r="N30">
-        <v>269.2303197797049</v>
+        <v>260.9371552747832</v>
       </c>
       <c r="O30">
-        <v>33.65378997246311</v>
+        <v>32.6171444093479</v>
       </c>
       <c r="P30">
-        <v>235.5765298072418</v>
+        <v>228.3200108654353</v>
       </c>
       <c r="Q30">
-        <v>245.6765298072418</v>
+        <v>238.4200108654353</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1248116409277321</v>
+        <v>0.1258206927530517</v>
       </c>
       <c r="T30">
-        <v>1.540083945971422</v>
+        <v>1.559752244194074</v>
       </c>
       <c r="U30">
-        <v>0.06373661666253409</v>
+        <v>0.0672366166625341</v>
       </c>
       <c r="V30">
         <v>0.125</v>
       </c>
       <c r="W30">
-        <v>0.05576953957971733</v>
+        <v>0.05883203957971733</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y30">
-        <v>4.005819816678337</v>
+        <v>3.66635571454573</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3897,22 +3897,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1063939833327847</v>
+        <v>0.1064506141152814</v>
       </c>
       <c r="C31">
-        <v>3488.567336337824</v>
+        <v>3434.412312928666</v>
       </c>
       <c r="D31">
-        <v>4547.766580394052</v>
+        <v>4543.801186090282</v>
       </c>
       <c r="E31">
-        <v>1089.936333517509</v>
+        <v>1140.125962622896</v>
       </c>
       <c r="F31">
-        <v>1455.499244056228</v>
+        <v>1505.688873161615</v>
       </c>
       <c r="G31">
         <v>396.3</v>
@@ -3933,28 +3933,28 @@
         <v>358.8</v>
       </c>
       <c r="M31">
-        <v>97.86284472521677</v>
+        <v>101.2374255778105</v>
       </c>
       <c r="N31">
-        <v>260.9371552747832</v>
+        <v>257.5625744221895</v>
       </c>
       <c r="O31">
-        <v>32.6171444093479</v>
+        <v>32.19532180277369</v>
       </c>
       <c r="P31">
-        <v>228.3200108654353</v>
+        <v>225.3672526194158</v>
       </c>
       <c r="Q31">
-        <v>238.4200108654353</v>
+        <v>235.4672526194158</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1258206927530516</v>
+        <v>0.1268585746305231</v>
       </c>
       <c r="T31">
-        <v>1.559752244194073</v>
+        <v>1.579982493794515</v>
       </c>
       <c r="U31">
         <v>0.0672366166625341</v>
@@ -3971,7 +3971,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>3.66635571454573</v>
+        <v>3.544143857394206</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3979,22 +3979,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1064506141152814</v>
+        <v>0.1072667448977781</v>
       </c>
       <c r="C32">
-        <v>3434.412312928666</v>
+        <v>3327.834071233158</v>
       </c>
       <c r="D32">
-        <v>4543.801186090282</v>
+        <v>4487.412573500161</v>
       </c>
       <c r="E32">
-        <v>1140.125962622896</v>
+        <v>1190.315591728284</v>
       </c>
       <c r="F32">
-        <v>1505.688873161615</v>
+        <v>1555.878502267003</v>
       </c>
       <c r="G32">
         <v>396.3</v>
@@ -4015,45 +4015,45 @@
         <v>358.8</v>
       </c>
       <c r="M32">
-        <v>101.2374255778105</v>
+        <v>108.9684662367518</v>
       </c>
       <c r="N32">
-        <v>257.5625744221895</v>
+        <v>249.8315337632483</v>
       </c>
       <c r="O32">
-        <v>32.19532180277369</v>
+        <v>31.22894172040603</v>
       </c>
       <c r="P32">
-        <v>225.3672526194158</v>
+        <v>218.6025920428422</v>
       </c>
       <c r="Q32">
-        <v>235.4672526194158</v>
+        <v>228.7025920428422</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1268585746305231</v>
+        <v>0.127926540040675</v>
       </c>
       <c r="T32">
-        <v>1.579982493794515</v>
+        <v>1.600799127441347</v>
       </c>
       <c r="U32">
-        <v>0.0672366166625341</v>
+        <v>0.07003661666253409</v>
       </c>
       <c r="V32">
         <v>0.125</v>
       </c>
       <c r="W32">
-        <v>0.05883203957971733</v>
+        <v>0.06128203957971733</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y32">
-        <v>3.544143857394206</v>
+        <v>3.292695698042116</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4061,22 +4061,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1072667448977781</v>
+        <v>0.1073478756802748</v>
       </c>
       <c r="C33">
-        <v>3327.834071233158</v>
+        <v>3272.115289856565</v>
       </c>
       <c r="D33">
-        <v>4487.412573500161</v>
+        <v>4481.883421228955</v>
       </c>
       <c r="E33">
-        <v>1190.315591728284</v>
+        <v>1240.505220833671</v>
       </c>
       <c r="F33">
-        <v>1555.878502267003</v>
+        <v>1606.06813137239</v>
       </c>
       <c r="G33">
         <v>396.3</v>
@@ -4097,28 +4097,28 @@
         <v>358.8</v>
       </c>
       <c r="M33">
-        <v>108.9684662367518</v>
+        <v>112.4835780508405</v>
       </c>
       <c r="N33">
-        <v>249.8315337632483</v>
+        <v>246.3164219491595</v>
       </c>
       <c r="O33">
-        <v>31.22894172040603</v>
+        <v>30.78955274364494</v>
       </c>
       <c r="P33">
-        <v>218.6025920428422</v>
+        <v>215.5268692055145</v>
       </c>
       <c r="Q33">
-        <v>228.7025920428422</v>
+        <v>225.6268692055145</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.127926540040675</v>
+        <v>0.1290259161981842</v>
       </c>
       <c r="T33">
-        <v>1.600799127441347</v>
+        <v>1.622228015018968</v>
       </c>
       <c r="U33">
         <v>0.07003661666253409</v>
@@ -4135,7 +4135,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>3.292695698042116</v>
+        <v>3.189798957478299</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4143,22 +4143,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1073478756802748</v>
+        <v>0.1074290064627715</v>
       </c>
       <c r="C34">
-        <v>3272.115289856565</v>
+        <v>3216.410117169646</v>
       </c>
       <c r="D34">
-        <v>4481.883421228955</v>
+        <v>4476.367877647423</v>
       </c>
       <c r="E34">
-        <v>1240.505220833671</v>
+        <v>1290.694849939058</v>
       </c>
       <c r="F34">
-        <v>1606.06813137239</v>
+        <v>1656.257760477777</v>
       </c>
       <c r="G34">
         <v>396.3</v>
@@ -4179,28 +4179,28 @@
         <v>358.8</v>
       </c>
       <c r="M34">
-        <v>112.4835780508405</v>
+        <v>115.9986898649293</v>
       </c>
       <c r="N34">
-        <v>246.3164219491595</v>
+        <v>242.8013101350707</v>
       </c>
       <c r="O34">
-        <v>30.78955274364494</v>
+        <v>30.35016376688384</v>
       </c>
       <c r="P34">
-        <v>215.5268692055145</v>
+        <v>212.4511463681869</v>
       </c>
       <c r="Q34">
-        <v>225.6268692055145</v>
+        <v>222.5511463681869</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1290259161981842</v>
+        <v>0.130158109554425</v>
       </c>
       <c r="T34">
-        <v>1.622228015018968</v>
+        <v>1.644296570882488</v>
       </c>
       <c r="U34">
         <v>0.07003661666253409</v>
@@ -4217,7 +4217,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>3.189798957478299</v>
+        <v>3.09313838300926</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4225,22 +4225,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1074290064627715</v>
+        <v>0.1075101372452682</v>
       </c>
       <c r="C35">
-        <v>3216.410117169646</v>
+        <v>3160.718502992339</v>
       </c>
       <c r="D35">
-        <v>4476.367877647423</v>
+        <v>4470.865892575503</v>
       </c>
       <c r="E35">
-        <v>1290.694849939058</v>
+        <v>1340.884479044445</v>
       </c>
       <c r="F35">
-        <v>1656.257760477777</v>
+        <v>1706.447389583164</v>
       </c>
       <c r="G35">
         <v>396.3</v>
@@ -4261,28 +4261,28 @@
         <v>358.8</v>
       </c>
       <c r="M35">
-        <v>115.9986898649293</v>
+        <v>119.513801679018</v>
       </c>
       <c r="N35">
-        <v>242.8013101350707</v>
+        <v>239.286198320982</v>
       </c>
       <c r="O35">
-        <v>30.35016376688384</v>
+        <v>29.91077479012274</v>
       </c>
       <c r="P35">
-        <v>212.4511463681869</v>
+        <v>209.3754235308592</v>
       </c>
       <c r="Q35">
-        <v>222.5511463681869</v>
+        <v>219.4754235308592</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.130158109554425</v>
+        <v>0.131324611800249</v>
       </c>
       <c r="T35">
-        <v>1.644296570882488</v>
+        <v>1.667033870863084</v>
       </c>
       <c r="U35">
         <v>0.07003661666253409</v>
@@ -4299,7 +4299,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>3.09313838300926</v>
+        <v>3.002163724685458</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4307,22 +4307,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1075101372452682</v>
+        <v>0.1099800180277649</v>
       </c>
       <c r="C36">
-        <v>3160.718502992339</v>
+        <v>2949.270712049904</v>
       </c>
       <c r="D36">
-        <v>4470.865892575503</v>
+        <v>4309.607730738456</v>
       </c>
       <c r="E36">
-        <v>1340.884479044445</v>
+        <v>1391.074108149833</v>
       </c>
       <c r="F36">
-        <v>1706.447389583164</v>
+        <v>1756.637018688552</v>
       </c>
       <c r="G36">
         <v>396.3</v>
@@ -4343,45 +4343,45 @@
         <v>358.8</v>
       </c>
       <c r="M36">
-        <v>119.513801679018</v>
+        <v>136.7306822388776</v>
       </c>
       <c r="N36">
-        <v>239.286198320982</v>
+        <v>222.0693177611224</v>
       </c>
       <c r="O36">
-        <v>29.91077479012274</v>
+        <v>27.75866472014031</v>
       </c>
       <c r="P36">
-        <v>209.3754235308592</v>
+        <v>194.3106530409821</v>
       </c>
       <c r="Q36">
-        <v>219.4754235308592</v>
+        <v>204.4106530409821</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.131324611800249</v>
+        <v>0.1325270064228674</v>
       </c>
       <c r="T36">
-        <v>1.667033870863084</v>
+        <v>1.690470780073852</v>
       </c>
       <c r="U36">
-        <v>0.07003661666253409</v>
+        <v>0.07783661666253411</v>
       </c>
       <c r="V36">
         <v>0.125</v>
       </c>
       <c r="W36">
-        <v>0.06128203957971733</v>
+        <v>0.06810703957971734</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y36">
-        <v>3.002163724685458</v>
+        <v>2.624136690645283</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4389,22 +4389,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1099800180277649</v>
+        <v>0.1101293988102616</v>
       </c>
       <c r="C37">
-        <v>2949.270712049904</v>
+        <v>2889.700276502635</v>
       </c>
       <c r="D37">
-        <v>4309.607730738456</v>
+        <v>4300.226924296574</v>
       </c>
       <c r="E37">
-        <v>1391.074108149833</v>
+        <v>1441.26373725522</v>
       </c>
       <c r="F37">
-        <v>1756.637018688552</v>
+        <v>1806.826647793939</v>
       </c>
       <c r="G37">
         <v>396.3</v>
@@ -4425,28 +4425,28 @@
         <v>358.8</v>
       </c>
       <c r="M37">
-        <v>136.7306822388776</v>
+        <v>140.6372731599884</v>
       </c>
       <c r="N37">
-        <v>222.0693177611224</v>
+        <v>218.1627268400117</v>
       </c>
       <c r="O37">
-        <v>27.75866472014031</v>
+        <v>27.27034085500146</v>
       </c>
       <c r="P37">
-        <v>194.3106530409821</v>
+        <v>190.8923859850102</v>
       </c>
       <c r="Q37">
-        <v>204.4106530409821</v>
+        <v>200.9923859850102</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1325270064228674</v>
+        <v>0.1337669758774427</v>
       </c>
       <c r="T37">
-        <v>1.690470780073852</v>
+        <v>1.714640092697457</v>
       </c>
       <c r="U37">
         <v>0.07783661666253411</v>
@@ -4463,7 +4463,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>2.624136690645283</v>
+        <v>2.551244004794025</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4471,22 +4471,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1101293988102616</v>
+        <v>0.1115414045927583</v>
       </c>
       <c r="C38">
-        <v>2889.700276502635</v>
+        <v>2752.816348321432</v>
       </c>
       <c r="D38">
-        <v>4300.226924296574</v>
+        <v>4213.532625220758</v>
       </c>
       <c r="E38">
-        <v>1441.263737255219</v>
+        <v>1491.453366360607</v>
       </c>
       <c r="F38">
-        <v>1806.826647793938</v>
+        <v>1857.016276899326</v>
       </c>
       <c r="G38">
         <v>396.3</v>
@@ -4507,45 +4507,45 @@
         <v>358.8</v>
       </c>
       <c r="M38">
-        <v>140.6372731599883</v>
+        <v>151.7862275610065</v>
       </c>
       <c r="N38">
-        <v>218.1627268400117</v>
+        <v>207.0137724389936</v>
       </c>
       <c r="O38">
-        <v>27.27034085500146</v>
+        <v>25.87672155487419</v>
       </c>
       <c r="P38">
-        <v>190.8923859850102</v>
+        <v>181.1370508841194</v>
       </c>
       <c r="Q38">
-        <v>200.9923859850102</v>
+        <v>191.2370508841194</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1337669758774427</v>
+        <v>0.1350463094416871</v>
       </c>
       <c r="T38">
-        <v>1.714640092697457</v>
+        <v>1.739576685086891</v>
       </c>
       <c r="U38">
-        <v>0.07783661666253411</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V38">
         <v>0.125</v>
       </c>
       <c r="W38">
-        <v>0.06810703957971734</v>
+        <v>0.07151953957971734</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y38">
-        <v>2.551244004794026</v>
+        <v>2.363850829982515</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4553,22 +4553,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1115414045927583</v>
+        <v>0.111724910375255</v>
       </c>
       <c r="C39">
-        <v>2752.816348321432</v>
+        <v>2691.61582950427</v>
       </c>
       <c r="D39">
-        <v>4213.532625220758</v>
+        <v>4202.521735508983</v>
       </c>
       <c r="E39">
-        <v>1491.453366360607</v>
+        <v>1541.642995465994</v>
       </c>
       <c r="F39">
-        <v>1857.016276899326</v>
+        <v>1907.205906004713</v>
       </c>
       <c r="G39">
         <v>396.3</v>
@@ -4589,28 +4589,28 @@
         <v>358.8</v>
       </c>
       <c r="M39">
-        <v>151.7862275610065</v>
+        <v>155.8885580356283</v>
       </c>
       <c r="N39">
-        <v>207.0137724389936</v>
+        <v>202.9114419643717</v>
       </c>
       <c r="O39">
-        <v>25.87672155487419</v>
+        <v>25.36393024554647</v>
       </c>
       <c r="P39">
-        <v>181.1370508841194</v>
+        <v>177.5475117188253</v>
       </c>
       <c r="Q39">
-        <v>191.2370508841194</v>
+        <v>187.6475117188253</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1350463094416871</v>
+        <v>0.1363669118305845</v>
       </c>
       <c r="T39">
-        <v>1.739576685086891</v>
+        <v>1.765317683682435</v>
       </c>
       <c r="U39">
         <v>0.0817366166625341</v>
@@ -4627,7 +4627,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>2.363850829982515</v>
+        <v>2.301644229193501</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4635,22 +4635,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.111724910375255</v>
+        <v>0.1119084161577517</v>
       </c>
       <c r="C40">
-        <v>2691.61582950427</v>
+        <v>2630.472708458874</v>
       </c>
       <c r="D40">
-        <v>4202.521735508983</v>
+        <v>4191.568243568974</v>
       </c>
       <c r="E40">
-        <v>1541.642995465994</v>
+        <v>1591.832624571381</v>
       </c>
       <c r="F40">
-        <v>1907.205906004713</v>
+        <v>1957.3955351101</v>
       </c>
       <c r="G40">
         <v>396.3</v>
@@ -4671,28 +4671,28 @@
         <v>358.8</v>
       </c>
       <c r="M40">
-        <v>155.8885580356283</v>
+        <v>159.9908885102501</v>
       </c>
       <c r="N40">
-        <v>202.9114419643717</v>
+        <v>198.8091114897499</v>
       </c>
       <c r="O40">
-        <v>25.36393024554647</v>
+        <v>24.85113893621874</v>
       </c>
       <c r="P40">
-        <v>177.5475117188253</v>
+        <v>173.9579725535312</v>
       </c>
       <c r="Q40">
-        <v>187.6475117188253</v>
+        <v>184.0579725535312</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1363669118305845</v>
+        <v>0.1377308126584622</v>
       </c>
       <c r="T40">
-        <v>1.765317683682435</v>
+        <v>1.791902649445047</v>
       </c>
       <c r="U40">
         <v>0.0817366166625341</v>
@@ -4709,7 +4709,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>2.301644229193501</v>
+        <v>2.242627710496232</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4717,22 +4717,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1119084161577517</v>
+        <v>0.1120919219402484</v>
       </c>
       <c r="C41">
-        <v>2630.472708458874</v>
+        <v>2569.38653754571</v>
       </c>
       <c r="D41">
-        <v>4191.568243568974</v>
+        <v>4180.671701761197</v>
       </c>
       <c r="E41">
-        <v>1591.832624571381</v>
+        <v>1642.022253676769</v>
       </c>
       <c r="F41">
-        <v>1957.3955351101</v>
+        <v>2007.585164215488</v>
       </c>
       <c r="G41">
         <v>396.3</v>
@@ -4753,28 +4753,28 @@
         <v>358.8</v>
       </c>
       <c r="M41">
-        <v>159.9908885102501</v>
+        <v>164.0932189848719</v>
       </c>
       <c r="N41">
-        <v>198.8091114897499</v>
+        <v>194.7067810151281</v>
       </c>
       <c r="O41">
-        <v>24.85113893621874</v>
+        <v>24.33834762689102</v>
       </c>
       <c r="P41">
-        <v>173.9579725535312</v>
+        <v>170.3684333882371</v>
       </c>
       <c r="Q41">
-        <v>184.0579725535312</v>
+        <v>180.4684333882371</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1377308126584622</v>
+        <v>0.1391401768472691</v>
       </c>
       <c r="T41">
-        <v>1.791902649445047</v>
+        <v>1.819373780733079</v>
       </c>
       <c r="U41">
         <v>0.0817366166625341</v>
@@ -4791,7 +4791,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>2.242627710496232</v>
+        <v>2.186562017733826</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4799,22 +4799,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1120919219402484</v>
+        <v>0.1122754277227451</v>
       </c>
       <c r="C42">
-        <v>2569.38653754571</v>
+        <v>2508.35687376797</v>
       </c>
       <c r="D42">
-        <v>4180.671701761197</v>
+        <v>4169.831667088844</v>
       </c>
       <c r="E42">
-        <v>1642.022253676769</v>
+        <v>1692.211882782156</v>
       </c>
       <c r="F42">
-        <v>2007.585164215488</v>
+        <v>2057.774793320875</v>
       </c>
       <c r="G42">
         <v>396.3</v>
@@ -4835,28 +4835,28 @@
         <v>358.8</v>
       </c>
       <c r="M42">
-        <v>164.0932189848719</v>
+        <v>168.1955494594937</v>
       </c>
       <c r="N42">
-        <v>194.7067810151281</v>
+        <v>190.6044505405063</v>
       </c>
       <c r="O42">
-        <v>24.33834762689102</v>
+        <v>23.82555631756329</v>
       </c>
       <c r="P42">
-        <v>170.3684333882371</v>
+        <v>166.7788942229431</v>
       </c>
       <c r="Q42">
-        <v>180.4684333882371</v>
+        <v>176.878894222943</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1391401768472691</v>
+        <v>0.1405973160933237</v>
       </c>
       <c r="T42">
-        <v>1.819373780733079</v>
+        <v>1.847776136810535</v>
       </c>
       <c r="U42">
         <v>0.0817366166625341</v>
@@ -4873,7 +4873,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>2.186562017733826</v>
+        <v>2.133231236813489</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4881,22 +4881,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1122754277227451</v>
+        <v>0.1124589335052418</v>
       </c>
       <c r="C43">
-        <v>2508.35687376797</v>
+        <v>2447.383278711533</v>
       </c>
       <c r="D43">
-        <v>4169.831667088844</v>
+        <v>4159.047701137795</v>
       </c>
       <c r="E43">
-        <v>1692.211882782156</v>
+        <v>1742.401511887543</v>
       </c>
       <c r="F43">
-        <v>2057.774793320875</v>
+        <v>2107.964422426262</v>
       </c>
       <c r="G43">
         <v>396.3</v>
@@ -4917,28 +4917,28 @@
         <v>358.8</v>
       </c>
       <c r="M43">
-        <v>168.1955494594937</v>
+        <v>172.2978799341155</v>
       </c>
       <c r="N43">
-        <v>190.6044505405063</v>
+        <v>186.5021200658846</v>
       </c>
       <c r="O43">
-        <v>23.82555631756329</v>
+        <v>23.31276500823557</v>
       </c>
       <c r="P43">
-        <v>166.7788942229431</v>
+        <v>163.189355057649</v>
       </c>
       <c r="Q43">
-        <v>176.878894222943</v>
+        <v>173.289355057649</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1405973160933237</v>
+        <v>0.1421047015202767</v>
       </c>
       <c r="T43">
-        <v>1.847776136810535</v>
+        <v>1.87715788447687</v>
       </c>
       <c r="U43">
         <v>0.0817366166625341</v>
@@ -4955,7 +4955,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>2.133231236813489</v>
+        <v>2.082440016889358</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4963,22 +4963,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1124589335052418</v>
+        <v>0.1126424392877385</v>
       </c>
       <c r="C44">
-        <v>2447.383278711534</v>
+        <v>2386.46531848587</v>
       </c>
       <c r="D44">
-        <v>4159.047701137795</v>
+        <v>4148.319370017519</v>
       </c>
       <c r="E44">
-        <v>1742.401511887542</v>
+        <v>1792.59114099293</v>
       </c>
       <c r="F44">
-        <v>2107.964422426262</v>
+        <v>2158.154051531649</v>
       </c>
       <c r="G44">
         <v>396.3</v>
@@ -4999,28 +4999,28 @@
         <v>358.8</v>
       </c>
       <c r="M44">
-        <v>172.2978799341154</v>
+        <v>176.4002104087372</v>
       </c>
       <c r="N44">
-        <v>186.5021200658846</v>
+        <v>182.3997895912628</v>
       </c>
       <c r="O44">
-        <v>23.31276500823557</v>
+        <v>22.79997369890785</v>
       </c>
       <c r="P44">
-        <v>163.189355057649</v>
+        <v>159.5998158923549</v>
       </c>
       <c r="Q44">
-        <v>173.289355057649</v>
+        <v>169.6998158923549</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1421047015202767</v>
+        <v>0.1436649776639649</v>
       </c>
       <c r="T44">
-        <v>1.877157884476869</v>
+        <v>1.907570570657812</v>
       </c>
       <c r="U44">
         <v>0.0817366166625341</v>
@@ -5037,7 +5037,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>2.082440016889358</v>
+        <v>2.034011179287281</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5045,22 +5045,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1126424392877385</v>
+        <v>0.1182929450702352</v>
       </c>
       <c r="C45">
-        <v>2386.46531848587</v>
+        <v>2031.02673857025</v>
       </c>
       <c r="D45">
-        <v>4148.319370017519</v>
+        <v>3843.070419207286</v>
       </c>
       <c r="E45">
-        <v>1792.59114099293</v>
+        <v>1842.780770098317</v>
       </c>
       <c r="F45">
-        <v>2158.154051531649</v>
+        <v>2208.343680637036</v>
       </c>
       <c r="G45">
         <v>396.3</v>
@@ -5081,45 +5081,45 @@
         <v>358.8</v>
       </c>
       <c r="M45">
-        <v>176.4002104087372</v>
+        <v>211.8610211484049</v>
       </c>
       <c r="N45">
-        <v>182.3997895912628</v>
+        <v>146.9389788515951</v>
       </c>
       <c r="O45">
-        <v>22.79997369890785</v>
+        <v>18.36737235644938</v>
       </c>
       <c r="P45">
-        <v>159.5998158923549</v>
+        <v>128.5716064951457</v>
       </c>
       <c r="Q45">
-        <v>169.6998158923549</v>
+        <v>138.6716064951457</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1436649776639649</v>
+        <v>0.145280977955642</v>
       </c>
       <c r="T45">
-        <v>1.907570570657812</v>
+        <v>1.93906942420236</v>
       </c>
       <c r="U45">
-        <v>0.0817366166625341</v>
+        <v>0.0959366166625341</v>
       </c>
       <c r="V45">
         <v>0.125</v>
       </c>
       <c r="W45">
-        <v>0.07151953957971734</v>
+        <v>0.08394453957971734</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y45">
-        <v>2.034011179287281</v>
+        <v>1.693563063441797</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5127,22 +5127,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1182929450702352</v>
+        <v>0.1186007008527319</v>
       </c>
       <c r="C46">
-        <v>2031.02673857025</v>
+        <v>1965.496515693221</v>
       </c>
       <c r="D46">
-        <v>3843.070419207286</v>
+        <v>3827.729825435644</v>
       </c>
       <c r="E46">
-        <v>1842.780770098317</v>
+        <v>1892.970399203704</v>
       </c>
       <c r="F46">
-        <v>2208.343680637036</v>
+        <v>2258.533309742423</v>
       </c>
       <c r="G46">
         <v>396.3</v>
@@ -5163,28 +5163,28 @@
         <v>358.8</v>
       </c>
       <c r="M46">
-        <v>211.8610211484049</v>
+        <v>216.6760443563232</v>
       </c>
       <c r="N46">
-        <v>146.9389788515951</v>
+        <v>142.1239556436768</v>
       </c>
       <c r="O46">
-        <v>18.36737235644938</v>
+        <v>17.7654944554596</v>
       </c>
       <c r="P46">
-        <v>128.5716064951457</v>
+        <v>124.3584611882172</v>
       </c>
       <c r="Q46">
-        <v>138.6716064951457</v>
+        <v>134.4584611882172</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.145280977955642</v>
+        <v>0.1469557418942892</v>
       </c>
       <c r="T46">
-        <v>1.93906942420236</v>
+        <v>1.971713690603073</v>
       </c>
       <c r="U46">
         <v>0.0959366166625341</v>
@@ -5201,7 +5201,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>1.693563063441797</v>
+        <v>1.655928328698646</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5209,22 +5209,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1186007008527319</v>
+        <v>0.1189084566352286</v>
       </c>
       <c r="C47">
-        <v>1965.496515693221</v>
+        <v>1900.088277652163</v>
       </c>
       <c r="D47">
-        <v>3827.729825435644</v>
+        <v>3812.511216499974</v>
       </c>
       <c r="E47">
-        <v>1892.970399203704</v>
+        <v>1943.160028309091</v>
       </c>
       <c r="F47">
-        <v>2258.533309742423</v>
+        <v>2308.72293884781</v>
       </c>
       <c r="G47">
         <v>396.3</v>
@@ -5245,28 +5245,28 @@
         <v>358.8</v>
       </c>
       <c r="M47">
-        <v>216.6760443563232</v>
+        <v>221.4910675642415</v>
       </c>
       <c r="N47">
-        <v>142.1239556436768</v>
+        <v>137.3089324357585</v>
       </c>
       <c r="O47">
-        <v>17.7654944554596</v>
+        <v>17.16361655446981</v>
       </c>
       <c r="P47">
-        <v>124.3584611882172</v>
+        <v>120.1453158812887</v>
       </c>
       <c r="Q47">
-        <v>134.4584611882172</v>
+        <v>130.2453158812887</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1469557418942892</v>
+        <v>0.1486925341269603</v>
       </c>
       <c r="T47">
-        <v>1.971713690603073</v>
+        <v>2.005567003907516</v>
       </c>
       <c r="U47">
         <v>0.0959366166625341</v>
@@ -5283,7 +5283,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>1.655928328698646</v>
+        <v>1.619929886770414</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5291,22 +5291,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1189084566352286</v>
+        <v>0.1192162124177253</v>
       </c>
       <c r="C48">
-        <v>1900.088277652163</v>
+        <v>1834.800575216459</v>
       </c>
       <c r="D48">
-        <v>3812.511216499974</v>
+        <v>3797.413143169656</v>
       </c>
       <c r="E48">
-        <v>1943.160028309091</v>
+        <v>1993.349657414479</v>
       </c>
       <c r="F48">
-        <v>2308.72293884781</v>
+        <v>2358.912567953198</v>
       </c>
       <c r="G48">
         <v>396.3</v>
@@ -5327,28 +5327,28 @@
         <v>358.8</v>
       </c>
       <c r="M48">
-        <v>221.4910675642415</v>
+        <v>226.3060907721598</v>
       </c>
       <c r="N48">
-        <v>137.3089324357585</v>
+        <v>132.4939092278402</v>
       </c>
       <c r="O48">
-        <v>17.16361655446981</v>
+        <v>16.56173865348002</v>
       </c>
       <c r="P48">
-        <v>120.1453158812887</v>
+        <v>115.9321705743601</v>
       </c>
       <c r="Q48">
-        <v>130.2453158812887</v>
+        <v>126.0321705743601</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1486925341269603</v>
+        <v>0.1504948656891663</v>
       </c>
       <c r="T48">
-        <v>2.005567003907516</v>
+        <v>2.040697800732882</v>
       </c>
       <c r="U48">
         <v>0.0959366166625341</v>
@@ -5365,7 +5365,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>1.619929886770414</v>
+        <v>1.585463293434874</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5373,22 +5373,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1192162124177253</v>
+        <v>0.119523968200222</v>
       </c>
       <c r="C49">
-        <v>1834.800575216459</v>
+        <v>1769.63198202155</v>
       </c>
       <c r="D49">
-        <v>3797.413143169656</v>
+        <v>3782.434179080135</v>
       </c>
       <c r="E49">
-        <v>1993.349657414479</v>
+        <v>2043.539286519866</v>
       </c>
       <c r="F49">
-        <v>2358.912567953198</v>
+        <v>2409.102197058585</v>
       </c>
       <c r="G49">
         <v>396.3</v>
@@ -5409,28 +5409,28 @@
         <v>358.8</v>
       </c>
       <c r="M49">
-        <v>226.3060907721598</v>
+        <v>231.1211139800782</v>
       </c>
       <c r="N49">
-        <v>132.4939092278402</v>
+        <v>127.6788860199218</v>
       </c>
       <c r="O49">
-        <v>16.56173865348002</v>
+        <v>15.95986075249023</v>
       </c>
       <c r="P49">
-        <v>115.9321705743601</v>
+        <v>111.7190252674316</v>
       </c>
       <c r="Q49">
-        <v>126.0321705743601</v>
+        <v>121.8190252674316</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1504948656891663</v>
+        <v>0.1523665176960724</v>
       </c>
       <c r="T49">
-        <v>2.040697800732882</v>
+        <v>2.077179782051531</v>
       </c>
       <c r="U49">
         <v>0.0959366166625341</v>
@@ -5447,7 +5447,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>1.585463293434874</v>
+        <v>1.55243280815498</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5455,22 +5455,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.119523968200222</v>
+        <v>0.1198317239827187</v>
       </c>
       <c r="C50">
-        <v>1769.631982021551</v>
+        <v>1704.58109411974</v>
       </c>
       <c r="D50">
-        <v>3782.434179080135</v>
+        <v>3767.572920283712</v>
       </c>
       <c r="E50">
-        <v>2043.539286519866</v>
+        <v>2093.728915625253</v>
       </c>
       <c r="F50">
-        <v>2409.102197058585</v>
+        <v>2459.291826163972</v>
       </c>
       <c r="G50">
         <v>396.3</v>
@@ -5491,28 +5491,28 @@
         <v>358.8</v>
       </c>
       <c r="M50">
-        <v>231.1211139800781</v>
+        <v>235.9361371879964</v>
       </c>
       <c r="N50">
-        <v>127.6788860199219</v>
+        <v>122.8638628120036</v>
       </c>
       <c r="O50">
-        <v>15.95986075249024</v>
+        <v>15.35798285150045</v>
       </c>
       <c r="P50">
-        <v>111.7190252674316</v>
+        <v>107.5058799605031</v>
       </c>
       <c r="Q50">
-        <v>121.8190252674316</v>
+        <v>117.6058799605031</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1523665176960724</v>
+        <v>0.1543115678208964</v>
       </c>
       <c r="T50">
-        <v>2.077179782051531</v>
+        <v>2.115092429304244</v>
       </c>
       <c r="U50">
         <v>0.0959366166625341</v>
@@ -5529,7 +5529,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>1.552432808154981</v>
+        <v>1.520750505947736</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5537,22 +5537,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1198317239827187</v>
+        <v>0.145834823466311</v>
       </c>
       <c r="C51">
-        <v>1704.58109411974</v>
+        <v>715.3835100035139</v>
       </c>
       <c r="D51">
-        <v>3767.572920283712</v>
+        <v>2828.564965272873</v>
       </c>
       <c r="E51">
-        <v>2093.728915625253</v>
+        <v>2143.91854473064</v>
       </c>
       <c r="F51">
-        <v>2459.291826163972</v>
+        <v>2509.481455269359</v>
       </c>
       <c r="G51">
         <v>396.3</v>
@@ -5573,45 +5573,45 @@
         <v>358.8</v>
       </c>
       <c r="M51">
-        <v>235.9361371879964</v>
+        <v>383.2897070552144</v>
       </c>
       <c r="N51">
-        <v>122.8638628120036</v>
+        <v>-24.48970705521435</v>
       </c>
       <c r="O51">
-        <v>15.35798285150045</v>
+        <v>-3.061213381901794</v>
       </c>
       <c r="P51">
-        <v>107.5058799605031</v>
+        <v>-21.42849367331256</v>
       </c>
       <c r="Q51">
-        <v>117.6058799605031</v>
+        <v>-11.32849367331256</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1543115678208964</v>
+        <v>0.1568052484153245</v>
       </c>
       <c r="T51">
-        <v>2.115092429304244</v>
+        <v>2.163698905574898</v>
       </c>
       <c r="U51">
-        <v>0.0959366166625341</v>
+        <v>0.1527366166625341</v>
       </c>
       <c r="V51">
-        <v>0.125</v>
+        <v>0.1170133170143783</v>
       </c>
       <c r="W51">
-        <v>0.08394453957971734</v>
+        <v>0.1348643985172974</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y51">
-        <v>1.520750505947736</v>
+        <v>0.9361065361150267</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5619,22 +5619,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.145834823466311</v>
+        <v>0.1469041896329363</v>
       </c>
       <c r="C52">
-        <v>715.3835100035139</v>
+        <v>636.4962280912005</v>
       </c>
       <c r="D52">
-        <v>2828.564965272873</v>
+        <v>2799.867312465947</v>
       </c>
       <c r="E52">
-        <v>2143.91854473064</v>
+        <v>2194.108173836027</v>
       </c>
       <c r="F52">
-        <v>2509.481455269359</v>
+        <v>2559.671084374746</v>
       </c>
       <c r="G52">
         <v>396.3</v>
@@ -5655,37 +5655,37 @@
         <v>358.8</v>
       </c>
       <c r="M52">
-        <v>383.2897070552144</v>
+        <v>390.9555011963186</v>
       </c>
       <c r="N52">
-        <v>-24.48970705521435</v>
+        <v>-32.1555011963186</v>
       </c>
       <c r="O52">
-        <v>-3.061213381901794</v>
+        <v>-4.019437649539825</v>
       </c>
       <c r="P52">
-        <v>-21.42849367331256</v>
+        <v>-28.13606354677877</v>
       </c>
       <c r="Q52">
-        <v>-11.32849367331256</v>
+        <v>-18.03606354677877</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1568052484153245</v>
+        <v>0.1590706616482903</v>
       </c>
       <c r="T52">
-        <v>2.163698905574898</v>
+        <v>2.207856026096835</v>
       </c>
       <c r="U52">
         <v>0.1527366166625341</v>
       </c>
       <c r="V52">
-        <v>0.1170133170143783</v>
+        <v>0.1147189382493905</v>
       </c>
       <c r="W52">
-        <v>0.1348643985172974</v>
+        <v>0.135214834167204</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5693,7 +5693,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.9361065361150267</v>
+        <v>0.9177515059951242</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5701,22 +5701,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1469041896329363</v>
+        <v>0.1479735557995617</v>
       </c>
       <c r="C53">
-        <v>636.4962280912005</v>
+        <v>558.185410709249</v>
       </c>
       <c r="D53">
-        <v>2799.867312465947</v>
+        <v>2771.746124189382</v>
       </c>
       <c r="E53">
-        <v>2194.108173836027</v>
+        <v>2244.297802941414</v>
       </c>
       <c r="F53">
-        <v>2559.671084374746</v>
+        <v>2609.860713480134</v>
       </c>
       <c r="G53">
         <v>396.3</v>
@@ -5737,37 +5737,37 @@
         <v>358.8</v>
       </c>
       <c r="M53">
-        <v>390.9555011963186</v>
+        <v>398.6212953374229</v>
       </c>
       <c r="N53">
-        <v>-32.1555011963186</v>
+        <v>-39.8212953374229</v>
       </c>
       <c r="O53">
-        <v>-4.019437649539825</v>
+        <v>-4.977661917177862</v>
       </c>
       <c r="P53">
-        <v>-28.13606354677877</v>
+        <v>-34.84363342024503</v>
       </c>
       <c r="Q53">
-        <v>-18.03606354677877</v>
+        <v>-24.74363342024503</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1590706616482903</v>
+        <v>0.1614304670992964</v>
       </c>
       <c r="T53">
-        <v>2.207856026096835</v>
+        <v>2.253853026640519</v>
       </c>
       <c r="U53">
         <v>0.1527366166625341</v>
       </c>
       <c r="V53">
-        <v>0.1147189382493905</v>
+        <v>0.1125128048215176</v>
       </c>
       <c r="W53">
-        <v>0.135214834167204</v>
+        <v>0.1355517915228835</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5775,7 +5775,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.9177515059951242</v>
+        <v>0.9001024385721411</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5783,22 +5783,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1479735557995617</v>
+        <v>0.149042921966187</v>
       </c>
       <c r="C54">
-        <v>558.185410709249</v>
+        <v>480.4338609692131</v>
       </c>
       <c r="D54">
-        <v>2771.746124189382</v>
+        <v>2744.184203554734</v>
       </c>
       <c r="E54">
-        <v>2244.297802941414</v>
+        <v>2294.487432046802</v>
       </c>
       <c r="F54">
-        <v>2609.860713480134</v>
+        <v>2660.050342585521</v>
       </c>
       <c r="G54">
         <v>396.3</v>
@@ -5819,37 +5819,37 @@
         <v>358.8</v>
       </c>
       <c r="M54">
-        <v>398.6212953374229</v>
+        <v>406.2870894785272</v>
       </c>
       <c r="N54">
-        <v>-39.8212953374229</v>
+        <v>-47.4870894785272</v>
       </c>
       <c r="O54">
-        <v>-4.977661917177862</v>
+        <v>-5.935886184815899</v>
       </c>
       <c r="P54">
-        <v>-34.84363342024503</v>
+        <v>-41.5512032937113</v>
       </c>
       <c r="Q54">
-        <v>-24.74363342024503</v>
+        <v>-31.45120329371129</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1614304670992964</v>
+        <v>0.1638906898035367</v>
       </c>
       <c r="T54">
-        <v>2.253853026640519</v>
+        <v>2.301807346356275</v>
       </c>
       <c r="U54">
         <v>0.1527366166625341</v>
       </c>
       <c r="V54">
-        <v>0.1125128048215176</v>
+        <v>0.1103899217116777</v>
       </c>
       <c r="W54">
-        <v>0.1355517915228835</v>
+        <v>0.1358760335066504</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5857,7 +5857,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.9001024385721411</v>
+        <v>0.8831193736934214</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5865,22 +5865,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.149042921966187</v>
+        <v>0.1501122881328123</v>
       </c>
       <c r="C55">
-        <v>480.4338609692131</v>
+        <v>403.2250592632677</v>
       </c>
       <c r="D55">
-        <v>2744.184203554734</v>
+        <v>2717.165030954176</v>
       </c>
       <c r="E55">
-        <v>2294.487432046802</v>
+        <v>2344.677061152189</v>
       </c>
       <c r="F55">
-        <v>2660.050342585521</v>
+        <v>2710.239971690908</v>
       </c>
       <c r="G55">
         <v>396.3</v>
@@ -5901,37 +5901,37 @@
         <v>358.8</v>
       </c>
       <c r="M55">
-        <v>406.2870894785272</v>
+        <v>413.9528836196315</v>
       </c>
       <c r="N55">
-        <v>-47.4870894785272</v>
+        <v>-55.1528836196315</v>
       </c>
       <c r="O55">
-        <v>-5.935886184815899</v>
+        <v>-6.894110452453937</v>
       </c>
       <c r="P55">
-        <v>-41.5512032937113</v>
+        <v>-48.25877316717756</v>
       </c>
       <c r="Q55">
-        <v>-31.45120329371129</v>
+        <v>-38.15877316717756</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1638906898035367</v>
+        <v>0.1664578787123093</v>
       </c>
       <c r="T55">
-        <v>2.301807346356275</v>
+        <v>2.351846636494455</v>
       </c>
       <c r="U55">
         <v>0.1527366166625341</v>
       </c>
       <c r="V55">
-        <v>0.1103899217116777</v>
+        <v>0.1083456639022022</v>
       </c>
       <c r="W55">
-        <v>0.1358760335066504</v>
+        <v>0.1361882665280557</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5939,7 +5939,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.8831193736934214</v>
+        <v>0.8667653112176172</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5947,22 +5947,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1501122881328123</v>
+        <v>0.1511816542994377</v>
       </c>
       <c r="C56">
-        <v>403.2250592632677</v>
+        <v>326.5431302468537</v>
       </c>
       <c r="D56">
-        <v>2717.165030954176</v>
+        <v>2690.672731043149</v>
       </c>
       <c r="E56">
-        <v>2344.677061152189</v>
+        <v>2394.866690257576</v>
       </c>
       <c r="F56">
-        <v>2710.239971690908</v>
+        <v>2760.429600796295</v>
       </c>
       <c r="G56">
         <v>396.3</v>
@@ -5983,37 +5983,37 @@
         <v>358.8</v>
       </c>
       <c r="M56">
-        <v>413.9528836196315</v>
+        <v>421.6186777607358</v>
       </c>
       <c r="N56">
-        <v>-55.1528836196315</v>
+        <v>-62.8186777607358</v>
       </c>
       <c r="O56">
-        <v>-6.894110452453937</v>
+        <v>-7.852334720091974</v>
       </c>
       <c r="P56">
-        <v>-48.25877316717756</v>
+        <v>-54.96634304064382</v>
       </c>
       <c r="Q56">
-        <v>-38.15877316717756</v>
+        <v>-44.86634304064382</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1664578787123093</v>
+        <v>0.1691391649059162</v>
       </c>
       <c r="T56">
-        <v>2.351846636494455</v>
+        <v>2.40410989508322</v>
       </c>
       <c r="U56">
         <v>0.1527366166625341</v>
       </c>
       <c r="V56">
-        <v>0.1083456639022022</v>
+        <v>0.1063757427403439</v>
       </c>
       <c r="W56">
-        <v>0.1361882665280557</v>
+        <v>0.1364891456214098</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -6021,7 +6021,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.8667653112176172</v>
+        <v>0.8510059419227515</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6029,22 +6029,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1511816542994377</v>
+        <v>0.152251020466063</v>
       </c>
       <c r="C57">
-        <v>326.5431302468537</v>
+        <v>250.3728117341875</v>
       </c>
       <c r="D57">
-        <v>2690.672731043149</v>
+        <v>2664.69204163587</v>
       </c>
       <c r="E57">
-        <v>2394.866690257576</v>
+        <v>2445.056319362963</v>
       </c>
       <c r="F57">
-        <v>2760.429600796295</v>
+        <v>2810.619229901683</v>
       </c>
       <c r="G57">
         <v>396.3</v>
@@ -6065,37 +6065,37 @@
         <v>358.8</v>
       </c>
       <c r="M57">
-        <v>421.6186777607358</v>
+        <v>429.2844719018401</v>
       </c>
       <c r="N57">
-        <v>-62.8186777607358</v>
+        <v>-70.4844719018401</v>
       </c>
       <c r="O57">
-        <v>-7.852334720091974</v>
+        <v>-8.810558987730012</v>
       </c>
       <c r="P57">
-        <v>-54.96634304064382</v>
+        <v>-61.67391291411008</v>
       </c>
       <c r="Q57">
-        <v>-44.86634304064382</v>
+        <v>-51.57391291411008</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1691391649059162</v>
+        <v>0.171942327744687</v>
       </c>
       <c r="T57">
-        <v>2.40410989508322</v>
+        <v>2.458748756335112</v>
       </c>
       <c r="U57">
         <v>0.1527366166625341</v>
       </c>
       <c r="V57">
-        <v>0.1063757427403439</v>
+        <v>0.1044761759056949</v>
       </c>
       <c r="W57">
-        <v>0.1364891456214098</v>
+        <v>0.1367792790328585</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6103,7 +6103,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.8510059419227515</v>
+        <v>0.8358094072455595</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6111,22 +6111,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.152251020466063</v>
+        <v>0.1533203866326884</v>
       </c>
       <c r="C58">
-        <v>250.3728117341875</v>
+        <v>174.6994253785601</v>
       </c>
       <c r="D58">
-        <v>2664.69204163587</v>
+        <v>2639.20828438563</v>
       </c>
       <c r="E58">
-        <v>2445.056319362963</v>
+        <v>2495.24594846835</v>
       </c>
       <c r="F58">
-        <v>2810.619229901683</v>
+        <v>2860.80885900707</v>
       </c>
       <c r="G58">
         <v>396.3</v>
@@ -6147,37 +6147,37 @@
         <v>358.8</v>
       </c>
       <c r="M58">
-        <v>429.2844719018401</v>
+        <v>436.9502660429444</v>
       </c>
       <c r="N58">
-        <v>-70.4844719018401</v>
+        <v>-78.15026604294439</v>
       </c>
       <c r="O58">
-        <v>-8.810558987730012</v>
+        <v>-9.768783255368049</v>
       </c>
       <c r="P58">
-        <v>-61.67391291411008</v>
+        <v>-68.38148278757635</v>
       </c>
       <c r="Q58">
-        <v>-51.57391291411008</v>
+        <v>-58.28148278757634</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.171942327744687</v>
+        <v>0.1748758702503774</v>
       </c>
       <c r="T58">
-        <v>2.458748756335112</v>
+        <v>2.515928959970812</v>
       </c>
       <c r="U58">
         <v>0.1527366166625341</v>
       </c>
       <c r="V58">
-        <v>0.1044761759056949</v>
+        <v>0.1026432605389284</v>
       </c>
       <c r="W58">
-        <v>0.1367792790328585</v>
+        <v>0.1370592323246072</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6185,7 +6185,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.8358094072455595</v>
+        <v>0.8211460843114269</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6193,22 +6193,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1533203866326884</v>
+        <v>0.1543897527993137</v>
       </c>
       <c r="C59">
-        <v>174.6994253785601</v>
+        <v>99.50884901911195</v>
       </c>
       <c r="D59">
-        <v>2639.20828438563</v>
+        <v>2614.207337131569</v>
       </c>
       <c r="E59">
-        <v>2495.24594846835</v>
+        <v>2545.435577573738</v>
       </c>
       <c r="F59">
-        <v>2860.80885900707</v>
+        <v>2910.998488112457</v>
       </c>
       <c r="G59">
         <v>396.3</v>
@@ -6229,37 +6229,37 @@
         <v>358.8</v>
       </c>
       <c r="M59">
-        <v>436.9502660429444</v>
+        <v>444.6160601840486</v>
       </c>
       <c r="N59">
-        <v>-78.15026604294439</v>
+        <v>-85.81606018404864</v>
       </c>
       <c r="O59">
-        <v>-9.768783255368049</v>
+        <v>-10.72700752300608</v>
       </c>
       <c r="P59">
-        <v>-68.38148278757635</v>
+        <v>-75.08905266104256</v>
       </c>
       <c r="Q59">
-        <v>-58.28148278757634</v>
+        <v>-64.98905266104256</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1748758702503774</v>
+        <v>0.1779491052563388</v>
       </c>
       <c r="T59">
-        <v>2.515928959970812</v>
+        <v>2.575832030446308</v>
       </c>
       <c r="U59">
         <v>0.1527366166625341</v>
       </c>
       <c r="V59">
-        <v>0.1026432605389284</v>
+        <v>0.1008735491503261</v>
       </c>
       <c r="W59">
-        <v>0.1370592323246072</v>
+        <v>0.1373295320545715</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6267,7 +6267,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.8211460843114269</v>
+        <v>0.8069883932026092</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6275,22 +6275,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1543897527993137</v>
+        <v>0.1882200217202431</v>
       </c>
       <c r="C60">
-        <v>99.50884901911286</v>
+        <v>-553.4686002891781</v>
       </c>
       <c r="D60">
-        <v>2614.207337131569</v>
+        <v>2011.419516928666</v>
       </c>
       <c r="E60">
-        <v>2545.435577573737</v>
+        <v>2595.625206679124</v>
       </c>
       <c r="F60">
-        <v>2910.998488112456</v>
+        <v>2961.188117217844</v>
       </c>
       <c r="G60">
         <v>396.3</v>
@@ -6311,45 +6311,45 @@
         <v>358.8</v>
       </c>
       <c r="M60">
-        <v>444.6160601840486</v>
+        <v>612.1860126549165</v>
       </c>
       <c r="N60">
-        <v>-85.81606018404858</v>
+        <v>-253.3860126549164</v>
       </c>
       <c r="O60">
-        <v>-10.72700752300607</v>
+        <v>-31.67325158186456</v>
       </c>
       <c r="P60">
-        <v>-75.0890526610425</v>
+        <v>-221.7127610730519</v>
       </c>
       <c r="Q60">
-        <v>-64.98905266104251</v>
+        <v>-211.6127610730519</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1779491052563387</v>
+        <v>0.1833695779560154</v>
       </c>
       <c r="T60">
-        <v>2.575832030446307</v>
+        <v>2.681487132483537</v>
       </c>
       <c r="U60">
-        <v>0.1527366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V60">
-        <v>0.1008735491503262</v>
+        <v>0.07326204629454924</v>
       </c>
       <c r="W60">
-        <v>0.1373295320545714</v>
+        <v>0.191590669081825</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y60">
-        <v>0.8069883932026093</v>
+        <v>0.5860963703563939</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6357,22 +6357,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1882200217202431</v>
+        <v>0.1898293878868684</v>
       </c>
       <c r="C61">
-        <v>-553.4686002891781</v>
+        <v>-625.4824429787614</v>
       </c>
       <c r="D61">
-        <v>2011.419516928666</v>
+        <v>1989.595303344469</v>
       </c>
       <c r="E61">
-        <v>2595.625206679124</v>
+        <v>2645.814835784512</v>
       </c>
       <c r="F61">
-        <v>2961.188117217844</v>
+        <v>3011.377746323231</v>
       </c>
       <c r="G61">
         <v>396.3</v>
@@ -6393,37 +6393,37 @@
         <v>358.8</v>
       </c>
       <c r="M61">
-        <v>612.1860126549165</v>
+        <v>622.5620467677116</v>
       </c>
       <c r="N61">
-        <v>-253.3860126549164</v>
+        <v>-263.7620467677116</v>
       </c>
       <c r="O61">
-        <v>-31.67325158186456</v>
+        <v>-32.97025584596395</v>
       </c>
       <c r="P61">
-        <v>-221.7127610730519</v>
+        <v>-230.7917909217477</v>
       </c>
       <c r="Q61">
-        <v>-211.6127610730519</v>
+        <v>-220.6917909217477</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1833695779560154</v>
+        <v>0.1868088174049158</v>
       </c>
       <c r="T61">
-        <v>2.681487132483537</v>
+        <v>2.748524310795626</v>
       </c>
       <c r="U61">
         <v>0.2067366166625341</v>
       </c>
       <c r="V61">
-        <v>0.07326204629454924</v>
+        <v>0.0720410121896401</v>
       </c>
       <c r="W61">
-        <v>0.191590669081825</v>
+        <v>0.1918431015415035</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6431,7 +6431,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.5860963703563939</v>
+        <v>0.5763280975171208</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6439,22 +6439,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1898293878868684</v>
+        <v>0.1914387540534938</v>
       </c>
       <c r="C62">
-        <v>-625.4824429787614</v>
+        <v>-697.0277768600599</v>
       </c>
       <c r="D62">
-        <v>1989.595303344469</v>
+        <v>1968.239598568558</v>
       </c>
       <c r="E62">
-        <v>2645.814835784512</v>
+        <v>2696.004464889899</v>
       </c>
       <c r="F62">
-        <v>3011.377746323231</v>
+        <v>3061.567375428618</v>
       </c>
       <c r="G62">
         <v>396.3</v>
@@ -6475,37 +6475,37 @@
         <v>358.8</v>
       </c>
       <c r="M62">
-        <v>622.5620467677116</v>
+        <v>632.9380808805068</v>
       </c>
       <c r="N62">
-        <v>-263.7620467677116</v>
+        <v>-274.1380808805068</v>
       </c>
       <c r="O62">
-        <v>-32.97025584596395</v>
+        <v>-34.26726011006335</v>
       </c>
       <c r="P62">
-        <v>-230.7917909217477</v>
+        <v>-239.8708207704435</v>
       </c>
       <c r="Q62">
-        <v>-220.6917909217477</v>
+        <v>-229.7708207704435</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1868088174049158</v>
+        <v>0.190424428107606</v>
       </c>
       <c r="T62">
-        <v>2.748524310795626</v>
+        <v>2.818999293123719</v>
       </c>
       <c r="U62">
         <v>0.2067366166625341</v>
       </c>
       <c r="V62">
-        <v>0.0720410121896401</v>
+        <v>0.07086001198980993</v>
       </c>
       <c r="W62">
-        <v>0.1918431015415035</v>
+        <v>0.1920872575270942</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6513,7 +6513,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.5763280975171208</v>
+        <v>0.5668800959184794</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6521,22 +6521,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1914387540534938</v>
+        <v>0.1930481202201191</v>
       </c>
       <c r="C63">
-        <v>-697.0277768600599</v>
+        <v>-768.1195282078852</v>
       </c>
       <c r="D63">
-        <v>1968.239598568558</v>
+        <v>1947.33747632612</v>
       </c>
       <c r="E63">
-        <v>2696.004464889899</v>
+        <v>2746.194093995286</v>
       </c>
       <c r="F63">
-        <v>3061.567375428618</v>
+        <v>3111.757004534005</v>
       </c>
       <c r="G63">
         <v>396.3</v>
@@ -6557,37 +6557,37 @@
         <v>358.8</v>
       </c>
       <c r="M63">
-        <v>632.9380808805068</v>
+        <v>643.314114993302</v>
       </c>
       <c r="N63">
-        <v>-274.1380808805068</v>
+        <v>-284.514114993302</v>
       </c>
       <c r="O63">
-        <v>-34.26726011006335</v>
+        <v>-35.56426437416275</v>
       </c>
       <c r="P63">
-        <v>-239.8708207704435</v>
+        <v>-248.9498506191393</v>
       </c>
       <c r="Q63">
-        <v>-229.7708207704435</v>
+        <v>-238.8498506191393</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.190424428107606</v>
+        <v>0.1942303341104377</v>
       </c>
       <c r="T63">
-        <v>2.818999293123719</v>
+        <v>2.893183485048028</v>
       </c>
       <c r="U63">
         <v>0.2067366166625341</v>
       </c>
       <c r="V63">
-        <v>0.07086001198980993</v>
+        <v>0.06971710857061944</v>
       </c>
       <c r="W63">
-        <v>0.1920872575270942</v>
+        <v>0.1923235375131497</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6595,7 +6595,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.5668800959184794</v>
+        <v>0.5577368685649555</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6603,22 +6603,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1930481202201191</v>
+        <v>0.1946574863867445</v>
       </c>
       <c r="C64">
-        <v>-768.1195282078852</v>
+        <v>-838.7719959092342</v>
       </c>
       <c r="D64">
-        <v>1947.33747632612</v>
+        <v>1926.874637730158</v>
       </c>
       <c r="E64">
-        <v>2746.194093995286</v>
+        <v>2796.383723100673</v>
       </c>
       <c r="F64">
-        <v>3111.757004534005</v>
+        <v>3161.946633639393</v>
       </c>
       <c r="G64">
         <v>396.3</v>
@@ -6639,37 +6639,37 @@
         <v>358.8</v>
       </c>
       <c r="M64">
-        <v>643.314114993302</v>
+        <v>653.6901491060972</v>
       </c>
       <c r="N64">
-        <v>-284.514114993302</v>
+        <v>-294.8901491060972</v>
       </c>
       <c r="O64">
-        <v>-35.56426437416275</v>
+        <v>-36.86126863826215</v>
       </c>
       <c r="P64">
-        <v>-248.9498506191393</v>
+        <v>-258.0288804678351</v>
       </c>
       <c r="Q64">
-        <v>-238.8498506191393</v>
+        <v>-247.9288804678351</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1942303341104377</v>
+        <v>0.1982419647620712</v>
       </c>
       <c r="T64">
-        <v>2.893183485048028</v>
+        <v>2.971377633292569</v>
       </c>
       <c r="U64">
         <v>0.2067366166625341</v>
       </c>
       <c r="V64">
-        <v>0.06971710857061944</v>
+        <v>0.06861048779965723</v>
       </c>
       <c r="W64">
-        <v>0.1923235375131497</v>
+        <v>0.1925523165472669</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6677,7 +6677,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.5577368685649555</v>
+        <v>0.5488839023972578</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6685,22 +6685,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1946574863867445</v>
+        <v>0.1962668525533698</v>
       </c>
       <c r="C65">
-        <v>-838.7719959092342</v>
+        <v>-908.9988840838105</v>
       </c>
       <c r="D65">
-        <v>1926.874637730158</v>
+        <v>1906.837378660969</v>
       </c>
       <c r="E65">
-        <v>2796.383723100673</v>
+        <v>2846.57335220606</v>
       </c>
       <c r="F65">
-        <v>3161.946633639393</v>
+        <v>3212.13626274478</v>
       </c>
       <c r="G65">
         <v>396.3</v>
@@ -6721,37 +6721,37 @@
         <v>358.8</v>
       </c>
       <c r="M65">
-        <v>653.6901491060972</v>
+        <v>664.0661832188924</v>
       </c>
       <c r="N65">
-        <v>-294.8901491060972</v>
+        <v>-305.2661832188924</v>
       </c>
       <c r="O65">
-        <v>-36.86126863826215</v>
+        <v>-38.15827290236155</v>
       </c>
       <c r="P65">
-        <v>-258.0288804678351</v>
+        <v>-267.1079103165309</v>
       </c>
       <c r="Q65">
-        <v>-247.9288804678351</v>
+        <v>-257.0079103165309</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1982419647620712</v>
+        <v>0.2024764637832398</v>
       </c>
       <c r="T65">
-        <v>2.971377633292569</v>
+        <v>3.053915900884029</v>
       </c>
       <c r="U65">
         <v>0.2067366166625341</v>
       </c>
       <c r="V65">
-        <v>0.06861048779965723</v>
+        <v>0.06753844892778758</v>
       </c>
       <c r="W65">
-        <v>0.1925523165472669</v>
+        <v>0.1927739462365679</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6759,7 +6759,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.5488839023972578</v>
+        <v>0.5403075914223008</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6767,22 +6767,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1962668525533698</v>
+        <v>0.1978762187199952</v>
       </c>
       <c r="C66">
-        <v>-908.9988840838105</v>
+        <v>-978.8133326902012</v>
       </c>
       <c r="D66">
-        <v>1906.837378660969</v>
+        <v>1887.212559159966</v>
       </c>
       <c r="E66">
-        <v>2846.57335220606</v>
+        <v>2896.762981311448</v>
       </c>
       <c r="F66">
-        <v>3212.13626274478</v>
+        <v>3262.325891850167</v>
       </c>
       <c r="G66">
         <v>396.3</v>
@@ -6803,37 +6803,37 @@
         <v>358.8</v>
       </c>
       <c r="M66">
-        <v>664.0661832188924</v>
+        <v>674.4422173316876</v>
       </c>
       <c r="N66">
-        <v>-305.2661832188924</v>
+        <v>-315.6422173316876</v>
       </c>
       <c r="O66">
-        <v>-38.15827290236155</v>
+        <v>-39.45527716646095</v>
       </c>
       <c r="P66">
-        <v>-267.1079103165309</v>
+        <v>-276.1869401652266</v>
       </c>
       <c r="Q66">
-        <v>-257.0079103165309</v>
+        <v>-266.0869401652266</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2024764637832398</v>
+        <v>0.2069529341770467</v>
       </c>
       <c r="T66">
-        <v>3.053915900884029</v>
+        <v>3.141170640909288</v>
       </c>
       <c r="U66">
         <v>0.2067366166625341</v>
       </c>
       <c r="V66">
-        <v>0.06753844892778758</v>
+        <v>0.06649939586736009</v>
       </c>
       <c r="W66">
-        <v>0.1927739462365679</v>
+        <v>0.1929887565508136</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6841,7 +6841,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.5403075914223008</v>
+        <v>0.5319951669388807</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6849,22 +6849,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1978762187199952</v>
+        <v>0.1994855848866205</v>
       </c>
       <c r="C67">
-        <v>-978.8133326902012</v>
+        <v>-1048.22794626135</v>
       </c>
       <c r="D67">
-        <v>1887.212559159966</v>
+        <v>1867.987574694204</v>
       </c>
       <c r="E67">
-        <v>2896.762981311448</v>
+        <v>2946.952610416835</v>
       </c>
       <c r="F67">
-        <v>3262.325891850167</v>
+        <v>3312.515520955554</v>
       </c>
       <c r="G67">
         <v>396.3</v>
@@ -6885,37 +6885,37 @@
         <v>358.8</v>
       </c>
       <c r="M67">
-        <v>674.4422173316876</v>
+        <v>684.8182514444828</v>
       </c>
       <c r="N67">
-        <v>-315.6422173316876</v>
+        <v>-326.0182514444828</v>
       </c>
       <c r="O67">
-        <v>-39.45527716646095</v>
+        <v>-40.75228143056035</v>
       </c>
       <c r="P67">
-        <v>-276.1869401652266</v>
+        <v>-285.2659700139225</v>
       </c>
       <c r="Q67">
-        <v>-266.0869401652266</v>
+        <v>-275.1659700139224</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2069529341770467</v>
+        <v>0.2116927263587246</v>
       </c>
       <c r="T67">
-        <v>3.141170640909288</v>
+        <v>3.233558012700737</v>
       </c>
       <c r="U67">
         <v>0.2067366166625341</v>
       </c>
       <c r="V67">
-        <v>0.06649939586736009</v>
+        <v>0.06549182926330918</v>
       </c>
       <c r="W67">
-        <v>0.1929887565508136</v>
+        <v>0.1931970574615972</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6923,7 +6923,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.5319951669388807</v>
+        <v>0.5239346341064735</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6931,22 +6931,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1994855848866205</v>
+        <v>0.2010949510532459</v>
       </c>
       <c r="C68">
-        <v>-1048.22794626135</v>
+        <v>-1117.254820901377</v>
       </c>
       <c r="D68">
-        <v>1867.987574694204</v>
+        <v>1849.150329159565</v>
       </c>
       <c r="E68">
-        <v>2946.952610416835</v>
+        <v>2997.142239522222</v>
       </c>
       <c r="F68">
-        <v>3312.515520955554</v>
+        <v>3362.705150060941</v>
       </c>
       <c r="G68">
         <v>396.3</v>
@@ -6967,37 +6967,37 @@
         <v>358.8</v>
       </c>
       <c r="M68">
-        <v>684.8182514444828</v>
+        <v>695.194285557278</v>
       </c>
       <c r="N68">
-        <v>-326.0182514444828</v>
+        <v>-336.394285557278</v>
       </c>
       <c r="O68">
-        <v>-40.75228143056035</v>
+        <v>-42.04928569465975</v>
       </c>
       <c r="P68">
-        <v>-285.2659700139225</v>
+        <v>-294.3449998626182</v>
       </c>
       <c r="Q68">
-        <v>-275.1659700139224</v>
+        <v>-284.2449998626182</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2116927263587246</v>
+        <v>0.2167197786726253</v>
       </c>
       <c r="T68">
-        <v>3.233558012700737</v>
+        <v>3.331544619146214</v>
       </c>
       <c r="U68">
         <v>0.2067366166625341</v>
       </c>
       <c r="V68">
-        <v>0.06549182926330918</v>
+        <v>0.06451433927430456</v>
       </c>
       <c r="W68">
-        <v>0.1931970574615972</v>
+        <v>0.1933991404347455</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -7005,7 +7005,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.5239346341064735</v>
+        <v>0.5161147141944364</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7013,22 +7013,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2010949510532459</v>
+        <v>0.2027043172198712</v>
       </c>
       <c r="C69">
-        <v>-1117.254820901377</v>
+        <v>-1185.905569665245</v>
       </c>
       <c r="D69">
-        <v>1849.150329159565</v>
+        <v>1830.689209501083</v>
       </c>
       <c r="E69">
-        <v>2997.142239522222</v>
+        <v>3047.331868627609</v>
       </c>
       <c r="F69">
-        <v>3362.705150060941</v>
+        <v>3412.894779166329</v>
       </c>
       <c r="G69">
         <v>396.3</v>
@@ -7049,37 +7049,37 @@
         <v>358.8</v>
       </c>
       <c r="M69">
-        <v>695.194285557278</v>
+        <v>705.5703196700732</v>
       </c>
       <c r="N69">
-        <v>-336.394285557278</v>
+        <v>-346.7703196700732</v>
       </c>
       <c r="O69">
-        <v>-42.04928569465975</v>
+        <v>-43.34628995875915</v>
       </c>
       <c r="P69">
-        <v>-294.3449998626182</v>
+        <v>-303.4240297113141</v>
       </c>
       <c r="Q69">
-        <v>-284.2449998626182</v>
+        <v>-293.324029711314</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2167197786726253</v>
+        <v>0.2220610217561448</v>
       </c>
       <c r="T69">
-        <v>3.331544619146214</v>
+        <v>3.435655388494533</v>
       </c>
       <c r="U69">
         <v>0.2067366166625341</v>
       </c>
       <c r="V69">
-        <v>0.06451433927430456</v>
+        <v>0.06356559899085891</v>
       </c>
       <c r="W69">
-        <v>0.1933991404347455</v>
+        <v>0.1935952797910365</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -7087,7 +7087,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.5161147141944364</v>
+        <v>0.5085247919268712</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7095,22 +7095,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2027043172198712</v>
+        <v>0.2043136833864965</v>
       </c>
       <c r="C70">
-        <v>-1185.905569665245</v>
+        <v>-1254.191346433188</v>
       </c>
       <c r="D70">
-        <v>1830.689209501083</v>
+        <v>1812.593061838528</v>
       </c>
       <c r="E70">
-        <v>3047.331868627609</v>
+        <v>3097.521497732997</v>
       </c>
       <c r="F70">
-        <v>3412.894779166329</v>
+        <v>3463.084408271716</v>
       </c>
       <c r="G70">
         <v>396.3</v>
@@ -7131,37 +7131,37 @@
         <v>358.8</v>
       </c>
       <c r="M70">
-        <v>705.5703196700732</v>
+        <v>715.9463537828684</v>
       </c>
       <c r="N70">
-        <v>-346.7703196700732</v>
+        <v>-357.1463537828684</v>
       </c>
       <c r="O70">
-        <v>-43.34628995875915</v>
+        <v>-44.64329422285855</v>
       </c>
       <c r="P70">
-        <v>-303.4240297113141</v>
+        <v>-312.5030595600098</v>
       </c>
       <c r="Q70">
-        <v>-293.324029711314</v>
+        <v>-302.4030595600098</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2220610217561448</v>
+        <v>0.2277468611676334</v>
       </c>
       <c r="T70">
-        <v>3.435655388494533</v>
+        <v>3.546482981671776</v>
       </c>
       <c r="U70">
         <v>0.2067366166625341</v>
       </c>
       <c r="V70">
-        <v>0.06356559899085891</v>
+        <v>0.062644358425774</v>
       </c>
       <c r="W70">
-        <v>0.1935952797910365</v>
+        <v>0.1937857339485945</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7169,7 +7169,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.5085247919268712</v>
+        <v>0.501154867406192</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7177,22 +7177,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2043136833864965</v>
+        <v>0.2307919871595789</v>
       </c>
       <c r="C71">
-        <v>-1254.191346433188</v>
+        <v>-1557.931627821986</v>
       </c>
       <c r="D71">
-        <v>1812.593061838528</v>
+        <v>1559.042409555118</v>
       </c>
       <c r="E71">
-        <v>3097.521497732997</v>
+        <v>3147.711126838384</v>
       </c>
       <c r="F71">
-        <v>3463.084408271716</v>
+        <v>3513.274037377103</v>
       </c>
       <c r="G71">
         <v>396.3</v>
@@ -7213,45 +7213,45 @@
         <v>358.8</v>
       </c>
       <c r="M71">
-        <v>715.9463537828684</v>
+        <v>849.2869792038623</v>
       </c>
       <c r="N71">
-        <v>-357.1463537828684</v>
+        <v>-490.4869792038623</v>
       </c>
       <c r="O71">
-        <v>-44.64329422285855</v>
+        <v>-61.31087240048279</v>
       </c>
       <c r="P71">
-        <v>-312.5030595600098</v>
+        <v>-429.1761068033795</v>
       </c>
       <c r="Q71">
-        <v>-302.4030595600098</v>
+        <v>-419.0761068033795</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2277468611676334</v>
+        <v>0.2350415485614113</v>
       </c>
       <c r="T71">
-        <v>3.546482981671776</v>
+        <v>3.688670016571013</v>
       </c>
       <c r="U71">
-        <v>0.2067366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V71">
-        <v>0.062644358425774</v>
+        <v>0.05280900461001208</v>
       </c>
       <c r="W71">
-        <v>0.1937857339485945</v>
+        <v>0.2289707465587936</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y71">
-        <v>0.501154867406192</v>
+        <v>0.4224720368800967</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7259,22 +7259,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2307919871595789</v>
+        <v>0.2327513533262042</v>
       </c>
       <c r="C72">
-        <v>-1557.931627821986</v>
+        <v>-1624.093850434229</v>
       </c>
       <c r="D72">
-        <v>1559.042409555118</v>
+        <v>1543.069816048261</v>
       </c>
       <c r="E72">
-        <v>3147.711126838384</v>
+        <v>3197.900755943771</v>
       </c>
       <c r="F72">
-        <v>3513.274037377103</v>
+        <v>3563.463666482491</v>
       </c>
       <c r="G72">
         <v>396.3</v>
@@ -7295,37 +7295,37 @@
         <v>358.8</v>
       </c>
       <c r="M72">
-        <v>849.2869792038623</v>
+        <v>861.4196503353461</v>
       </c>
       <c r="N72">
-        <v>-490.4869792038623</v>
+        <v>-502.6196503353461</v>
       </c>
       <c r="O72">
-        <v>-61.31087240048279</v>
+        <v>-62.82745629191826</v>
       </c>
       <c r="P72">
-        <v>-429.1761068033795</v>
+        <v>-439.7921940434278</v>
       </c>
       <c r="Q72">
-        <v>-419.0761068033795</v>
+        <v>-429.6921940434278</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2350415485614113</v>
+        <v>0.2415671192014599</v>
       </c>
       <c r="T72">
-        <v>3.688670016571013</v>
+        <v>3.815865534383807</v>
       </c>
       <c r="U72">
         <v>0.2417366166625341</v>
       </c>
       <c r="V72">
-        <v>0.05280900461001208</v>
+        <v>0.05206521581268797</v>
       </c>
       <c r="W72">
-        <v>0.2289707465587936</v>
+        <v>0.2291505475461702</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7333,7 +7333,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.4224720368800967</v>
+        <v>0.4165217265015038</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7341,22 +7341,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2327513533262042</v>
+        <v>0.2347107194928296</v>
       </c>
       <c r="C73">
-        <v>-1624.093850434228</v>
+        <v>-1689.932109474265</v>
       </c>
       <c r="D73">
-        <v>1543.069816048261</v>
+        <v>1527.421186113612</v>
       </c>
       <c r="E73">
-        <v>3197.90075594377</v>
+        <v>3248.090385049158</v>
       </c>
       <c r="F73">
-        <v>3563.46366648249</v>
+        <v>3613.653295587877</v>
       </c>
       <c r="G73">
         <v>396.3</v>
@@ -7377,37 +7377,37 @@
         <v>358.8</v>
       </c>
       <c r="M73">
-        <v>861.4196503353459</v>
+        <v>873.5523214668297</v>
       </c>
       <c r="N73">
-        <v>-502.6196503353459</v>
+        <v>-514.7523214668297</v>
       </c>
       <c r="O73">
-        <v>-62.82745629191823</v>
+        <v>-64.34404018335371</v>
       </c>
       <c r="P73">
-        <v>-439.7921940434276</v>
+        <v>-450.408281283476</v>
       </c>
       <c r="Q73">
-        <v>-429.6921940434276</v>
+        <v>-440.3082812834759</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2415671192014599</v>
+        <v>0.2485588020300835</v>
       </c>
       <c r="T73">
-        <v>3.815865534383805</v>
+        <v>3.952146446326084</v>
       </c>
       <c r="U73">
         <v>0.2417366166625341</v>
       </c>
       <c r="V73">
-        <v>0.05206521581268798</v>
+        <v>0.05134208781528953</v>
       </c>
       <c r="W73">
-        <v>0.2291505475461702</v>
+        <v>0.2293253540616753</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7415,7 +7415,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.4165217265015039</v>
+        <v>0.4107367025223162</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7423,22 +7423,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2347107194928296</v>
+        <v>0.2366700856594549</v>
       </c>
       <c r="C74">
-        <v>-1689.932109474265</v>
+        <v>-1755.456162161689</v>
       </c>
       <c r="D74">
-        <v>1527.421186113612</v>
+        <v>1512.086762531575</v>
       </c>
       <c r="E74">
-        <v>3248.090385049158</v>
+        <v>3298.280014154545</v>
       </c>
       <c r="F74">
-        <v>3613.653295587877</v>
+        <v>3663.842924693264</v>
       </c>
       <c r="G74">
         <v>396.3</v>
@@ -7459,37 +7459,37 @@
         <v>358.8</v>
       </c>
       <c r="M74">
-        <v>873.5523214668297</v>
+        <v>885.6849925983134</v>
       </c>
       <c r="N74">
-        <v>-514.7523214668297</v>
+        <v>-526.8849925983134</v>
       </c>
       <c r="O74">
-        <v>-64.34404018335371</v>
+        <v>-65.86062407478917</v>
       </c>
       <c r="P74">
-        <v>-450.408281283476</v>
+        <v>-461.0243685235242</v>
       </c>
       <c r="Q74">
-        <v>-440.3082812834759</v>
+        <v>-450.9243685235242</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2485588020300835</v>
+        <v>0.2560683872904569</v>
       </c>
       <c r="T74">
-        <v>3.952146446326084</v>
+        <v>4.098522240634457</v>
       </c>
       <c r="U74">
         <v>0.2417366166625341</v>
       </c>
       <c r="V74">
-        <v>0.05134208781528953</v>
+        <v>0.05063877154384721</v>
       </c>
       <c r="W74">
-        <v>0.2293253540616753</v>
+        <v>0.2294953713575775</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7497,7 +7497,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.4107367025223162</v>
+        <v>0.4051101723507777</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7505,22 +7505,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2366700856594549</v>
+        <v>0.2386294518260803</v>
       </c>
       <c r="C75">
-        <v>-1755.456162161689</v>
+        <v>-1820.675377783391</v>
       </c>
       <c r="D75">
-        <v>1512.086762531575</v>
+        <v>1497.057176015261</v>
       </c>
       <c r="E75">
-        <v>3298.280014154545</v>
+        <v>3348.469643259932</v>
       </c>
       <c r="F75">
-        <v>3663.842924693264</v>
+        <v>3714.032553798651</v>
       </c>
       <c r="G75">
         <v>396.3</v>
@@ -7541,37 +7541,37 @@
         <v>358.8</v>
       </c>
       <c r="M75">
-        <v>885.6849925983134</v>
+        <v>897.8176637297971</v>
       </c>
       <c r="N75">
-        <v>-526.8849925983134</v>
+        <v>-539.0176637297971</v>
       </c>
       <c r="O75">
-        <v>-65.86062407478917</v>
+        <v>-67.37720796622463</v>
       </c>
       <c r="P75">
-        <v>-461.0243685235242</v>
+        <v>-471.6404557635724</v>
       </c>
       <c r="Q75">
-        <v>-450.9243685235242</v>
+        <v>-461.5404557635724</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2560683872904569</v>
+        <v>0.2641556329554745</v>
       </c>
       <c r="T75">
-        <v>4.098522240634457</v>
+        <v>4.256157711428091</v>
       </c>
       <c r="U75">
         <v>0.2417366166625341</v>
       </c>
       <c r="V75">
-        <v>0.05063877154384721</v>
+        <v>0.04995446382028171</v>
       </c>
       <c r="W75">
-        <v>0.2294953713575775</v>
+        <v>0.2296607935914282</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7579,7 +7579,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.4051101723507777</v>
+        <v>0.3996357105622538</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7587,22 +7587,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2386294518260803</v>
+        <v>0.2405888179927056</v>
       </c>
       <c r="C76">
-        <v>-1820.675377783391</v>
+        <v>-1885.598756783354</v>
       </c>
       <c r="D76">
-        <v>1497.057176015261</v>
+        <v>1482.323426120685</v>
       </c>
       <c r="E76">
-        <v>3348.469643259932</v>
+        <v>3398.65927236532</v>
       </c>
       <c r="F76">
-        <v>3714.032553798651</v>
+        <v>3764.222182904039</v>
       </c>
       <c r="G76">
         <v>396.3</v>
@@ -7623,37 +7623,37 @@
         <v>358.8</v>
       </c>
       <c r="M76">
-        <v>897.8176637297971</v>
+        <v>909.950334861281</v>
       </c>
       <c r="N76">
-        <v>-539.0176637297971</v>
+        <v>-551.150334861281</v>
       </c>
       <c r="O76">
-        <v>-67.37720796622463</v>
+        <v>-68.89379185766012</v>
       </c>
       <c r="P76">
-        <v>-471.6404557635724</v>
+        <v>-482.2565430036208</v>
       </c>
       <c r="Q76">
-        <v>-461.5404557635724</v>
+        <v>-472.1565430036208</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2641556329554745</v>
+        <v>0.2728898582736934</v>
       </c>
       <c r="T76">
-        <v>4.256157711428091</v>
+        <v>4.426404019885214</v>
       </c>
       <c r="U76">
         <v>0.2417366166625341</v>
       </c>
       <c r="V76">
-        <v>0.04995446382028171</v>
+        <v>0.04928840430267795</v>
       </c>
       <c r="W76">
-        <v>0.2296607935914282</v>
+        <v>0.2298218045657096</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7661,7 +7661,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.3996357105622538</v>
+        <v>0.3943072344214237</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7669,22 +7669,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2405888179927056</v>
+        <v>0.2425481841593309</v>
       </c>
       <c r="C77">
-        <v>-1885.598756783354</v>
+        <v>-1950.234948736173</v>
       </c>
       <c r="D77">
-        <v>1482.323426120685</v>
+        <v>1467.876863273253</v>
       </c>
       <c r="E77">
-        <v>3398.65927236532</v>
+        <v>3448.848901470707</v>
       </c>
       <c r="F77">
-        <v>3764.222182904039</v>
+        <v>3814.411812009426</v>
       </c>
       <c r="G77">
         <v>396.3</v>
@@ -7705,37 +7705,37 @@
         <v>358.8</v>
       </c>
       <c r="M77">
-        <v>909.950334861281</v>
+        <v>922.0830059927648</v>
       </c>
       <c r="N77">
-        <v>-551.150334861281</v>
+        <v>-563.2830059927649</v>
       </c>
       <c r="O77">
-        <v>-68.89379185766012</v>
+        <v>-70.41037574909561</v>
       </c>
       <c r="P77">
-        <v>-482.2565430036208</v>
+        <v>-492.8726302436693</v>
       </c>
       <c r="Q77">
-        <v>-472.1565430036208</v>
+        <v>-482.7726302436693</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2728898582736934</v>
+        <v>0.282351935701764</v>
       </c>
       <c r="T77">
-        <v>4.426404019885214</v>
+        <v>4.610837520713766</v>
       </c>
       <c r="U77">
         <v>0.2417366166625341</v>
       </c>
       <c r="V77">
-        <v>0.04928840430267795</v>
+        <v>0.04863987266711639</v>
       </c>
       <c r="W77">
-        <v>0.2298218045657096</v>
+        <v>0.2299785784090889</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7743,7 +7743,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.3943072344214237</v>
+        <v>0.3891189813369311</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7751,22 +7751,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2425481841593309</v>
+        <v>0.2445075503259563</v>
       </c>
       <c r="C78">
-        <v>-1950.234948736173</v>
+        <v>-2014.5922692797</v>
       </c>
       <c r="D78">
-        <v>1467.876863273253</v>
+        <v>1453.709171835113</v>
       </c>
       <c r="E78">
-        <v>3448.848901470707</v>
+        <v>3499.038530576094</v>
       </c>
       <c r="F78">
-        <v>3814.411812009426</v>
+        <v>3864.601441114813</v>
       </c>
       <c r="G78">
         <v>396.3</v>
@@ -7787,37 +7787,37 @@
         <v>358.8</v>
       </c>
       <c r="M78">
-        <v>922.0830059927648</v>
+        <v>934.2156771242485</v>
       </c>
       <c r="N78">
-        <v>-563.2830059927649</v>
+        <v>-575.4156771242485</v>
       </c>
       <c r="O78">
-        <v>-70.41037574909561</v>
+        <v>-71.92695964053107</v>
       </c>
       <c r="P78">
-        <v>-492.8726302436693</v>
+        <v>-503.4887174837174</v>
       </c>
       <c r="Q78">
-        <v>-482.7726302436693</v>
+        <v>-493.3887174837174</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.282351935701764</v>
+        <v>0.2926368024714059</v>
       </c>
       <c r="T78">
-        <v>4.610837520713766</v>
+        <v>4.811308717266536</v>
       </c>
       <c r="U78">
         <v>0.2417366166625341</v>
       </c>
       <c r="V78">
-        <v>0.04863987266711639</v>
+        <v>0.04800818600910189</v>
       </c>
       <c r="W78">
-        <v>0.2299785784090889</v>
+        <v>0.2301312802045882</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7825,7 +7825,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.3891189813369311</v>
+        <v>0.3840654880728152</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7833,22 +7833,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2445075503259563</v>
+        <v>0.2464669164925816</v>
       </c>
       <c r="C79">
-        <v>-2014.5922692797</v>
+        <v>-2078.678716076486</v>
       </c>
       <c r="D79">
-        <v>1453.709171835113</v>
+        <v>1439.812354143715</v>
       </c>
       <c r="E79">
-        <v>3499.038530576094</v>
+        <v>3549.228159681481</v>
       </c>
       <c r="F79">
-        <v>3864.601441114813</v>
+        <v>3914.791070220201</v>
       </c>
       <c r="G79">
         <v>396.3</v>
@@ -7869,37 +7869,37 @@
         <v>358.8</v>
       </c>
       <c r="M79">
-        <v>934.2156771242485</v>
+        <v>946.3483482557323</v>
       </c>
       <c r="N79">
-        <v>-575.4156771242485</v>
+        <v>-587.5483482557322</v>
       </c>
       <c r="O79">
-        <v>-71.92695964053107</v>
+        <v>-73.44354353196653</v>
       </c>
       <c r="P79">
-        <v>-503.4887174837174</v>
+        <v>-514.1048047237657</v>
       </c>
       <c r="Q79">
-        <v>-493.3887174837174</v>
+        <v>-504.0048047237657</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2926368024714059</v>
+        <v>0.3038566571291972</v>
       </c>
       <c r="T79">
-        <v>4.811308717266536</v>
+        <v>5.030004568051381</v>
       </c>
       <c r="U79">
         <v>0.2417366166625341</v>
       </c>
       <c r="V79">
-        <v>0.04800818600910189</v>
+        <v>0.04739269644488264</v>
       </c>
       <c r="W79">
-        <v>0.2301312802045882</v>
+        <v>0.2302800665694337</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7907,7 +7907,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.3840654880728152</v>
+        <v>0.3791415715590611</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7915,22 +7915,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2464669164925816</v>
+        <v>0.248426282659207</v>
       </c>
       <c r="C80">
-        <v>-2078.678716076486</v>
+        <v>-2142.501983868381</v>
       </c>
       <c r="D80">
-        <v>1439.812354143715</v>
+        <v>1426.178715457207</v>
       </c>
       <c r="E80">
-        <v>3549.228159681481</v>
+        <v>3599.417788786869</v>
       </c>
       <c r="F80">
-        <v>3914.791070220201</v>
+        <v>3964.980699325588</v>
       </c>
       <c r="G80">
         <v>396.3</v>
@@ -7951,37 +7951,37 @@
         <v>358.8</v>
       </c>
       <c r="M80">
-        <v>946.3483482557323</v>
+        <v>958.4810193872161</v>
       </c>
       <c r="N80">
-        <v>-587.5483482557322</v>
+        <v>-599.6810193872161</v>
       </c>
       <c r="O80">
-        <v>-73.44354353196653</v>
+        <v>-74.96012742340201</v>
       </c>
       <c r="P80">
-        <v>-514.1048047237657</v>
+        <v>-524.7208919638141</v>
       </c>
       <c r="Q80">
-        <v>-504.0048047237657</v>
+        <v>-514.6208919638141</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3038566571291972</v>
+        <v>0.3161450693734447</v>
       </c>
       <c r="T80">
-        <v>5.030004568051381</v>
+        <v>5.269528595101447</v>
       </c>
       <c r="U80">
         <v>0.2417366166625341</v>
       </c>
       <c r="V80">
-        <v>0.04739269644488264</v>
+        <v>0.04679278889494742</v>
       </c>
       <c r="W80">
-        <v>0.2302800665694337</v>
+        <v>0.2304250861908653</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7989,7 +7989,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.3791415715590611</v>
+        <v>0.3743423111595793</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7997,22 +7997,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.248426282659207</v>
+        <v>0.2503856488258323</v>
       </c>
       <c r="C81">
-        <v>-2142.501983868381</v>
+        <v>-2206.069478683843</v>
       </c>
       <c r="D81">
-        <v>1426.178715457207</v>
+        <v>1412.800849747132</v>
       </c>
       <c r="E81">
-        <v>3599.417788786869</v>
+        <v>3649.607417892256</v>
       </c>
       <c r="F81">
-        <v>3964.980699325588</v>
+        <v>4015.170328430975</v>
       </c>
       <c r="G81">
         <v>396.3</v>
@@ -8033,37 +8033,37 @@
         <v>358.8</v>
       </c>
       <c r="M81">
-        <v>958.4810193872161</v>
+        <v>970.6136905186997</v>
       </c>
       <c r="N81">
-        <v>-599.6810193872161</v>
+        <v>-611.8136905186998</v>
       </c>
       <c r="O81">
-        <v>-74.96012742340201</v>
+        <v>-76.47671131483747</v>
       </c>
       <c r="P81">
-        <v>-524.7208919638141</v>
+        <v>-535.3369792038623</v>
       </c>
       <c r="Q81">
-        <v>-514.6208919638141</v>
+        <v>-525.2369792038622</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3161450693734447</v>
+        <v>0.3296623228421169</v>
       </c>
       <c r="T81">
-        <v>5.269528595101447</v>
+        <v>5.533005024856519</v>
       </c>
       <c r="U81">
         <v>0.2417366166625341</v>
       </c>
       <c r="V81">
-        <v>0.04679278889494742</v>
+        <v>0.04620787903376058</v>
       </c>
       <c r="W81">
-        <v>0.2304250861908653</v>
+        <v>0.2305664803217612</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -8071,7 +8071,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3743423111595793</v>
+        <v>0.3696630322700846</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8079,22 +8079,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2503856488258323</v>
+        <v>0.2523450149924577</v>
       </c>
       <c r="C82">
-        <v>-2206.069478683843</v>
+        <v>-2269.388331253078</v>
       </c>
       <c r="D82">
-        <v>1412.800849747132</v>
+        <v>1399.671626283284</v>
       </c>
       <c r="E82">
-        <v>3649.607417892256</v>
+        <v>3699.797046997643</v>
       </c>
       <c r="F82">
-        <v>4015.170328430975</v>
+        <v>4065.359957536362</v>
       </c>
       <c r="G82">
         <v>396.3</v>
@@ -8115,37 +8115,37 @@
         <v>358.8</v>
       </c>
       <c r="M82">
-        <v>970.6136905186997</v>
+        <v>982.7463616501835</v>
       </c>
       <c r="N82">
-        <v>-611.8136905186998</v>
+        <v>-623.9463616501835</v>
       </c>
       <c r="O82">
-        <v>-76.47671131483747</v>
+        <v>-77.99329520627293</v>
       </c>
       <c r="P82">
-        <v>-535.3369792038623</v>
+        <v>-545.9530664439105</v>
       </c>
       <c r="Q82">
-        <v>-525.2369792038622</v>
+        <v>-535.8530664439105</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3296623228421169</v>
+        <v>0.3446024450969651</v>
       </c>
       <c r="T82">
-        <v>5.533005024856519</v>
+        <v>5.824215815638441</v>
       </c>
       <c r="U82">
         <v>0.2417366166625341</v>
       </c>
       <c r="V82">
-        <v>0.04620787903376058</v>
+        <v>0.04563741139136847</v>
       </c>
       <c r="W82">
-        <v>0.2305664803217612</v>
+        <v>0.2307043832395485</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8153,7 +8153,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.3696630322700846</v>
+        <v>0.3650992911309477</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8161,22 +8161,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2523450149924577</v>
+        <v>0.254304381159083</v>
       </c>
       <c r="C83">
-        <v>-2269.388331253078</v>
+        <v>-2332.465409682049</v>
       </c>
       <c r="D83">
-        <v>1399.671626283284</v>
+        <v>1386.784176959701</v>
       </c>
       <c r="E83">
-        <v>3699.797046997643</v>
+        <v>3749.98667610303</v>
       </c>
       <c r="F83">
-        <v>4065.359957536362</v>
+        <v>4115.54958664175</v>
       </c>
       <c r="G83">
         <v>396.3</v>
@@ -8197,37 +8197,37 @@
         <v>358.8</v>
       </c>
       <c r="M83">
-        <v>982.7463616501835</v>
+        <v>994.8790327816673</v>
       </c>
       <c r="N83">
-        <v>-623.9463616501835</v>
+        <v>-636.0790327816674</v>
       </c>
       <c r="O83">
-        <v>-77.99329520627293</v>
+        <v>-79.50987909770842</v>
       </c>
       <c r="P83">
-        <v>-545.9530664439105</v>
+        <v>-556.5691536839589</v>
       </c>
       <c r="Q83">
-        <v>-535.8530664439105</v>
+        <v>-546.4691536839589</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3446024450969651</v>
+        <v>0.3612025809356855</v>
       </c>
       <c r="T83">
-        <v>5.824215815638441</v>
+        <v>6.147783360951689</v>
       </c>
       <c r="U83">
         <v>0.2417366166625341</v>
       </c>
       <c r="V83">
-        <v>0.04563741139136847</v>
+        <v>0.04508085759391275</v>
       </c>
       <c r="W83">
-        <v>0.2307043832395485</v>
+        <v>0.2308389226715361</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8235,7 +8235,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3650992911309477</v>
+        <v>0.3606468607513019</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8243,22 +8243,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.254304381159083</v>
+        <v>0.2562637473257083</v>
       </c>
       <c r="C84">
-        <v>-2332.465409682049</v>
+        <v>-2395.30733143271</v>
       </c>
       <c r="D84">
-        <v>1386.784176959701</v>
+        <v>1374.131884314427</v>
       </c>
       <c r="E84">
-        <v>3749.98667610303</v>
+        <v>3800.176305208417</v>
       </c>
       <c r="F84">
-        <v>4115.54958664175</v>
+        <v>4165.739215747137</v>
       </c>
       <c r="G84">
         <v>396.3</v>
@@ -8279,37 +8279,37 @@
         <v>358.8</v>
       </c>
       <c r="M84">
-        <v>994.8790327816673</v>
+        <v>1007.011703913151</v>
       </c>
       <c r="N84">
-        <v>-636.0790327816674</v>
+        <v>-648.211703913151</v>
       </c>
       <c r="O84">
-        <v>-79.50987909770842</v>
+        <v>-81.02646298914388</v>
       </c>
       <c r="P84">
-        <v>-556.5691536839589</v>
+        <v>-567.1852409240072</v>
       </c>
       <c r="Q84">
-        <v>-546.4691536839589</v>
+        <v>-557.0852409240072</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3612025809356855</v>
+        <v>0.3797556739319023</v>
       </c>
       <c r="T84">
-        <v>6.147783360951689</v>
+        <v>6.509417676301789</v>
       </c>
       <c r="U84">
         <v>0.2417366166625341</v>
       </c>
       <c r="V84">
-        <v>0.04508085759391275</v>
+        <v>0.04453771473133549</v>
       </c>
       <c r="W84">
-        <v>0.2308389226715361</v>
+        <v>0.2309702201894999</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8317,7 +8317,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3606468607513019</v>
+        <v>0.3563017178506839</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8325,22 +8325,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2562637473257083</v>
+        <v>0.2582231134923337</v>
       </c>
       <c r="C85">
-        <v>-2395.30733143271</v>
+        <v>-2457.920474653358</v>
       </c>
       <c r="D85">
-        <v>1374.131884314427</v>
+        <v>1361.708370199166</v>
       </c>
       <c r="E85">
-        <v>3800.176305208417</v>
+        <v>3850.365934313805</v>
       </c>
       <c r="F85">
-        <v>4165.739215747137</v>
+        <v>4215.928844852524</v>
       </c>
       <c r="G85">
         <v>396.3</v>
@@ -8361,37 +8361,37 @@
         <v>358.8</v>
       </c>
       <c r="M85">
-        <v>1007.011703913151</v>
+        <v>1019.144375044635</v>
       </c>
       <c r="N85">
-        <v>-648.211703913151</v>
+        <v>-660.3443750446347</v>
       </c>
       <c r="O85">
-        <v>-81.02646298914388</v>
+        <v>-82.54304688057934</v>
       </c>
       <c r="P85">
-        <v>-567.1852409240072</v>
+        <v>-577.8013281640553</v>
       </c>
       <c r="Q85">
-        <v>-557.0852409240072</v>
+        <v>-567.7013281640553</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3797556739319023</v>
+        <v>0.4006279035526463</v>
       </c>
       <c r="T85">
-        <v>6.509417676301789</v>
+        <v>6.916256281070652</v>
       </c>
       <c r="U85">
         <v>0.2417366166625341</v>
       </c>
       <c r="V85">
-        <v>0.04453771473133549</v>
+        <v>0.04400750384167674</v>
       </c>
       <c r="W85">
-        <v>0.2309702201894999</v>
+        <v>0.2310983915760837</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8399,7 +8399,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3563017178506839</v>
+        <v>0.352060030733414</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8407,22 +8407,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2582231134923337</v>
+        <v>0.260182479658959</v>
       </c>
       <c r="C86">
-        <v>-2457.920474653357</v>
+        <v>-2520.310988899863</v>
       </c>
       <c r="D86">
-        <v>1361.708370199166</v>
+        <v>1349.507485058047</v>
       </c>
       <c r="E86">
-        <v>3850.365934313804</v>
+        <v>3900.555563419191</v>
       </c>
       <c r="F86">
-        <v>4215.928844852523</v>
+        <v>4266.11847395791</v>
       </c>
       <c r="G86">
         <v>396.3</v>
@@ -8443,37 +8443,37 @@
         <v>358.8</v>
       </c>
       <c r="M86">
-        <v>1019.144375044635</v>
+        <v>1031.277046176118</v>
       </c>
       <c r="N86">
-        <v>-660.3443750446345</v>
+        <v>-672.4770461761184</v>
       </c>
       <c r="O86">
-        <v>-82.54304688057931</v>
+        <v>-84.0596307720148</v>
       </c>
       <c r="P86">
-        <v>-577.8013281640551</v>
+        <v>-588.4174154041036</v>
       </c>
       <c r="Q86">
-        <v>-567.7013281640551</v>
+        <v>-578.3174154041036</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.400627903552646</v>
+        <v>0.4242830971228224</v>
       </c>
       <c r="T86">
-        <v>6.916256281070646</v>
+        <v>7.377340033142024</v>
       </c>
       <c r="U86">
         <v>0.2417366166625341</v>
       </c>
       <c r="V86">
-        <v>0.04400750384167675</v>
+        <v>0.0434897685023629</v>
       </c>
       <c r="W86">
-        <v>0.2310983915760837</v>
+        <v>0.2312235471653361</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8481,7 +8481,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3520600307334141</v>
+        <v>0.3479181480189032</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8489,22 +8489,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.260182479658959</v>
+        <v>0.2621418458255843</v>
       </c>
       <c r="C87">
-        <v>-2520.310988899863</v>
+        <v>-2582.484805285649</v>
       </c>
       <c r="D87">
-        <v>1349.507485058047</v>
+        <v>1337.523297777648</v>
       </c>
       <c r="E87">
-        <v>3900.555563419191</v>
+        <v>3950.745192524578</v>
       </c>
       <c r="F87">
-        <v>4266.11847395791</v>
+        <v>4316.308103063297</v>
       </c>
       <c r="G87">
         <v>396.3</v>
@@ -8525,37 +8525,37 @@
         <v>358.8</v>
       </c>
       <c r="M87">
-        <v>1031.277046176118</v>
+        <v>1043.409717307602</v>
       </c>
       <c r="N87">
-        <v>-672.4770461761184</v>
+        <v>-684.6097173076021</v>
       </c>
       <c r="O87">
-        <v>-84.0596307720148</v>
+        <v>-85.57621466345026</v>
       </c>
       <c r="P87">
-        <v>-588.4174154041036</v>
+        <v>-599.0335026441518</v>
       </c>
       <c r="Q87">
-        <v>-578.3174154041036</v>
+        <v>-588.9335026441518</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.4242830971228224</v>
+        <v>0.4513176040601669</v>
       </c>
       <c r="T87">
-        <v>7.377340033142024</v>
+        <v>7.904292892652167</v>
       </c>
       <c r="U87">
         <v>0.2417366166625341</v>
       </c>
       <c r="V87">
-        <v>0.0434897685023629</v>
+        <v>0.04298407351977729</v>
       </c>
       <c r="W87">
-        <v>0.2312235471653361</v>
+        <v>0.2313457921594895</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8563,7 +8563,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3479181480189032</v>
+        <v>0.3438725881582182</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8571,22 +8571,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2621418458255843</v>
+        <v>0.2641012119922097</v>
       </c>
       <c r="C88">
-        <v>-2582.484805285649</v>
+        <v>-2644.447646095618</v>
       </c>
       <c r="D88">
-        <v>1337.523297777648</v>
+        <v>1325.750086073067</v>
       </c>
       <c r="E88">
-        <v>3950.745192524578</v>
+        <v>4000.934821629965</v>
       </c>
       <c r="F88">
-        <v>4316.308103063297</v>
+        <v>4366.497732168685</v>
       </c>
       <c r="G88">
         <v>396.3</v>
@@ -8607,37 +8607,37 @@
         <v>358.8</v>
       </c>
       <c r="M88">
-        <v>1043.409717307602</v>
+        <v>1055.542388439086</v>
       </c>
       <c r="N88">
-        <v>-684.6097173076021</v>
+        <v>-696.742388439086</v>
       </c>
       <c r="O88">
-        <v>-85.57621466345026</v>
+        <v>-87.09279855488575</v>
       </c>
       <c r="P88">
-        <v>-599.0335026441518</v>
+        <v>-609.6495898842002</v>
       </c>
       <c r="Q88">
-        <v>-588.9335026441518</v>
+        <v>-599.5495898842001</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4513176040601669</v>
+        <v>0.4825112659109489</v>
       </c>
       <c r="T88">
-        <v>7.904292892652167</v>
+        <v>8.512315422856181</v>
       </c>
       <c r="U88">
         <v>0.2417366166625341</v>
       </c>
       <c r="V88">
-        <v>0.04298407351977729</v>
+        <v>0.04249000370920513</v>
       </c>
       <c r="W88">
-        <v>0.2313457921594895</v>
+        <v>0.2314652269238923</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8645,7 +8645,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3438725881582182</v>
+        <v>0.339920029673641</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8653,22 +8653,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2641012119922097</v>
+        <v>0.266060578158835</v>
       </c>
       <c r="C89">
-        <v>-2644.447646095618</v>
+        <v>-2706.205033896753</v>
       </c>
       <c r="D89">
-        <v>1325.750086073067</v>
+        <v>1314.182327377319</v>
       </c>
       <c r="E89">
-        <v>4000.934821629965</v>
+        <v>4051.124450735353</v>
       </c>
       <c r="F89">
-        <v>4366.497732168685</v>
+        <v>4416.687361274072</v>
       </c>
       <c r="G89">
         <v>396.3</v>
@@ -8689,37 +8689,37 @@
         <v>358.8</v>
       </c>
       <c r="M89">
-        <v>1055.542388439086</v>
+        <v>1067.67505957057</v>
       </c>
       <c r="N89">
-        <v>-696.742388439086</v>
+        <v>-708.8750595705696</v>
       </c>
       <c r="O89">
-        <v>-87.09279855488575</v>
+        <v>-88.60938244632121</v>
       </c>
       <c r="P89">
-        <v>-609.6495898842002</v>
+        <v>-620.2656771242484</v>
       </c>
       <c r="Q89">
-        <v>-599.5495898842001</v>
+        <v>-610.1656771242484</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4825112659109489</v>
+        <v>0.5189038714035281</v>
       </c>
       <c r="T89">
-        <v>8.512315422856181</v>
+        <v>9.221675041427531</v>
       </c>
       <c r="U89">
         <v>0.2417366166625341</v>
       </c>
       <c r="V89">
-        <v>0.04249000370920513</v>
+        <v>0.04200716275796416</v>
       </c>
       <c r="W89">
-        <v>0.2314652269238923</v>
+        <v>0.2315819472618315</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8727,7 +8727,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.339920029673641</v>
+        <v>0.3360573020637132</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8735,22 +8735,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.266060578158835</v>
+        <v>0.2680199443254603</v>
       </c>
       <c r="C90">
-        <v>-2706.205033896753</v>
+        <v>-2767.762300175893</v>
       </c>
       <c r="D90">
-        <v>1314.182327377319</v>
+        <v>1302.814690203566</v>
       </c>
       <c r="E90">
-        <v>4051.124450735353</v>
+        <v>4101.31407984074</v>
       </c>
       <c r="F90">
-        <v>4416.687361274072</v>
+        <v>4466.876990379459</v>
       </c>
       <c r="G90">
         <v>396.3</v>
@@ -8771,37 +8771,37 @@
         <v>358.8</v>
       </c>
       <c r="M90">
-        <v>1067.67505957057</v>
+        <v>1079.807730702053</v>
       </c>
       <c r="N90">
-        <v>-708.8750595705696</v>
+        <v>-721.0077307020533</v>
       </c>
       <c r="O90">
-        <v>-88.60938244632121</v>
+        <v>-90.12596633775667</v>
       </c>
       <c r="P90">
-        <v>-620.2656771242484</v>
+        <v>-630.8817643642967</v>
       </c>
       <c r="Q90">
-        <v>-610.1656771242484</v>
+        <v>-620.7817643642967</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.5189038714035281</v>
+        <v>0.5619133142583943</v>
       </c>
       <c r="T90">
-        <v>9.221675041427531</v>
+        <v>10.06000913610276</v>
       </c>
       <c r="U90">
         <v>0.2417366166625341</v>
       </c>
       <c r="V90">
-        <v>0.04200716275796416</v>
+        <v>0.04153517216517805</v>
       </c>
       <c r="W90">
-        <v>0.2315819472618315</v>
+        <v>0.2316960446708281</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8809,7 +8809,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3360573020637132</v>
+        <v>0.3322813773214244</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8817,22 +8817,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2680199443254603</v>
+        <v>0.2699793104920857</v>
       </c>
       <c r="C91">
-        <v>-2767.762300175893</v>
+        <v>-2829.124593533046</v>
       </c>
       <c r="D91">
-        <v>1302.814690203566</v>
+        <v>1291.6420259518</v>
       </c>
       <c r="E91">
-        <v>4101.31407984074</v>
+        <v>4151.503708946128</v>
       </c>
       <c r="F91">
-        <v>4466.876990379459</v>
+        <v>4517.066619484846</v>
       </c>
       <c r="G91">
         <v>396.3</v>
@@ -8853,37 +8853,37 @@
         <v>358.8</v>
       </c>
       <c r="M91">
-        <v>1079.807730702053</v>
+        <v>1091.940401833537</v>
       </c>
       <c r="N91">
-        <v>-721.0077307020533</v>
+        <v>-733.1404018335372</v>
       </c>
       <c r="O91">
-        <v>-90.12596633775667</v>
+        <v>-91.64255022919215</v>
       </c>
       <c r="P91">
-        <v>-630.8817643642967</v>
+        <v>-641.4978516043451</v>
       </c>
       <c r="Q91">
-        <v>-620.7817643642967</v>
+        <v>-631.3978516043451</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.5619133142583943</v>
+        <v>0.6135246456842337</v>
       </c>
       <c r="T91">
-        <v>10.06000913610276</v>
+        <v>11.06601004971304</v>
       </c>
       <c r="U91">
         <v>0.2417366166625341</v>
       </c>
       <c r="V91">
-        <v>0.04153517216517805</v>
+        <v>0.04107367025223162</v>
       </c>
       <c r="W91">
-        <v>0.2316960446708281</v>
+        <v>0.231807606581847</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8891,7 +8891,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3322813773214244</v>
+        <v>0.3285893620178529</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8899,22 +8899,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2699793104920857</v>
+        <v>0.2719386766587111</v>
       </c>
       <c r="C92">
-        <v>-2829.124593533046</v>
+        <v>-2890.296887456705</v>
       </c>
       <c r="D92">
-        <v>1291.6420259518</v>
+        <v>1280.659361133529</v>
       </c>
       <c r="E92">
-        <v>4151.503708946128</v>
+        <v>4201.693338051515</v>
       </c>
       <c r="F92">
-        <v>4517.066619484846</v>
+        <v>4567.256248590234</v>
       </c>
       <c r="G92">
         <v>396.3</v>
@@ -8935,37 +8935,37 @@
         <v>358.8</v>
       </c>
       <c r="M92">
-        <v>1091.940401833537</v>
+        <v>1104.073072965021</v>
       </c>
       <c r="N92">
-        <v>-733.1404018335372</v>
+        <v>-745.2730729650209</v>
       </c>
       <c r="O92">
-        <v>-91.64255022919215</v>
+        <v>-93.15913412062761</v>
       </c>
       <c r="P92">
-        <v>-641.4978516043451</v>
+        <v>-652.1139388443933</v>
       </c>
       <c r="Q92">
-        <v>-631.3978516043451</v>
+        <v>-642.0139388443932</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.6135246456842337</v>
+        <v>0.6766051618713709</v>
       </c>
       <c r="T92">
-        <v>11.06601004971304</v>
+        <v>12.29556672190338</v>
       </c>
       <c r="U92">
         <v>0.2417366166625341</v>
       </c>
       <c r="V92">
-        <v>0.04107367025223162</v>
+        <v>0.04062231123847084</v>
       </c>
       <c r="W92">
-        <v>0.231807606581847</v>
+        <v>0.2319167165827337</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8973,7 +8973,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3285893620178529</v>
+        <v>0.3249784899077667</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8981,22 +8981,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2719386766587111</v>
+        <v>0.2738980428253364</v>
       </c>
       <c r="C93">
-        <v>-2890.296887456705</v>
+        <v>-2951.283987705831</v>
       </c>
       <c r="D93">
-        <v>1280.659361133529</v>
+        <v>1269.86188998979</v>
       </c>
       <c r="E93">
-        <v>4201.693338051515</v>
+        <v>4251.882967156902</v>
       </c>
       <c r="F93">
-        <v>4567.256248590234</v>
+        <v>4617.445877695621</v>
       </c>
       <c r="G93">
         <v>396.3</v>
@@ -9017,37 +9017,37 @@
         <v>358.8</v>
       </c>
       <c r="M93">
-        <v>1104.073072965021</v>
+        <v>1116.205744096505</v>
       </c>
       <c r="N93">
-        <v>-745.2730729650209</v>
+        <v>-757.4057440965046</v>
       </c>
       <c r="O93">
-        <v>-93.15913412062761</v>
+        <v>-94.67571801206307</v>
       </c>
       <c r="P93">
-        <v>-652.1139388443933</v>
+        <v>-662.7300260844415</v>
       </c>
       <c r="Q93">
-        <v>-642.0139388443932</v>
+        <v>-652.6300260844415</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.6766051618713709</v>
+        <v>0.7554558071052925</v>
       </c>
       <c r="T93">
-        <v>12.29556672190338</v>
+        <v>13.8325125621413</v>
       </c>
       <c r="U93">
         <v>0.2417366166625341</v>
       </c>
       <c r="V93">
-        <v>0.04062231123847084</v>
+        <v>0.04018076437718311</v>
       </c>
       <c r="W93">
-        <v>0.2319167165827337</v>
+        <v>0.2320234546270794</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9055,7 +9055,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3249784899077667</v>
+        <v>0.3214461150174649</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9063,22 +9063,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2738980428253364</v>
+        <v>0.2758574089919618</v>
       </c>
       <c r="C94">
-        <v>-2951.283987705831</v>
+        <v>-3012.090539321528</v>
       </c>
       <c r="D94">
-        <v>1269.86188998979</v>
+        <v>1259.24496747948</v>
       </c>
       <c r="E94">
-        <v>4251.882967156902</v>
+        <v>4302.072596262289</v>
       </c>
       <c r="F94">
-        <v>4617.445877695621</v>
+        <v>4667.635506801008</v>
       </c>
       <c r="G94">
         <v>396.3</v>
@@ -9099,37 +9099,37 @@
         <v>358.8</v>
       </c>
       <c r="M94">
-        <v>1116.205744096505</v>
+        <v>1128.338415227988</v>
       </c>
       <c r="N94">
-        <v>-757.4057440965046</v>
+        <v>-769.5384152279885</v>
       </c>
       <c r="O94">
-        <v>-94.67571801206307</v>
+        <v>-96.19230190349856</v>
       </c>
       <c r="P94">
-        <v>-662.7300260844415</v>
+        <v>-673.3461133244899</v>
       </c>
       <c r="Q94">
-        <v>-652.6300260844415</v>
+        <v>-663.2461133244899</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.7554558071052925</v>
+        <v>0.8568352081203343</v>
       </c>
       <c r="T94">
-        <v>13.8325125621413</v>
+        <v>15.80858578530435</v>
       </c>
       <c r="U94">
         <v>0.2417366166625341</v>
       </c>
       <c r="V94">
-        <v>0.04018076437718311</v>
+        <v>0.03974871314732092</v>
       </c>
       <c r="W94">
-        <v>0.2320234546270794</v>
+        <v>0.2321278972296112</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9137,7 +9137,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3214461150174649</v>
+        <v>0.3179897051785674</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9145,22 +9145,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2758574089919618</v>
+        <v>0.277816775158587</v>
       </c>
       <c r="C95">
-        <v>-3012.090539321528</v>
+        <v>-3072.721033289899</v>
       </c>
       <c r="D95">
-        <v>1259.24496747948</v>
+        <v>1248.804102616496</v>
       </c>
       <c r="E95">
-        <v>4302.072596262289</v>
+        <v>4352.262225367676</v>
       </c>
       <c r="F95">
-        <v>4667.635506801008</v>
+        <v>4717.825135906395</v>
       </c>
       <c r="G95">
         <v>396.3</v>
@@ -9181,37 +9181,37 @@
         <v>358.8</v>
       </c>
       <c r="M95">
-        <v>1128.338415227988</v>
+        <v>1140.471086359472</v>
       </c>
       <c r="N95">
-        <v>-769.5384152279885</v>
+        <v>-781.6710863594722</v>
       </c>
       <c r="O95">
-        <v>-96.19230190349856</v>
+        <v>-97.70888579493402</v>
       </c>
       <c r="P95">
-        <v>-673.3461133244899</v>
+        <v>-683.9622005645381</v>
       </c>
       <c r="Q95">
-        <v>-663.2461133244899</v>
+        <v>-673.8622005645381</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.8568352081203343</v>
+        <v>0.9920077428070568</v>
       </c>
       <c r="T95">
-        <v>15.80858578530435</v>
+        <v>18.44335008285508</v>
       </c>
       <c r="U95">
         <v>0.2417366166625341</v>
       </c>
       <c r="V95">
-        <v>0.03974871314732092</v>
+        <v>0.03932585449681751</v>
       </c>
       <c r="W95">
-        <v>0.2321278972296112</v>
+        <v>0.2322301176491103</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9219,7 +9219,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3179897051785674</v>
+        <v>0.3146068359745401</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9227,22 +9227,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.277816775158587</v>
+        <v>0.2797761413252124</v>
       </c>
       <c r="C96">
-        <v>-3072.721033289899</v>
+        <v>-3133.179812876162</v>
       </c>
       <c r="D96">
-        <v>1248.804102616496</v>
+        <v>1238.534952135622</v>
       </c>
       <c r="E96">
-        <v>4352.262225367676</v>
+        <v>4402.451854473064</v>
       </c>
       <c r="F96">
-        <v>4717.825135906395</v>
+        <v>4768.014765011783</v>
       </c>
       <c r="G96">
         <v>396.3</v>
@@ -9263,37 +9263,37 @@
         <v>358.8</v>
       </c>
       <c r="M96">
-        <v>1140.471086359472</v>
+        <v>1152.603757490956</v>
       </c>
       <c r="N96">
-        <v>-781.6710863594722</v>
+        <v>-793.8037574909561</v>
       </c>
       <c r="O96">
-        <v>-97.70888579493402</v>
+        <v>-99.22546968636951</v>
       </c>
       <c r="P96">
-        <v>-683.9622005645381</v>
+        <v>-694.5782878045866</v>
       </c>
       <c r="Q96">
-        <v>-673.8622005645381</v>
+        <v>-684.4782878045866</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.9920077428070568</v>
+        <v>1.181249291368469</v>
       </c>
       <c r="T96">
-        <v>18.44335008285508</v>
+        <v>22.1320200994261</v>
       </c>
       <c r="U96">
         <v>0.2417366166625341</v>
       </c>
       <c r="V96">
-        <v>0.03932585449681751</v>
+        <v>0.03891189813369311</v>
       </c>
       <c r="W96">
-        <v>0.2322301176491103</v>
+        <v>0.232330186059778</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9301,7 +9301,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3146068359745401</v>
+        <v>0.3112951850695449</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9309,22 +9309,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2797761413252124</v>
+        <v>0.2817355074918377</v>
       </c>
       <c r="C97">
-        <v>-3133.179812876162</v>
+        <v>-3193.471079648788</v>
       </c>
       <c r="D97">
-        <v>1238.534952135622</v>
+        <v>1228.433314468382</v>
       </c>
       <c r="E97">
-        <v>4402.451854473064</v>
+        <v>4452.641483578452</v>
       </c>
       <c r="F97">
-        <v>4768.014765011783</v>
+        <v>4818.204394117171</v>
       </c>
       <c r="G97">
         <v>396.3</v>
@@ -9345,37 +9345,37 @@
         <v>358.8</v>
       </c>
       <c r="M97">
-        <v>1152.603757490956</v>
+        <v>1164.73642862244</v>
       </c>
       <c r="N97">
-        <v>-793.8037574909561</v>
+        <v>-805.93642862244</v>
       </c>
       <c r="O97">
-        <v>-99.22546968636951</v>
+        <v>-100.742053577805</v>
       </c>
       <c r="P97">
-        <v>-694.5782878045866</v>
+        <v>-705.194375044635</v>
       </c>
       <c r="Q97">
-        <v>-684.4782878045866</v>
+        <v>-695.0943750446349</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.181249291368469</v>
+        <v>1.465111614210587</v>
       </c>
       <c r="T97">
-        <v>22.1320200994261</v>
+        <v>27.66502512428264</v>
       </c>
       <c r="U97">
         <v>0.2417366166625341</v>
       </c>
       <c r="V97">
-        <v>0.03891189813369311</v>
+        <v>0.03850656586146714</v>
       </c>
       <c r="W97">
-        <v>0.232330186059778</v>
+        <v>0.23242816971189</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9383,7 +9383,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3112951850695449</v>
+        <v>0.308052526891737</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9391,22 +9391,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2817355074918377</v>
+        <v>0.2836948736584631</v>
       </c>
       <c r="C98">
-        <v>-3193.471079648788</v>
+        <v>-3253.598899211244</v>
       </c>
       <c r="D98">
-        <v>1228.433314468382</v>
+        <v>1218.495124011313</v>
       </c>
       <c r="E98">
-        <v>4452.641483578451</v>
+        <v>4502.831112683838</v>
       </c>
       <c r="F98">
-        <v>4818.20439411717</v>
+        <v>4868.394023222557</v>
       </c>
       <c r="G98">
         <v>396.3</v>
@@ -9427,37 +9427,37 @@
         <v>358.8</v>
       </c>
       <c r="M98">
-        <v>1164.73642862244</v>
+        <v>1176.869099753923</v>
       </c>
       <c r="N98">
-        <v>-805.9364286224397</v>
+        <v>-818.0690997539234</v>
       </c>
       <c r="O98">
-        <v>-100.742053577805</v>
+        <v>-102.2586374692404</v>
       </c>
       <c r="P98">
-        <v>-705.1943750446347</v>
+        <v>-715.810462284683</v>
       </c>
       <c r="Q98">
-        <v>-695.0943750446347</v>
+        <v>-705.710462284683</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.465111614210583</v>
+        <v>1.938215485614111</v>
       </c>
       <c r="T98">
-        <v>27.66502512428257</v>
+        <v>36.88670016571009</v>
       </c>
       <c r="U98">
         <v>0.2417366166625341</v>
       </c>
       <c r="V98">
-        <v>0.03850656586146715</v>
+        <v>0.03810959095567883</v>
       </c>
       <c r="W98">
-        <v>0.23242816971189</v>
+        <v>0.2325241330825152</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9465,7 +9465,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3080525268917371</v>
+        <v>0.3048767276454306</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9473,22 +9473,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2836948736584631</v>
+        <v>0.2856542398250884</v>
       </c>
       <c r="C99">
-        <v>-3253.598899211244</v>
+        <v>-3313.567206657719</v>
       </c>
       <c r="D99">
-        <v>1218.495124011313</v>
+        <v>1208.716445670225</v>
       </c>
       <c r="E99">
-        <v>4502.831112683838</v>
+        <v>4553.020741789225</v>
       </c>
       <c r="F99">
-        <v>4868.394023222557</v>
+        <v>4918.583652327944</v>
       </c>
       <c r="G99">
         <v>396.3</v>
@@ -9509,37 +9509,37 @@
         <v>358.8</v>
       </c>
       <c r="M99">
-        <v>1176.869099753923</v>
+        <v>1189.001770885407</v>
       </c>
       <c r="N99">
-        <v>-818.0690997539234</v>
+        <v>-830.2017708854071</v>
       </c>
       <c r="O99">
-        <v>-102.2586374692404</v>
+        <v>-103.7752213606759</v>
       </c>
       <c r="P99">
-        <v>-715.810462284683</v>
+        <v>-726.4265495247312</v>
       </c>
       <c r="Q99">
-        <v>-705.710462284683</v>
+        <v>-716.3265495247311</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.938215485614111</v>
+        <v>2.884423228421166</v>
       </c>
       <c r="T99">
-        <v>36.88670016571009</v>
+        <v>55.33005024856514</v>
       </c>
       <c r="U99">
         <v>0.2417366166625341</v>
       </c>
       <c r="V99">
-        <v>0.03810959095567883</v>
+        <v>0.03772071757858007</v>
       </c>
       <c r="W99">
-        <v>0.2325241330825152</v>
+        <v>0.2326181380170052</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9547,7 +9547,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3048767276454306</v>
+        <v>0.3017657406286405</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9555,22 +9555,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2856542398250884</v>
+        <v>0.2876136059917138</v>
       </c>
       <c r="C100">
-        <v>-3313.567206657719</v>
+        <v>-3373.379811768256</v>
       </c>
       <c r="D100">
-        <v>1208.716445670225</v>
+        <v>1199.093469665075</v>
       </c>
       <c r="E100">
-        <v>4553.020741789225</v>
+        <v>4603.210370894612</v>
       </c>
       <c r="F100">
-        <v>4918.583652327944</v>
+        <v>4968.773281433331</v>
       </c>
       <c r="G100">
         <v>396.3</v>
@@ -9591,37 +9591,37 @@
         <v>358.8</v>
       </c>
       <c r="M100">
-        <v>1189.001770885407</v>
+        <v>1201.134442016891</v>
       </c>
       <c r="N100">
-        <v>-830.2017708854071</v>
+        <v>-842.334442016891</v>
       </c>
       <c r="O100">
-        <v>-103.7752213606759</v>
+        <v>-105.2918052521114</v>
       </c>
       <c r="P100">
-        <v>-726.4265495247312</v>
+        <v>-737.0426367647797</v>
       </c>
       <c r="Q100">
-        <v>-716.3265495247311</v>
+        <v>-726.9426367647796</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.884423228421166</v>
+        <v>5.723046456842332</v>
       </c>
       <c r="T100">
-        <v>55.33005024856514</v>
+        <v>110.6601004971303</v>
       </c>
       <c r="U100">
         <v>0.2417366166625341</v>
       </c>
       <c r="V100">
-        <v>0.03772071757858007</v>
+        <v>0.03733970022930148</v>
       </c>
       <c r="W100">
-        <v>0.2326181380170052</v>
+        <v>0.2327102438619095</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9629,91 +9629,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3017657406286405</v>
+        <v>0.2987176018344118</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2876136059917138</v>
-      </c>
-      <c r="C101">
-        <v>-3373.379811768256</v>
-      </c>
-      <c r="D101">
-        <v>1199.093469665075</v>
-      </c>
-      <c r="E101">
-        <v>4603.210370894612</v>
-      </c>
-      <c r="F101">
-        <v>4968.773281433331</v>
-      </c>
-      <c r="G101">
-        <v>396.3</v>
-      </c>
-      <c r="H101">
-        <v>4653.4</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>368.9</v>
-      </c>
-      <c r="K101">
-        <v>10.1</v>
-      </c>
-      <c r="L101">
-        <v>358.8</v>
-      </c>
-      <c r="M101">
-        <v>1201.134442016891</v>
-      </c>
-      <c r="N101">
-        <v>-842.334442016891</v>
-      </c>
-      <c r="O101">
-        <v>-105.2918052521114</v>
-      </c>
-      <c r="P101">
-        <v>-737.0426367647797</v>
-      </c>
-      <c r="Q101">
-        <v>-726.9426367647796</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>5.723046456842332</v>
-      </c>
-      <c r="T101">
-        <v>110.6601004971303</v>
-      </c>
-      <c r="U101">
-        <v>0.2417366166625341</v>
-      </c>
-      <c r="V101">
-        <v>0.03733970022930148</v>
-      </c>
-      <c r="W101">
-        <v>0.2327102438619095</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.2987176018344118</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
